--- a/Send_Message/Send_Message_Test_Cases.xlsx
+++ b/Send_Message/Send_Message_Test_Cases.xlsx
@@ -410,7 +410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H143"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="15.86" customWidth="1" style="7" min="1" max="1"/>
@@ -4312,40 +4312,1153 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="15.75" customHeight="1" s="7"/>
-    <row r="111" ht="15.75" customHeight="1" s="7"/>
-    <row r="112" ht="15.75" customHeight="1" s="7"/>
-    <row r="113" ht="15.75" customHeight="1" s="7"/>
-    <row r="114" ht="15.75" customHeight="1" s="7"/>
-    <row r="115" ht="15.75" customHeight="1" s="7"/>
-    <row r="116" ht="15.75" customHeight="1" s="7"/>
-    <row r="117" ht="15.75" customHeight="1" s="7"/>
-    <row r="118" ht="15.75" customHeight="1" s="7"/>
-    <row r="119" ht="15.75" customHeight="1" s="7"/>
-    <row r="120" ht="15.75" customHeight="1" s="7"/>
-    <row r="121" ht="15.75" customHeight="1" s="7"/>
-    <row r="122" ht="15.75" customHeight="1" s="7"/>
-    <row r="123" ht="15.75" customHeight="1" s="7"/>
-    <row r="124" ht="15.75" customHeight="1" s="7"/>
-    <row r="125" ht="15.75" customHeight="1" s="7"/>
-    <row r="126" ht="15.75" customHeight="1" s="7"/>
-    <row r="127" ht="15.75" customHeight="1" s="7"/>
-    <row r="128" ht="15.75" customHeight="1" s="7"/>
-    <row r="129" ht="15.75" customHeight="1" s="7"/>
-    <row r="130" ht="15.75" customHeight="1" s="7"/>
-    <row r="131" ht="15.75" customHeight="1" s="7"/>
-    <row r="132" ht="15.75" customHeight="1" s="7"/>
-    <row r="133" ht="15.75" customHeight="1" s="7"/>
-    <row r="134" ht="15.75" customHeight="1" s="7"/>
-    <row r="135" ht="15.75" customHeight="1" s="7"/>
-    <row r="136" ht="15.75" customHeight="1" s="7"/>
-    <row r="137" ht="15.75" customHeight="1" s="7"/>
-    <row r="138" ht="15.75" customHeight="1" s="7"/>
-    <row r="139" ht="15.75" customHeight="1" s="7"/>
-    <row r="140" ht="15.75" customHeight="1" s="7"/>
-    <row r="141" ht="15.75" customHeight="1" s="7"/>
-    <row r="142" ht="15.75" customHeight="1" s="7"/>
-    <row r="143" ht="15.75" customHeight="1" s="7"/>
+    <row r="110" ht="15.75" customHeight="1" s="7">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>MSG_109</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C110" s="11" t="inlineStr">
+        <is>
+          <t>Integration: Send Message with Delivery</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>Verify sent message shows sent/delivered/read status progression</t>
+        </is>
+      </c>
+      <c r="F110" s="11" t="inlineStr">
+        <is>
+          <t>1. Send a message.
+2. Observe status indicators over time.</t>
+        </is>
+      </c>
+      <c r="G110" s="11" t="inlineStr">
+        <is>
+          <t>Message should progress: sending → sent (single tick) → delivered (double tick) → read (blue tick).</t>
+        </is>
+      </c>
+      <c r="H110" s="11" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="15.75" customHeight="1" s="7">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>MSG_110</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr"/>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>Integration: Send Message with Push Notification</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr"/>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>Verify sent message triggers push notification for receiver</t>
+        </is>
+      </c>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>1. Send a message to User B (app in background).</t>
+        </is>
+      </c>
+      <c r="G111" s="11" t="inlineStr">
+        <is>
+          <t>User B should receive a push notification with sender name and message preview.</t>
+        </is>
+      </c>
+      <c r="H111" s="11" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="15.75" customHeight="1" s="7">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>MSG_111</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="inlineStr"/>
+      <c r="C112" s="11" t="inlineStr">
+        <is>
+          <t>Integration: Send Message with Conversation List</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="inlineStr"/>
+      <c r="E112" s="11" t="inlineStr">
+        <is>
+          <t>Verify sent message updates conversation list for both sender and receiver</t>
+        </is>
+      </c>
+      <c r="F112" s="11" t="inlineStr">
+        <is>
+          <t>1. Send a message.
+2. Check conversation list on both devices.</t>
+        </is>
+      </c>
+      <c r="G112" s="11" t="inlineStr">
+        <is>
+          <t>Both sender and receiver conversation lists should update with latest message preview.</t>
+        </is>
+      </c>
+      <c r="H112" s="11" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="15.75" customHeight="1" s="7">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>MSG_112</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>Regression: Send Message</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>Verify message sending works after failed attempt</t>
+        </is>
+      </c>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>1. Send a message during network error (fails).
+2. Restore network.
+3. Retry sending.</t>
+        </is>
+      </c>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>Message should send successfully on retry. No duplicate messages.</t>
+        </is>
+      </c>
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="15.75" customHeight="1" s="7">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t>MSG_113</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr"/>
+      <c r="C114" s="11" t="inlineStr"/>
+      <c r="D114" s="11" t="inlineStr"/>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>Verify message order preserved after rapid sending</t>
+        </is>
+      </c>
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>1. Send 10 messages rapidly one after another.</t>
+        </is>
+      </c>
+      <c r="G114" s="11" t="inlineStr">
+        <is>
+          <t>All 10 messages should appear in the exact order they were sent.</t>
+        </is>
+      </c>
+      <c r="H114" s="11" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="15.75" customHeight="1" s="7">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>MSG_114</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr"/>
+      <c r="C115" s="11" t="inlineStr"/>
+      <c r="D115" s="11" t="inlineStr"/>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>Verify media message sending after app crash recovery</t>
+        </is>
+      </c>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>1. Start uploading a large file.
+2. Force close app.
+3. Reopen.</t>
+        </is>
+      </c>
+      <c r="G115" s="11" t="inlineStr">
+        <is>
+          <t>Upload should either resume or show failed state with retry option.</t>
+        </is>
+      </c>
+      <c r="H115" s="11" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="15.75" customHeight="1" s="7">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>MSG_115</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>Security: Send Message</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>Verify message cannot be sent to unauthorized conversation</t>
+        </is>
+      </c>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>1. Try to send a message to a group you've been removed from.</t>
+        </is>
+      </c>
+      <c r="G116" s="11" t="inlineStr">
+        <is>
+          <t>Message should fail with appropriate error. No message delivered.</t>
+        </is>
+      </c>
+      <c r="H116" s="11" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="15.75" customHeight="1" s="7">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>MSG_116</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr"/>
+      <c r="C117" s="11" t="inlineStr"/>
+      <c r="D117" s="11" t="inlineStr"/>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>Verify file upload scans for malware (if applicable)</t>
+        </is>
+      </c>
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>1. Upload a file flagged as potentially malicious.</t>
+        </is>
+      </c>
+      <c r="G117" s="11" t="inlineStr">
+        <is>
+          <t>File should be rejected or quarantined based on security policy.</t>
+        </is>
+      </c>
+      <c r="H117" s="11" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="15.75" customHeight="1" s="7">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t>MSG_117</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr"/>
+      <c r="C118" s="11" t="inlineStr"/>
+      <c r="D118" s="11" t="inlineStr"/>
+      <c r="E118" s="11" t="inlineStr">
+        <is>
+          <t>Verify message encryption in transit</t>
+        </is>
+      </c>
+      <c r="F118" s="11" t="inlineStr">
+        <is>
+          <t>1. Send a message.
+2. Inspect network traffic.</t>
+        </is>
+      </c>
+      <c r="G118" s="11" t="inlineStr">
+        <is>
+          <t>Message content should be encrypted (HTTPS/WSS). Not visible in plain text.</t>
+        </is>
+      </c>
+      <c r="H118" s="11" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="15.75" customHeight="1" s="7">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t>MSG_118</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr"/>
+      <c r="C119" s="11" t="inlineStr"/>
+      <c r="D119" s="11" t="inlineStr"/>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>Verify spoofed sender ID prevention</t>
+        </is>
+      </c>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>1. Try to send a message with a manipulated sender ID via API.</t>
+        </is>
+      </c>
+      <c r="G119" s="11" t="inlineStr">
+        <is>
+          <t>Server should reject the message. Sender ID should be validated server-side.</t>
+        </is>
+      </c>
+      <c r="H119" s="11" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="15.75" customHeight="1" s="7">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>MSG_119</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>Edge Case: Send Message</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending message while receiver is typing</t>
+        </is>
+      </c>
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>1. Both users type simultaneously.
+2. Both send at the same time.</t>
+        </is>
+      </c>
+      <c r="G120" s="11" t="inlineStr">
+        <is>
+          <t>Both messages should appear in correct order. No message loss.</t>
+        </is>
+      </c>
+      <c r="H120" s="11" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="15.75" customHeight="1" s="7">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>MSG_120</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr"/>
+      <c r="C121" s="11" t="inlineStr"/>
+      <c r="D121" s="11" t="inlineStr"/>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending message to a user who blocked you</t>
+        </is>
+      </c>
+      <c r="F121" s="11" t="inlineStr">
+        <is>
+          <t>1. Send a message to a user who has blocked you.</t>
+        </is>
+      </c>
+      <c r="G121" s="11" t="inlineStr">
+        <is>
+          <t>Message should fail or appear sent but not delivered. Appropriate handling per app policy.</t>
+        </is>
+      </c>
+      <c r="H121" s="11" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="15.75" customHeight="1" s="7">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>MSG_121</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr"/>
+      <c r="C122" s="11" t="inlineStr"/>
+      <c r="D122" s="11" t="inlineStr"/>
+      <c r="E122" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending message immediately after joining a group</t>
+        </is>
+      </c>
+      <c r="F122" s="11" t="inlineStr">
+        <is>
+          <t>1. Join a new group.
+2. Immediately send a message.</t>
+        </is>
+      </c>
+      <c r="G122" s="11" t="inlineStr">
+        <is>
+          <t>Message should send successfully. Should appear for all group members.</t>
+        </is>
+      </c>
+      <c r="H122" s="11" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="15.75" customHeight="1" s="7">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>MSG_122</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr"/>
+      <c r="C123" s="11" t="inlineStr"/>
+      <c r="D123" s="11" t="inlineStr"/>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending multiple media types in sequence</t>
+        </is>
+      </c>
+      <c r="F123" s="11" t="inlineStr">
+        <is>
+          <t>1. Send an image.
+2. Immediately send a video.
+3. Send a document.</t>
+        </is>
+      </c>
+      <c r="G123" s="11" t="inlineStr">
+        <is>
+          <t>All three should upload and appear in correct order. No upload conflicts.</t>
+        </is>
+      </c>
+      <c r="H123" s="11" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="15.75" customHeight="1" s="7">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>MSG_123</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="inlineStr">
+        <is>
+          <t>Edge Case: Send Message</t>
+        </is>
+      </c>
+      <c r="D124" s="11" t="inlineStr"/>
+      <c r="E124" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending message with zero-width characters</t>
+        </is>
+      </c>
+      <c r="F124" s="11" t="inlineStr">
+        <is>
+          <t>1. Send a message containing only zero-width unicode characters.</t>
+        </is>
+      </c>
+      <c r="G124" s="11" t="inlineStr">
+        <is>
+          <t>Message should be blocked or displayed as empty. No invisible messages.</t>
+        </is>
+      </c>
+      <c r="H124" s="11" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="15.75" customHeight="1" s="7">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>MSG_124</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="inlineStr"/>
+      <c r="C125" s="11" t="inlineStr"/>
+      <c r="D125" s="11" t="inlineStr"/>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending corrupted media file</t>
+        </is>
+      </c>
+      <c r="F125" s="11" t="inlineStr">
+        <is>
+          <t>1. Rename a .txt file to .jpg.
+2. Try to send as image.</t>
+        </is>
+      </c>
+      <c r="G125" s="11" t="inlineStr">
+        <is>
+          <t>App should detect invalid file and show error. Should not crash.</t>
+        </is>
+      </c>
+      <c r="H125" s="11" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="15.75" customHeight="1" s="7">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>MSG_125</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
+          <t>Boundary: Send Message</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending text message with exactly 1 character</t>
+        </is>
+      </c>
+      <c r="F126" s="11" t="inlineStr">
+        <is>
+          <t>1. Send 'a'.</t>
+        </is>
+      </c>
+      <c r="G126" s="11" t="inlineStr">
+        <is>
+          <t>Single character message should send and display correctly.</t>
+        </is>
+      </c>
+      <c r="H126" s="11" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="15.75" customHeight="1" s="7">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>MSG_126</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr"/>
+      <c r="C127" s="11" t="inlineStr"/>
+      <c r="D127" s="11" t="inlineStr"/>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending text at max character limit</t>
+        </is>
+      </c>
+      <c r="F127" s="11" t="inlineStr">
+        <is>
+          <t>1. Send a message at exactly the maximum character limit.</t>
+        </is>
+      </c>
+      <c r="G127" s="11" t="inlineStr">
+        <is>
+          <t>Message should send successfully.</t>
+        </is>
+      </c>
+      <c r="H127" s="11" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="15.75" customHeight="1" s="7">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>MSG_127</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="inlineStr"/>
+      <c r="D128" s="11" t="inlineStr"/>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending text exceeding max character limit</t>
+        </is>
+      </c>
+      <c r="F128" s="11" t="inlineStr">
+        <is>
+          <t>1. Try to send a message exceeding the max limit.</t>
+        </is>
+      </c>
+      <c r="G128" s="11" t="inlineStr">
+        <is>
+          <t>Should be blocked at input or rejected by server with error.</t>
+        </is>
+      </c>
+      <c r="H128" s="11" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="15.75" customHeight="1" s="7">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>MSG_128</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr"/>
+      <c r="D129" s="11" t="inlineStr"/>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending media at minimum file size (1 byte)</t>
+        </is>
+      </c>
+      <c r="F129" s="11" t="inlineStr">
+        <is>
+          <t>1. Send a 1-byte file.</t>
+        </is>
+      </c>
+      <c r="G129" s="11" t="inlineStr">
+        <is>
+          <t>File should either send or be rejected as too small. No crash.</t>
+        </is>
+      </c>
+      <c r="H129" s="11" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="15.75" customHeight="1" s="7">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>MSG_129</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr"/>
+      <c r="C130" s="11" t="inlineStr"/>
+      <c r="D130" s="11" t="inlineStr"/>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending media at exactly max file size</t>
+        </is>
+      </c>
+      <c r="F130" s="11" t="inlineStr">
+        <is>
+          <t>1. Send a file at exactly the maximum allowed size.</t>
+        </is>
+      </c>
+      <c r="G130" s="11" t="inlineStr">
+        <is>
+          <t>File should upload and send successfully.</t>
+        </is>
+      </c>
+      <c r="H130" s="11" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="15.75" customHeight="1" s="7">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>MSG_130</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning: Message Destinations</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending message in one-on-one chat</t>
+        </is>
+      </c>
+      <c r="F131" s="11" t="inlineStr">
+        <is>
+          <t>1. Open a one-on-one conversation.
+2. Send a text message.</t>
+        </is>
+      </c>
+      <c r="G131" s="11" t="inlineStr">
+        <is>
+          <t>Message should deliver to the single recipient.</t>
+        </is>
+      </c>
+      <c r="H131" s="11" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="15.75" customHeight="1" s="7">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>MSG_131</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr"/>
+      <c r="C132" s="11" t="inlineStr"/>
+      <c r="D132" s="11" t="inlineStr"/>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending message in small group (2-10 members)</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="inlineStr">
+        <is>
+          <t>1. Open a group with 5 members.
+2. Send a message.</t>
+        </is>
+      </c>
+      <c r="G132" s="11" t="inlineStr">
+        <is>
+          <t>Message should deliver to all group members.</t>
+        </is>
+      </c>
+      <c r="H132" s="11" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="15.75" customHeight="1" s="7">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>MSG_132</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="inlineStr"/>
+      <c r="C133" s="11" t="inlineStr"/>
+      <c r="D133" s="11" t="inlineStr"/>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending message in large group (100+ members)</t>
+        </is>
+      </c>
+      <c r="F133" s="11" t="inlineStr">
+        <is>
+          <t>1. Open a group with 100+ members.
+2. Send a message.</t>
+        </is>
+      </c>
+      <c r="G133" s="11" t="inlineStr">
+        <is>
+          <t>Message should deliver to all members. May have slight delay but should complete.</t>
+        </is>
+      </c>
+      <c r="H133" s="11" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="15.75" customHeight="1" s="7">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>MSG_133</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr"/>
+      <c r="C134" s="11" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning: Image Formats</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending JPEG image</t>
+        </is>
+      </c>
+      <c r="F134" s="11" t="inlineStr">
+        <is>
+          <t>1. Send a .jpg image.</t>
+        </is>
+      </c>
+      <c r="G134" s="11" t="inlineStr">
+        <is>
+          <t>Image should upload and display correctly.</t>
+        </is>
+      </c>
+      <c r="H134" s="11" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="15.75" customHeight="1" s="7">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>MSG_134</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="inlineStr"/>
+      <c r="C135" s="11" t="inlineStr"/>
+      <c r="D135" s="11" t="inlineStr"/>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending PNG image</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="inlineStr">
+        <is>
+          <t>1. Send a .png image.</t>
+        </is>
+      </c>
+      <c r="G135" s="11" t="inlineStr">
+        <is>
+          <t>Image should upload and display correctly with transparency if applicable.</t>
+        </is>
+      </c>
+      <c r="H135" s="11" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="15.75" customHeight="1" s="7">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>MSG_135</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="inlineStr"/>
+      <c r="C136" s="11" t="inlineStr"/>
+      <c r="D136" s="11" t="inlineStr"/>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending GIF image</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr">
+        <is>
+          <t>1. Send a .gif image.</t>
+        </is>
+      </c>
+      <c r="G136" s="11" t="inlineStr">
+        <is>
+          <t>GIF should upload and animate in chat.</t>
+        </is>
+      </c>
+      <c r="H136" s="11" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="15.75" customHeight="1" s="7">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>MSG_136</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="inlineStr"/>
+      <c r="C137" s="11" t="inlineStr"/>
+      <c r="D137" s="11" t="inlineStr"/>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending WebP image</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>1. Send a .webp image.</t>
+        </is>
+      </c>
+      <c r="G137" s="11" t="inlineStr">
+        <is>
+          <t>Image should upload and display correctly.</t>
+        </is>
+      </c>
+      <c r="H137" s="11" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="15.75" customHeight="1" s="7">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>MSG_137</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="inlineStr"/>
+      <c r="C138" s="11" t="inlineStr"/>
+      <c r="D138" s="11" t="inlineStr"/>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending SVG image</t>
+        </is>
+      </c>
+      <c r="F138" s="11" t="inlineStr">
+        <is>
+          <t>1. Send a .svg file.</t>
+        </is>
+      </c>
+      <c r="G138" s="11" t="inlineStr">
+        <is>
+          <t>Should either render or be treated as document. No XSS via SVG.</t>
+        </is>
+      </c>
+      <c r="H138" s="11" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="15.75" customHeight="1" s="7">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>MSG_138</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="inlineStr"/>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning: Video Formats</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr"/>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending MP4 video</t>
+        </is>
+      </c>
+      <c r="F139" s="11" t="inlineStr">
+        <is>
+          <t>1. Send a .mp4 video.</t>
+        </is>
+      </c>
+      <c r="G139" s="11" t="inlineStr">
+        <is>
+          <t>Video should upload with thumbnail and be playable.</t>
+        </is>
+      </c>
+      <c r="H139" s="11" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="15.75" customHeight="1" s="7">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>MSG_139</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="inlineStr"/>
+      <c r="C140" s="11" t="inlineStr"/>
+      <c r="D140" s="11" t="inlineStr"/>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending MOV video</t>
+        </is>
+      </c>
+      <c r="F140" s="11" t="inlineStr">
+        <is>
+          <t>1. Send a .mov video.</t>
+        </is>
+      </c>
+      <c r="G140" s="11" t="inlineStr">
+        <is>
+          <t>Video should upload and be playable.</t>
+        </is>
+      </c>
+      <c r="H140" s="11" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="15.75" customHeight="1" s="7">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
+          <t>MSG_140</t>
+        </is>
+      </c>
+      <c r="B141" s="11" t="inlineStr"/>
+      <c r="C141" s="11" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning: Document Formats</t>
+        </is>
+      </c>
+      <c r="D141" s="11" t="inlineStr"/>
+      <c r="E141" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending PDF document</t>
+        </is>
+      </c>
+      <c r="F141" s="11" t="inlineStr">
+        <is>
+          <t>1. Send a .pdf file.</t>
+        </is>
+      </c>
+      <c r="G141" s="11" t="inlineStr">
+        <is>
+          <t>PDF should upload with file icon and be downloadable/viewable.</t>
+        </is>
+      </c>
+      <c r="H141" s="11" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="15.75" customHeight="1" s="7">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t>MSG_141</t>
+        </is>
+      </c>
+      <c r="B142" s="11" t="inlineStr"/>
+      <c r="C142" s="11" t="inlineStr"/>
+      <c r="D142" s="11" t="inlineStr"/>
+      <c r="E142" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending DOCX document</t>
+        </is>
+      </c>
+      <c r="F142" s="11" t="inlineStr">
+        <is>
+          <t>1. Send a .docx file.</t>
+        </is>
+      </c>
+      <c r="G142" s="11" t="inlineStr">
+        <is>
+          <t>Document should upload with Word icon and be downloadable.</t>
+        </is>
+      </c>
+      <c r="H142" s="11" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="15.75" customHeight="1" s="7">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>MSG_142</t>
+        </is>
+      </c>
+      <c r="B143" s="11" t="inlineStr"/>
+      <c r="C143" s="11" t="inlineStr"/>
+      <c r="D143" s="11" t="inlineStr"/>
+      <c r="E143" s="11" t="inlineStr">
+        <is>
+          <t>Verify sending XLSX spreadsheet</t>
+        </is>
+      </c>
+      <c r="F143" s="11" t="inlineStr">
+        <is>
+          <t>1. Send a .xlsx file.</t>
+        </is>
+      </c>
+      <c r="G143" s="11" t="inlineStr">
+        <is>
+          <t>Spreadsheet should upload with Excel icon and be downloadable.</t>
+        </is>
+      </c>
+      <c r="H143" s="11" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
     <row r="144" ht="15.75" customHeight="1" s="7"/>
     <row r="145" ht="15.75" customHeight="1" s="7"/>
     <row r="146" ht="15.75" customHeight="1" s="7"/>

--- a/Send_Message/Send_Message_Test_Cases.xlsx
+++ b/Send_Message/Send_Message_Test_Cases.xlsx
@@ -2,8 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Send Message Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Functional" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Integration" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Regression" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Security" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Edge Cases" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Boundary Values" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Equivalence Partitioning" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13,90 +23,41 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color theme="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color theme="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font/>
   </fonts>
   <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
-    <border/>
+  <borders count="2">
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
@@ -108,37 +69,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -211,20 +154,20 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="4F81BD"/>
@@ -248,19 +191,77 @@
         <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -272,159 +273,190 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H143"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:H109"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15.86" customWidth="1" style="7" min="1" max="1"/>
-    <col width="10" customWidth="1" style="7" min="2" max="2"/>
-    <col width="26" customWidth="1" style="7" min="3" max="3"/>
-    <col width="28" customWidth="1" style="7" min="4" max="4"/>
-    <col width="32" customWidth="1" style="7" min="5" max="5"/>
-    <col width="36" customWidth="1" style="7" min="6" max="6"/>
-    <col width="42" customWidth="1" style="7" min="7" max="7"/>
-    <col width="18" customWidth="1" style="7" min="8" max="8"/>
-    <col width="8.710000000000001" customWidth="1" style="7" min="9" max="26"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1" s="7">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
@@ -472,7 +504,7 @@
           <t>MSG_001</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -515,9 +547,9 @@
           <t>MSG_002</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n"/>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="9" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify message input field is clickable</t>
@@ -546,9 +578,9 @@
           <t>MSG_003</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify typing in message input field</t>
@@ -578,9 +610,9 @@
           <t>MSG_004</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n"/>
-      <c r="C5" s="10" t="n"/>
-      <c r="D5" s="10" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify multi-line message input</t>
@@ -610,7 +642,7 @@
           <t>MSG_005</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -654,9 +686,9 @@
           <t>MSG_006</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n"/>
-      <c r="C7" s="10" t="n"/>
-      <c r="D7" s="10" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Verify message with only spaces</t>
@@ -686,7 +718,7 @@
           <t>MSG_007</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -729,9 +761,9 @@
           <t>MSG_008</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="10" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Verify send button enabled when text entered</t>
@@ -761,8 +793,8 @@
           <t>MSG_009</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t>User is logged in and message typed</t>
@@ -797,9 +829,9 @@
           <t>MSG_010</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="10" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Verify send button visual feedback on click</t>
@@ -873,7 +905,7 @@
           <t>MSG_012</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -917,9 +949,9 @@
           <t>MSG_013</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Verify sending long text message</t>
@@ -949,9 +981,9 @@
           <t>MSG_014</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Verify sending message with special characters</t>
@@ -981,9 +1013,9 @@
           <t>MSG_015</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Verify sending message with emojis</t>
@@ -1013,9 +1045,9 @@
           <t>MSG_016</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Verify sending message with numbers</t>
@@ -1045,9 +1077,9 @@
           <t>MSG_017</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Verify sending message with URL</t>
@@ -1077,7 +1109,7 @@
           <t>MSG_018</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -1121,8 +1153,8 @@
           <t>MSG_019</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
@@ -1150,13 +1182,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" s="7">
+    <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>MSG_020</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1193,15 +1225,15 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1" s="7">
+    <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>MSG_021</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Verify sent message bubble color</t>
@@ -1224,15 +1256,15 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="7">
+    <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>MSG_022</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Verify sent message timestamp</t>
@@ -1255,15 +1287,15 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="7">
+    <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>MSG_023</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Verify sent message status indicator</t>
@@ -1286,13 +1318,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1" s="7">
+    <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>MSG_024</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1329,15 +1361,15 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1" s="7">
+    <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>MSG_025</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Verify received message bubble color</t>
@@ -1360,15 +1392,15 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1" s="7">
+    <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>MSG_026</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Verify received message sender info</t>
@@ -1391,15 +1423,15 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1" s="7">
+    <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>MSG_027</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Verify received message timestamp</t>
@@ -1422,13 +1454,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1" s="7">
+    <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>MSG_028</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1466,15 +1498,15 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1" s="7">
+    <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>MSG_029</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Verify Shift+Enter creates new line</t>
@@ -1498,7 +1530,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1" s="7">
+    <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t>MSG_030</t>
@@ -1541,7 +1573,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1" s="7">
+    <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>MSG_031</t>
@@ -1585,13 +1617,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1" s="7">
+    <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
           <t>MSG_032</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1628,15 +1660,15 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1" s="7">
+    <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>MSG_033</t>
         </is>
       </c>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10" t="n"/>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Verify typing indicator</t>
@@ -1659,13 +1691,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1" s="7">
+    <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
           <t>MSG_034</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1702,15 +1734,15 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="15.75" customHeight="1" s="7">
+    <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>MSG_035</t>
         </is>
       </c>
-      <c r="B36" s="9" t="n"/>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="10" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Verify scroll up to view history</t>
@@ -1733,14 +1765,14 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="15.75" customHeight="1" s="7">
+    <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
           <t>MSG_036</t>
         </is>
       </c>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="10" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
           <t>User is scrolled up in chat</t>
@@ -1768,13 +1800,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1" s="7">
+    <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>MSG_037</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1811,15 +1843,15 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1" s="7">
+    <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
           <t>MSG_038</t>
         </is>
       </c>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="10" t="n"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Verify attachment button click opens options</t>
@@ -1842,13 +1874,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1" s="7">
+    <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>MSG_039</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1885,15 +1917,15 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1" s="7">
+    <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
           <t>MSG_040</t>
         </is>
       </c>
-      <c r="B41" s="9" t="n"/>
-      <c r="C41" s="9" t="n"/>
-      <c r="D41" s="10" t="n"/>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Verify emoji button click opens picker</t>
@@ -1916,14 +1948,14 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1" s="7">
+    <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>MSG_041</t>
         </is>
       </c>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="10" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
           <t>User is logged in and emoji picker open</t>
@@ -1951,13 +1983,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1" s="7">
+    <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
           <t>MSG_042</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1995,15 +2027,15 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="15.75" customHeight="1" s="7">
+    <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>MSG_043</t>
         </is>
       </c>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Verify message input on mobile</t>
@@ -2027,13 +2059,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1" s="7">
+    <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
           <t>MSG_044</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -2071,14 +2103,14 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1" s="7">
+    <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>MSG_045</t>
         </is>
       </c>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="10" t="n"/>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network error</t>
@@ -2107,13 +2139,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1" s="7">
+    <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
           <t>MSG_046</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -2150,15 +2182,15 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="15.75" customHeight="1" s="7">
+    <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>MSG_047</t>
         </is>
       </c>
-      <c r="B48" s="9" t="n"/>
-      <c r="C48" s="9" t="n"/>
-      <c r="D48" s="10" t="n"/>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Verify attachment options menu</t>
@@ -2181,14 +2213,14 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1" s="7">
+    <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
           <t>MSG_048</t>
         </is>
       </c>
-      <c r="B49" s="9" t="n"/>
-      <c r="C49" s="9" t="n"/>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="inlineStr">
         <is>
           <t>User is logged in and attachment menu open</t>
@@ -2218,15 +2250,15 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="15.75" customHeight="1" s="7">
+    <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>MSG_049</t>
         </is>
       </c>
-      <c r="B50" s="9" t="n"/>
-      <c r="C50" s="9" t="n"/>
-      <c r="D50" s="9" t="n"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Verify sending document attachment</t>
@@ -2251,15 +2283,15 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="15.75" customHeight="1" s="7">
+    <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
           <t>MSG_050</t>
         </is>
       </c>
-      <c r="B51" s="9" t="n"/>
-      <c r="C51" s="9" t="n"/>
-      <c r="D51" s="9" t="n"/>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Verify sending video attachment</t>
@@ -2284,15 +2316,15 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1" s="7">
+    <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>MSG_051</t>
         </is>
       </c>
-      <c r="B52" s="10" t="n"/>
-      <c r="C52" s="10" t="n"/>
-      <c r="D52" s="10" t="n"/>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Verify attachment upload progress</t>
@@ -2316,13 +2348,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="15.75" customHeight="1" s="7">
+    <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
           <t>MSG_052</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -2359,15 +2391,15 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1" s="7">
+    <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
           <t>MSG_053</t>
         </is>
       </c>
-      <c r="B54" s="9" t="n"/>
-      <c r="C54" s="9" t="n"/>
-      <c r="D54" s="10" t="n"/>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Verify file size limit handling</t>
@@ -2390,14 +2422,14 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="15.75" customHeight="1" s="7">
+    <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
           <t>MSG_054</t>
         </is>
       </c>
-      <c r="B55" s="10" t="n"/>
-      <c r="C55" s="10" t="n"/>
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network error</t>
@@ -2425,13 +2457,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="15.75" customHeight="1" s="7">
+    <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>MSG_055</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -2468,15 +2500,15 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="15.75" customHeight="1" s="7">
+    <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
           <t>MSG_056</t>
         </is>
       </c>
-      <c r="B57" s="9" t="n"/>
-      <c r="C57" s="9" t="n"/>
-      <c r="D57" s="10" t="n"/>
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Verify recording starts on button press</t>
@@ -2499,14 +2531,14 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="15.75" customHeight="1" s="7">
+    <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>MSG_057</t>
         </is>
       </c>
-      <c r="B58" s="9" t="n"/>
-      <c r="C58" s="9" t="n"/>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="inlineStr">
         <is>
           <t>User is recording voice message</t>
@@ -2534,15 +2566,15 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="15.75" customHeight="1" s="7">
+    <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
           <t>MSG_058</t>
         </is>
       </c>
-      <c r="B59" s="9" t="n"/>
-      <c r="C59" s="9" t="n"/>
-      <c r="D59" s="9" t="n"/>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Verify sending voice message</t>
@@ -2566,15 +2598,15 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="15.75" customHeight="1" s="7">
+    <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>MSG_059</t>
         </is>
       </c>
-      <c r="B60" s="9" t="n"/>
-      <c r="C60" s="9" t="n"/>
-      <c r="D60" s="10" t="n"/>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Verify cancel recording</t>
@@ -2597,14 +2629,14 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="15.75" customHeight="1" s="7">
+    <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
           <t>MSG_060</t>
         </is>
       </c>
-      <c r="B61" s="10" t="n"/>
-      <c r="C61" s="10" t="n"/>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="inlineStr">
         <is>
           <t>User has received voice message</t>
@@ -2632,13 +2664,13 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="15.75" customHeight="1" s="7">
+    <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
           <t>MSG_061</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -2675,14 +2707,14 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="15.75" customHeight="1" s="7">
+    <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
           <t>MSG_062</t>
         </is>
       </c>
-      <c r="B63" s="10" t="n"/>
-      <c r="C63" s="10" t="n"/>
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
@@ -2709,13 +2741,13 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="15.75" customHeight="1" s="7">
+    <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
           <t>MSG_063</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -2752,15 +2784,15 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="15.75" customHeight="1" s="7">
+    <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
           <t>MSG_064</t>
         </is>
       </c>
-      <c r="B65" s="9" t="n"/>
-      <c r="C65" s="9" t="n"/>
-      <c r="D65" s="10" t="n"/>
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n"/>
       <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Verify emoji picker opens</t>
@@ -2783,14 +2815,14 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="15.75" customHeight="1" s="7">
+    <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>MSG_065</t>
         </is>
       </c>
-      <c r="B66" s="9" t="n"/>
-      <c r="C66" s="9" t="n"/>
+      <c r="B66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="inlineStr">
         <is>
           <t>User is logged in and emoji picker open</t>
@@ -2818,15 +2850,15 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="15.75" customHeight="1" s="7">
+    <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
           <t>MSG_066</t>
         </is>
       </c>
-      <c r="B67" s="9" t="n"/>
-      <c r="C67" s="9" t="n"/>
-      <c r="D67" s="9" t="n"/>
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Verify selecting emoji adds to input</t>
@@ -2849,15 +2881,15 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="15.75" customHeight="1" s="7">
+    <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>MSG_067</t>
         </is>
       </c>
-      <c r="B68" s="9" t="n"/>
-      <c r="C68" s="9" t="n"/>
-      <c r="D68" s="9" t="n"/>
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n"/>
       <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Verify multiple emoji selection</t>
@@ -2880,15 +2912,15 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="15.75" customHeight="1" s="7">
+    <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
           <t>MSG_068</t>
         </is>
       </c>
-      <c r="B69" s="9" t="n"/>
-      <c r="C69" s="9" t="n"/>
-      <c r="D69" s="9" t="n"/>
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Verify emoji search functionality</t>
@@ -2912,15 +2944,15 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="15.75" customHeight="1" s="7">
+    <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>MSG_069</t>
         </is>
       </c>
-      <c r="B70" s="9" t="n"/>
-      <c r="C70" s="9" t="n"/>
-      <c r="D70" s="9" t="n"/>
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Verify recent emojis section</t>
@@ -2944,15 +2976,15 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="15.75" customHeight="1" s="7">
+    <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
           <t>MSG_070</t>
         </is>
       </c>
-      <c r="B71" s="10" t="n"/>
-      <c r="C71" s="10" t="n"/>
-      <c r="D71" s="10" t="n"/>
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n"/>
       <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Verify closing emoji picker</t>
@@ -2975,13 +3007,13 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="15.75" customHeight="1" s="7">
+    <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>MSG_071</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -3018,15 +3050,15 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="15.75" customHeight="1" s="7">
+    <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
           <t>MSG_072</t>
         </is>
       </c>
-      <c r="B73" s="9" t="n"/>
-      <c r="C73" s="9" t="n"/>
-      <c r="D73" s="10" t="n"/>
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Verify sticker picker opens</t>
@@ -3049,14 +3081,14 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="15.75" customHeight="1" s="7">
+    <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>MSG_073</t>
         </is>
       </c>
-      <c r="B74" s="9" t="n"/>
-      <c r="C74" s="9" t="n"/>
+      <c r="B74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="inlineStr">
         <is>
           <t>User is logged in and sticker picker open</t>
@@ -3084,15 +3116,15 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="15.75" customHeight="1" s="7">
+    <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
           <t>MSG_074</t>
         </is>
       </c>
-      <c r="B75" s="9" t="n"/>
-      <c r="C75" s="9" t="n"/>
-      <c r="D75" s="10" t="n"/>
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n"/>
       <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Verify sending sticker</t>
@@ -3115,14 +3147,14 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="15.75" customHeight="1" s="7">
+    <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>MSG_075</t>
         </is>
       </c>
-      <c r="B76" s="9" t="n"/>
-      <c r="C76" s="9" t="n"/>
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="inlineStr">
         <is>
           <t>User has received sticker</t>
@@ -3150,14 +3182,14 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="15.75" customHeight="1" s="7">
+    <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
           <t>MSG_076</t>
         </is>
       </c>
-      <c r="B77" s="10" t="n"/>
-      <c r="C77" s="10" t="n"/>
+      <c r="B77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="inlineStr">
         <is>
           <t>User is logged in and sticker picker open</t>
@@ -3185,7 +3217,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="15.75" customHeight="1" s="7">
+    <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
           <t>MSG_077</t>
@@ -3228,13 +3260,13 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="15.75" customHeight="1" s="7">
+    <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
           <t>MSG_078</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -3271,15 +3303,15 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="15.75" customHeight="1" s="7">
+    <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
           <t>MSG_079</t>
         </is>
       </c>
-      <c r="B80" s="9" t="n"/>
-      <c r="C80" s="9" t="n"/>
-      <c r="D80" s="9" t="n"/>
+      <c r="B80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Verify selecting @all mention</t>
@@ -3302,15 +3334,15 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="15.75" customHeight="1" s="7">
+    <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
           <t>MSG_080</t>
         </is>
       </c>
-      <c r="B81" s="9" t="n"/>
-      <c r="C81" s="9" t="n"/>
-      <c r="D81" s="10" t="n"/>
+      <c r="B81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n"/>
       <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Verify sending message with @all</t>
@@ -3333,14 +3365,14 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="15.75" customHeight="1" s="7">
+    <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
           <t>MSG_081</t>
         </is>
       </c>
-      <c r="B82" s="9" t="n"/>
-      <c r="C82" s="9" t="n"/>
+      <c r="B82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="inlineStr">
         <is>
           <t>User has received @all mention</t>
@@ -3368,15 +3400,15 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="15.75" customHeight="1" s="7">
+    <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
           <t>MSG_082</t>
         </is>
       </c>
-      <c r="B83" s="10" t="n"/>
-      <c r="C83" s="10" t="n"/>
-      <c r="D83" s="10" t="n"/>
+      <c r="B83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Verify @all highlight in message</t>
@@ -3399,7 +3431,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="15.75" customHeight="1" s="7">
+    <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
           <t>MSG_083</t>
@@ -3442,13 +3474,13 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="15.75" customHeight="1" s="7">
+    <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
           <t>MSG_084</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -3485,15 +3517,15 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="15.75" customHeight="1" s="7">
+    <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
           <t>MSG_085</t>
         </is>
       </c>
-      <c r="B86" s="9" t="n"/>
-      <c r="C86" s="9" t="n"/>
-      <c r="D86" s="9" t="n"/>
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n"/>
       <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Verify filtering members by name</t>
@@ -3516,15 +3548,15 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="15.75" customHeight="1" s="7">
+    <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
           <t>MSG_086</t>
         </is>
       </c>
-      <c r="B87" s="9" t="n"/>
-      <c r="C87" s="9" t="n"/>
-      <c r="D87" s="9" t="n"/>
+      <c r="B87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Verify selecting member from suggestions</t>
@@ -3547,15 +3579,15 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="15.75" customHeight="1" s="7">
+    <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
           <t>MSG_087</t>
         </is>
       </c>
-      <c r="B88" s="9" t="n"/>
-      <c r="C88" s="9" t="n"/>
-      <c r="D88" s="10" t="n"/>
+      <c r="B88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Verify sending message with @ mention</t>
@@ -3578,14 +3610,14 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="15.75" customHeight="1" s="7">
+    <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
           <t>MSG_088</t>
         </is>
       </c>
-      <c r="B89" s="9" t="n"/>
-      <c r="C89" s="9" t="n"/>
+      <c r="B89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="inlineStr">
         <is>
           <t>User has been mentioned</t>
@@ -3613,15 +3645,15 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="15.75" customHeight="1" s="7">
+    <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
           <t>MSG_089</t>
         </is>
       </c>
-      <c r="B90" s="9" t="n"/>
-      <c r="C90" s="9" t="n"/>
-      <c r="D90" s="10" t="n"/>
+      <c r="B90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Verify @ mention highlight in message</t>
@@ -3644,14 +3676,14 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="15.75" customHeight="1" s="7">
+    <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
           <t>MSG_090</t>
         </is>
       </c>
-      <c r="B91" s="9" t="n"/>
-      <c r="C91" s="9" t="n"/>
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="inlineStr">
         <is>
           <t>User is logged in and group chat is open</t>
@@ -3679,15 +3711,15 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="15.75" customHeight="1" s="7">
+    <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
           <t>MSG_091</t>
         </is>
       </c>
-      <c r="B92" s="10" t="n"/>
-      <c r="C92" s="10" t="n"/>
-      <c r="D92" s="10" t="n"/>
+      <c r="B92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Verify @ mention with profile picture in suggestions</t>
@@ -3710,13 +3742,13 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="15.75" customHeight="1" s="7">
+    <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
           <t>MSG_092</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -3753,14 +3785,14 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="15.75" customHeight="1" s="7">
+    <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
           <t>MSG_093</t>
         </is>
       </c>
-      <c r="B94" s="10" t="n"/>
-      <c r="C94" s="10" t="n"/>
+      <c r="B94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="inlineStr">
         <is>
           <t>User is logged in and one-on-one chat is open</t>
@@ -3788,244 +3820,244 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="15.75" customHeight="1" s="7">
-      <c r="A95" s="11" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>MSG_094</t>
         </is>
       </c>
-      <c r="B95" s="11" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C95" s="11" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>Verify Custom Message</t>
         </is>
       </c>
-      <c r="D95" s="11" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E95" s="11" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Verify sending a custom message (poll)</t>
         </is>
       </c>
-      <c r="F95" s="11" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Open a conversation.
 2. Create a poll via custom message option.
 3. Send.</t>
         </is>
       </c>
-      <c r="G95" s="11" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>Poll should be sent and display in chat with options for recipients to vote.</t>
         </is>
       </c>
-      <c r="H95" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="15.75" customHeight="1" s="7">
-      <c r="A96" s="11" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>MSG_095</t>
         </is>
       </c>
-      <c r="B96" s="11" t="inlineStr"/>
-      <c r="C96" s="11" t="inlineStr"/>
-      <c r="D96" s="11" t="inlineStr"/>
-      <c r="E96" s="11" t="inlineStr">
+      <c r="B96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n"/>
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Verify sending a custom message (meeting link)</t>
         </is>
       </c>
-      <c r="F96" s="11" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. Open a conversation.
 2. Send a meeting/conference link as custom message.</t>
         </is>
       </c>
-      <c r="G96" s="11" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>Custom message with meeting link should display with appropriate formatting and join button.</t>
         </is>
       </c>
-      <c r="H96" s="11" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="15.75" customHeight="1" s="7">
-      <c r="A97" s="11" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>MSG_096</t>
         </is>
       </c>
-      <c r="B97" s="11" t="inlineStr"/>
-      <c r="C97" s="11" t="inlineStr"/>
-      <c r="D97" s="11" t="inlineStr"/>
-      <c r="E97" s="11" t="inlineStr">
+      <c r="B97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n"/>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Verify sending a custom message (collaborative document)</t>
         </is>
       </c>
-      <c r="F97" s="11" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. Open a conversation.
 2. Share a collaborative document as custom message.</t>
         </is>
       </c>
-      <c r="G97" s="11" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>Custom message should display with document preview and open/join action.</t>
         </is>
       </c>
-      <c r="H97" s="11" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="15.75" customHeight="1" s="7">
-      <c r="A98" s="11" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>MSG_097</t>
         </is>
       </c>
-      <c r="B98" s="11" t="inlineStr"/>
-      <c r="C98" s="11" t="inlineStr"/>
-      <c r="D98" s="11" t="inlineStr"/>
-      <c r="E98" s="11" t="inlineStr">
+      <c r="B98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n"/>
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Verify custom message renders correctly for receiver</t>
         </is>
       </c>
-      <c r="F98" s="11" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>1. Send a custom message from User A.
 2. Observe on User B's side.</t>
         </is>
       </c>
-      <c r="G98" s="11" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>Custom message should render correctly with all interactive elements on receiver's end.</t>
         </is>
       </c>
-      <c r="H98" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="15.75" customHeight="1" s="7">
-      <c r="A99" s="11" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>MSG_098</t>
         </is>
       </c>
-      <c r="B99" s="11" t="inlineStr"/>
-      <c r="C99" s="11" t="inlineStr"/>
-      <c r="D99" s="11" t="inlineStr"/>
-      <c r="E99" s="11" t="inlineStr">
+      <c r="B99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n"/>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Verify custom message in group chat</t>
         </is>
       </c>
-      <c r="F99" s="11" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>1. Open a group conversation.
 2. Send a custom message.</t>
         </is>
       </c>
-      <c r="G99" s="11" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>Custom message should display correctly for all group members.</t>
         </is>
       </c>
-      <c r="H99" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="15.75" customHeight="1" s="7">
-      <c r="A100" s="11" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>MSG_099</t>
         </is>
       </c>
-      <c r="B100" s="11" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C100" s="11" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>Verify Custom Message</t>
         </is>
       </c>
-      <c r="D100" s="11" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
         </is>
       </c>
-      <c r="E100" s="11" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Verify custom message fails without network</t>
         </is>
       </c>
-      <c r="F100" s="11" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Try to send a custom message.</t>
         </is>
       </c>
-      <c r="G100" s="11" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>Error message should display or message should queue with retry option.</t>
         </is>
       </c>
-      <c r="H100" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="15.75" customHeight="1" s="7">
-      <c r="A101" s="11" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>MSG_100</t>
         </is>
       </c>
-      <c r="B101" s="11" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C101" s="11" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>Verify Audio Message</t>
         </is>
       </c>
-      <c r="D101" s="11" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E101" s="11" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Verify sending an audio file attachment</t>
         </is>
       </c>
-      <c r="F101" s="11" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>1. Open a conversation.
 2. Click attach.
@@ -4033,125 +4065,125 @@
 4. Send.</t>
         </is>
       </c>
-      <c r="G101" s="11" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>Audio file should upload and display with audio player, file name, and duration.</t>
         </is>
       </c>
-      <c r="H101" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="15.75" customHeight="1" s="7">
-      <c r="A102" s="11" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>MSG_101</t>
         </is>
       </c>
-      <c r="B102" s="11" t="inlineStr"/>
-      <c r="C102" s="11" t="inlineStr"/>
-      <c r="D102" s="11" t="inlineStr"/>
-      <c r="E102" s="11" t="inlineStr">
+      <c r="B102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n"/>
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Verify audio message playback by sender</t>
         </is>
       </c>
-      <c r="F102" s="11" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>1. Send an audio message.
 2. Click play on the audio player.</t>
         </is>
       </c>
-      <c r="G102" s="11" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>Audio should play with progress bar, play/pause button, and duration indicator.</t>
         </is>
       </c>
-      <c r="H102" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="15.75" customHeight="1" s="7">
-      <c r="A103" s="11" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>MSG_102</t>
         </is>
       </c>
-      <c r="B103" s="11" t="inlineStr"/>
-      <c r="C103" s="11" t="inlineStr"/>
-      <c r="D103" s="11" t="inlineStr"/>
-      <c r="E103" s="11" t="inlineStr">
+      <c r="B103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n"/>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Verify audio message playback by receiver</t>
         </is>
       </c>
-      <c r="F103" s="11" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. Receive an audio message.
 2. Click play.</t>
         </is>
       </c>
-      <c r="G103" s="11" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>Audio should download (if needed) and play correctly with player controls.</t>
         </is>
       </c>
-      <c r="H103" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="15.75" customHeight="1" s="7">
-      <c r="A104" s="11" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>MSG_103</t>
         </is>
       </c>
-      <c r="B104" s="11" t="inlineStr"/>
-      <c r="C104" s="11" t="inlineStr"/>
-      <c r="D104" s="11" t="inlineStr"/>
-      <c r="E104" s="11" t="inlineStr">
+      <c r="B104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Verify audio message shows duration</t>
         </is>
       </c>
-      <c r="F104" s="11" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. Send/receive an audio message.
 2. Observe audio player.</t>
         </is>
       </c>
-      <c r="G104" s="11" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>Audio duration should display (e.g., '0:45', '2:30').</t>
         </is>
       </c>
-      <c r="H104" s="11" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="15.75" customHeight="1" s="7">
-      <c r="A105" s="11" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>MSG_104</t>
         </is>
       </c>
-      <c r="B105" s="11" t="inlineStr"/>
-      <c r="C105" s="11" t="inlineStr"/>
-      <c r="D105" s="11" t="inlineStr"/>
-      <c r="E105" s="11" t="inlineStr">
+      <c r="B105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n"/>
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Verify sending recorded audio message</t>
         </is>
       </c>
-      <c r="F105" s="11" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. Open a conversation.
 2. Press and hold record button.
@@ -4159,2240 +4191,1709 @@
 4. Release to send.</t>
         </is>
       </c>
-      <c r="G105" s="11" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>Recorded audio should be sent and display with audio player in chat.</t>
         </is>
       </c>
-      <c r="H105" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="15.75" customHeight="1" s="7">
-      <c r="A106" s="11" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>MSG_105</t>
         </is>
       </c>
-      <c r="B106" s="11" t="inlineStr"/>
-      <c r="C106" s="11" t="inlineStr"/>
-      <c r="D106" s="11" t="inlineStr"/>
-      <c r="E106" s="11" t="inlineStr">
+      <c r="B106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n"/>
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Verify audio message in group chat</t>
         </is>
       </c>
-      <c r="F106" s="11" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Open a group conversation.
 2. Send an audio message.</t>
         </is>
       </c>
-      <c r="G106" s="11" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>Audio message should display correctly for all group members with sender info.</t>
         </is>
       </c>
-      <c r="H106" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="15.75" customHeight="1" s="7">
-      <c r="A107" s="11" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>MSG_106</t>
         </is>
       </c>
-      <c r="B107" s="11" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C107" s="11" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>Verify Audio Message</t>
         </is>
       </c>
-      <c r="D107" s="11" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E107" s="11" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Verify large audio file exceeding size limit</t>
         </is>
       </c>
-      <c r="F107" s="11" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. Try to send an audio file exceeding the size limit.</t>
         </is>
       </c>
-      <c r="G107" s="11" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>Error message should display indicating file size limit exceeded.</t>
         </is>
       </c>
-      <c r="H107" s="11" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="15.75" customHeight="1" s="7">
-      <c r="A108" s="11" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>MSG_107</t>
         </is>
       </c>
-      <c r="B108" s="11" t="inlineStr"/>
-      <c r="C108" s="11" t="inlineStr"/>
-      <c r="D108" s="11" t="inlineStr">
+      <c r="B108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
         </is>
       </c>
-      <c r="E108" s="11" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Verify audio message fails without network</t>
         </is>
       </c>
-      <c r="F108" s="11" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Try to send an audio message.</t>
         </is>
       </c>
-      <c r="G108" s="11" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>Error message should display or upload should queue with retry option.</t>
         </is>
       </c>
-      <c r="H108" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="15.75" customHeight="1" s="7">
-      <c r="A109" s="11" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>MSG_108</t>
         </is>
       </c>
-      <c r="B109" s="11" t="inlineStr"/>
-      <c r="C109" s="11" t="inlineStr"/>
-      <c r="D109" s="11" t="inlineStr">
+      <c r="B109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E109" s="11" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Verify unsupported audio format</t>
         </is>
       </c>
-      <c r="F109" s="11" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. Try to send an unsupported audio file format.</t>
         </is>
       </c>
-      <c r="G109" s="11" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>Error message should display or file should be rejected.</t>
         </is>
       </c>
-      <c r="H109" s="11" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="15.75" customHeight="1" s="7">
-      <c r="A110" s="11" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>MSG_109</t>
         </is>
       </c>
-      <c r="B110" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C110" s="11" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Integration: Send Message with Delivery</t>
         </is>
       </c>
-      <c r="D110" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E110" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify sent message shows sent/delivered/read status progression</t>
         </is>
       </c>
-      <c r="F110" s="11" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Observe status indicators over time.</t>
         </is>
       </c>
-      <c r="G110" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Message should progress: sending → sent (single tick) → delivered (double tick) → read (blue tick).</t>
         </is>
       </c>
-      <c r="H110" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="15.75" customHeight="1" s="7">
-      <c r="A111" s="11" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>MSG_110</t>
         </is>
       </c>
-      <c r="B111" s="11" t="inlineStr"/>
-      <c r="C111" s="11" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Integration: Send Message with Push Notification</t>
         </is>
       </c>
-      <c r="D111" s="11" t="inlineStr"/>
-      <c r="E111" s="11" t="inlineStr">
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify sent message triggers push notification for receiver</t>
         </is>
       </c>
-      <c r="F111" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Send a message to User B (app in background).</t>
         </is>
       </c>
-      <c r="G111" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>User B should receive a push notification with sender name and message preview.</t>
         </is>
       </c>
-      <c r="H111" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="15.75" customHeight="1" s="7">
-      <c r="A112" s="11" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>MSG_111</t>
         </is>
       </c>
-      <c r="B112" s="11" t="inlineStr"/>
-      <c r="C112" s="11" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Integration: Send Message with Conversation List</t>
         </is>
       </c>
-      <c r="D112" s="11" t="inlineStr"/>
-      <c r="E112" s="11" t="inlineStr">
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify sent message updates conversation list for both sender and receiver</t>
         </is>
       </c>
-      <c r="F112" s="11" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Check conversation list on both devices.</t>
         </is>
       </c>
-      <c r="G112" s="11" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Both sender and receiver conversation lists should update with latest message preview.</t>
         </is>
       </c>
-      <c r="H112" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="15.75" customHeight="1" s="7">
-      <c r="A113" s="11" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFC000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>MSG_112</t>
         </is>
       </c>
-      <c r="B113" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C113" s="11" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Regression: Send Message</t>
         </is>
       </c>
-      <c r="D113" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E113" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify message sending works after failed attempt</t>
         </is>
       </c>
-      <c r="F113" s="11" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Send a message during network error (fails).
 2. Restore network.
 3. Retry sending.</t>
         </is>
       </c>
-      <c r="G113" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Message should send successfully on retry. No duplicate messages.</t>
         </is>
       </c>
-      <c r="H113" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="15.75" customHeight="1" s="7">
-      <c r="A114" s="11" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>MSG_113</t>
         </is>
       </c>
-      <c r="B114" s="11" t="inlineStr"/>
-      <c r="C114" s="11" t="inlineStr"/>
-      <c r="D114" s="11" t="inlineStr"/>
-      <c r="E114" s="11" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify message order preserved after rapid sending</t>
         </is>
       </c>
-      <c r="F114" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Send 10 messages rapidly one after another.</t>
         </is>
       </c>
-      <c r="G114" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>All 10 messages should appear in the exact order they were sent.</t>
         </is>
       </c>
-      <c r="H114" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="15.75" customHeight="1" s="7">
-      <c r="A115" s="11" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>MSG_114</t>
         </is>
       </c>
-      <c r="B115" s="11" t="inlineStr"/>
-      <c r="C115" s="11" t="inlineStr"/>
-      <c r="D115" s="11" t="inlineStr"/>
-      <c r="E115" s="11" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify media message sending after app crash recovery</t>
         </is>
       </c>
-      <c r="F115" s="11" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Start uploading a large file.
 2. Force close app.
 3. Reopen.</t>
         </is>
       </c>
-      <c r="G115" s="11" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Upload should either resume or show failed state with retry option.</t>
         </is>
       </c>
-      <c r="H115" s="11" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="15.75" customHeight="1" s="7">
-      <c r="A116" s="11" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FF0000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>MSG_115</t>
         </is>
       </c>
-      <c r="B116" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C116" s="11" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Security: Send Message</t>
         </is>
       </c>
-      <c r="D116" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E116" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify message cannot be sent to unauthorized conversation</t>
         </is>
       </c>
-      <c r="F116" s="11" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Try to send a message to a group you've been removed from.</t>
         </is>
       </c>
-      <c r="G116" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Message should fail with appropriate error. No message delivered.</t>
         </is>
       </c>
-      <c r="H116" s="11" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="15.75" customHeight="1" s="7">
-      <c r="A117" s="11" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>MSG_116</t>
         </is>
       </c>
-      <c r="B117" s="11" t="inlineStr"/>
-      <c r="C117" s="11" t="inlineStr"/>
-      <c r="D117" s="11" t="inlineStr"/>
-      <c r="E117" s="11" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify file upload scans for malware (if applicable)</t>
         </is>
       </c>
-      <c r="F117" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Upload a file flagged as potentially malicious.</t>
         </is>
       </c>
-      <c r="G117" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>File should be rejected or quarantined based on security policy.</t>
         </is>
       </c>
-      <c r="H117" s="11" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="15.75" customHeight="1" s="7">
-      <c r="A118" s="11" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>MSG_117</t>
         </is>
       </c>
-      <c r="B118" s="11" t="inlineStr"/>
-      <c r="C118" s="11" t="inlineStr"/>
-      <c r="D118" s="11" t="inlineStr"/>
-      <c r="E118" s="11" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify message encryption in transit</t>
         </is>
       </c>
-      <c r="F118" s="11" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Inspect network traffic.</t>
         </is>
       </c>
-      <c r="G118" s="11" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Message content should be encrypted (HTTPS/WSS). Not visible in plain text.</t>
         </is>
       </c>
-      <c r="H118" s="11" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="15.75" customHeight="1" s="7">
-      <c r="A119" s="11" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>MSG_118</t>
         </is>
       </c>
-      <c r="B119" s="11" t="inlineStr"/>
-      <c r="C119" s="11" t="inlineStr"/>
-      <c r="D119" s="11" t="inlineStr"/>
-      <c r="E119" s="11" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify spoofed sender ID prevention</t>
         </is>
       </c>
-      <c r="F119" s="11" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Try to send a message with a manipulated sender ID via API.</t>
         </is>
       </c>
-      <c r="G119" s="11" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Server should reject the message. Sender ID should be validated server-side.</t>
         </is>
       </c>
-      <c r="H119" s="11" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="15.75" customHeight="1" s="7">
-      <c r="A120" s="11" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>MSG_119</t>
         </is>
       </c>
-      <c r="B120" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C120" s="11" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Edge Case: Send Message</t>
         </is>
       </c>
-      <c r="D120" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E120" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify sending message while receiver is typing</t>
         </is>
       </c>
-      <c r="F120" s="11" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Both users type simultaneously.
 2. Both send at the same time.</t>
         </is>
       </c>
-      <c r="G120" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Both messages should appear in correct order. No message loss.</t>
         </is>
       </c>
-      <c r="H120" s="11" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="15.75" customHeight="1" s="7">
-      <c r="A121" s="11" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>MSG_120</t>
         </is>
       </c>
-      <c r="B121" s="11" t="inlineStr"/>
-      <c r="C121" s="11" t="inlineStr"/>
-      <c r="D121" s="11" t="inlineStr"/>
-      <c r="E121" s="11" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify sending message to a user who blocked you</t>
         </is>
       </c>
-      <c r="F121" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Send a message to a user who has blocked you.</t>
         </is>
       </c>
-      <c r="G121" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Message should fail or appear sent but not delivered. Appropriate handling per app policy.</t>
         </is>
       </c>
-      <c r="H121" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="15.75" customHeight="1" s="7">
-      <c r="A122" s="11" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>MSG_121</t>
         </is>
       </c>
-      <c r="B122" s="11" t="inlineStr"/>
-      <c r="C122" s="11" t="inlineStr"/>
-      <c r="D122" s="11" t="inlineStr"/>
-      <c r="E122" s="11" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify sending message immediately after joining a group</t>
         </is>
       </c>
-      <c r="F122" s="11" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Join a new group.
 2. Immediately send a message.</t>
         </is>
       </c>
-      <c r="G122" s="11" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Message should send successfully. Should appear for all group members.</t>
         </is>
       </c>
-      <c r="H122" s="11" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="15.75" customHeight="1" s="7">
-      <c r="A123" s="11" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>MSG_122</t>
         </is>
       </c>
-      <c r="B123" s="11" t="inlineStr"/>
-      <c r="C123" s="11" t="inlineStr"/>
-      <c r="D123" s="11" t="inlineStr"/>
-      <c r="E123" s="11" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify sending multiple media types in sequence</t>
         </is>
       </c>
-      <c r="F123" s="11" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Send an image.
 2. Immediately send a video.
 3. Send a document.</t>
         </is>
       </c>
-      <c r="G123" s="11" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>All three should upload and appear in correct order. No upload conflicts.</t>
         </is>
       </c>
-      <c r="H123" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="15.75" customHeight="1" s="7">
-      <c r="A124" s="11" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>MSG_123</t>
         </is>
       </c>
-      <c r="B124" s="11" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C124" s="11" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Edge Case: Send Message</t>
         </is>
       </c>
-      <c r="D124" s="11" t="inlineStr"/>
-      <c r="E124" s="11" t="inlineStr">
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify sending message with zero-width characters</t>
         </is>
       </c>
-      <c r="F124" s="11" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1. Send a message containing only zero-width unicode characters.</t>
         </is>
       </c>
-      <c r="G124" s="11" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Message should be blocked or displayed as empty. No invisible messages.</t>
         </is>
       </c>
-      <c r="H124" s="11" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="15.75" customHeight="1" s="7">
-      <c r="A125" s="11" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>MSG_124</t>
         </is>
       </c>
-      <c r="B125" s="11" t="inlineStr"/>
-      <c r="C125" s="11" t="inlineStr"/>
-      <c r="D125" s="11" t="inlineStr"/>
-      <c r="E125" s="11" t="inlineStr">
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Verify sending corrupted media file</t>
         </is>
       </c>
-      <c r="F125" s="11" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Rename a .txt file to .jpg.
 2. Try to send as image.</t>
         </is>
       </c>
-      <c r="G125" s="11" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>App should detect invalid file and show error. Should not crash.</t>
         </is>
       </c>
-      <c r="H125" s="11" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="15.75" customHeight="1" s="7">
-      <c r="A126" s="11" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>MSG_125</t>
         </is>
       </c>
-      <c r="B126" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C126" s="11" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Boundary: Send Message</t>
         </is>
       </c>
-      <c r="D126" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E126" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify sending text message with exactly 1 character</t>
         </is>
       </c>
-      <c r="F126" s="11" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Send 'a'.</t>
         </is>
       </c>
-      <c r="G126" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Single character message should send and display correctly.</t>
         </is>
       </c>
-      <c r="H126" s="11" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="15.75" customHeight="1" s="7">
-      <c r="A127" s="11" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>MSG_126</t>
         </is>
       </c>
-      <c r="B127" s="11" t="inlineStr"/>
-      <c r="C127" s="11" t="inlineStr"/>
-      <c r="D127" s="11" t="inlineStr"/>
-      <c r="E127" s="11" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify sending text at max character limit</t>
         </is>
       </c>
-      <c r="F127" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Send a message at exactly the maximum character limit.</t>
         </is>
       </c>
-      <c r="G127" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Message should send successfully.</t>
         </is>
       </c>
-      <c r="H127" s="11" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="15.75" customHeight="1" s="7">
-      <c r="A128" s="11" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>MSG_127</t>
         </is>
       </c>
-      <c r="B128" s="11" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C128" s="11" t="inlineStr"/>
-      <c r="D128" s="11" t="inlineStr"/>
-      <c r="E128" s="11" t="inlineStr">
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify sending text exceeding max character limit</t>
         </is>
       </c>
-      <c r="F128" s="11" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Try to send a message exceeding the max limit.</t>
         </is>
       </c>
-      <c r="G128" s="11" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Should be blocked at input or rejected by server with error.</t>
         </is>
       </c>
-      <c r="H128" s="11" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="15.75" customHeight="1" s="7">
-      <c r="A129" s="11" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>MSG_128</t>
         </is>
       </c>
-      <c r="B129" s="11" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C129" s="11" t="inlineStr"/>
-      <c r="D129" s="11" t="inlineStr"/>
-      <c r="E129" s="11" t="inlineStr">
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify sending media at minimum file size (1 byte)</t>
         </is>
       </c>
-      <c r="F129" s="11" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Send a 1-byte file.</t>
         </is>
       </c>
-      <c r="G129" s="11" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>File should either send or be rejected as too small. No crash.</t>
         </is>
       </c>
-      <c r="H129" s="11" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="15.75" customHeight="1" s="7">
-      <c r="A130" s="11" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>MSG_129</t>
         </is>
       </c>
-      <c r="B130" s="11" t="inlineStr"/>
-      <c r="C130" s="11" t="inlineStr"/>
-      <c r="D130" s="11" t="inlineStr"/>
-      <c r="E130" s="11" t="inlineStr">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify sending media at exactly max file size</t>
         </is>
       </c>
-      <c r="F130" s="11" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1. Send a file at exactly the maximum allowed size.</t>
         </is>
       </c>
-      <c r="G130" s="11" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>File should upload and send successfully.</t>
         </is>
       </c>
-      <c r="H130" s="11" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="15.75" customHeight="1" s="7">
-      <c r="A131" s="11" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0000B0F0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>MSG_130</t>
         </is>
       </c>
-      <c r="B131" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C131" s="11" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Message Destinations</t>
         </is>
       </c>
-      <c r="D131" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E131" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify sending message in one-on-one chat</t>
         </is>
       </c>
-      <c r="F131" s="11" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Open a one-on-one conversation.
 2. Send a text message.</t>
         </is>
       </c>
-      <c r="G131" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Message should deliver to the single recipient.</t>
         </is>
       </c>
-      <c r="H131" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="15.75" customHeight="1" s="7">
-      <c r="A132" s="11" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>MSG_131</t>
         </is>
       </c>
-      <c r="B132" s="11" t="inlineStr"/>
-      <c r="C132" s="11" t="inlineStr"/>
-      <c r="D132" s="11" t="inlineStr"/>
-      <c r="E132" s="11" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify sending message in small group (2-10 members)</t>
         </is>
       </c>
-      <c r="F132" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Open a group with 5 members.
 2. Send a message.</t>
         </is>
       </c>
-      <c r="G132" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Message should deliver to all group members.</t>
         </is>
       </c>
-      <c r="H132" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="15.75" customHeight="1" s="7">
-      <c r="A133" s="11" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>MSG_132</t>
         </is>
       </c>
-      <c r="B133" s="11" t="inlineStr"/>
-      <c r="C133" s="11" t="inlineStr"/>
-      <c r="D133" s="11" t="inlineStr"/>
-      <c r="E133" s="11" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify sending message in large group (100+ members)</t>
         </is>
       </c>
-      <c r="F133" s="11" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Open a group with 100+ members.
 2. Send a message.</t>
         </is>
       </c>
-      <c r="G133" s="11" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Message should deliver to all members. May have slight delay but should complete.</t>
         </is>
       </c>
-      <c r="H133" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="15.75" customHeight="1" s="7">
-      <c r="A134" s="11" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>MSG_133</t>
         </is>
       </c>
-      <c r="B134" s="11" t="inlineStr"/>
-      <c r="C134" s="11" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Image Formats</t>
         </is>
       </c>
-      <c r="D134" s="11" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E134" s="11" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify sending JPEG image</t>
         </is>
       </c>
-      <c r="F134" s="11" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Send a .jpg image.</t>
         </is>
       </c>
-      <c r="G134" s="11" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Image should upload and display correctly.</t>
         </is>
       </c>
-      <c r="H134" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="15.75" customHeight="1" s="7">
-      <c r="A135" s="11" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>MSG_134</t>
         </is>
       </c>
-      <c r="B135" s="11" t="inlineStr"/>
-      <c r="C135" s="11" t="inlineStr"/>
-      <c r="D135" s="11" t="inlineStr"/>
-      <c r="E135" s="11" t="inlineStr">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify sending PNG image</t>
         </is>
       </c>
-      <c r="F135" s="11" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1. Send a .png image.</t>
         </is>
       </c>
-      <c r="G135" s="11" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Image should upload and display correctly with transparency if applicable.</t>
         </is>
       </c>
-      <c r="H135" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="15.75" customHeight="1" s="7">
-      <c r="A136" s="11" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>MSG_135</t>
         </is>
       </c>
-      <c r="B136" s="11" t="inlineStr"/>
-      <c r="C136" s="11" t="inlineStr"/>
-      <c r="D136" s="11" t="inlineStr"/>
-      <c r="E136" s="11" t="inlineStr">
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Verify sending GIF image</t>
         </is>
       </c>
-      <c r="F136" s="11" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Send a .gif image.</t>
         </is>
       </c>
-      <c r="G136" s="11" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>GIF should upload and animate in chat.</t>
         </is>
       </c>
-      <c r="H136" s="11" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="15.75" customHeight="1" s="7">
-      <c r="A137" s="11" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>MSG_136</t>
         </is>
       </c>
-      <c r="B137" s="11" t="inlineStr"/>
-      <c r="C137" s="11" t="inlineStr"/>
-      <c r="D137" s="11" t="inlineStr"/>
-      <c r="E137" s="11" t="inlineStr">
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Verify sending WebP image</t>
         </is>
       </c>
-      <c r="F137" s="11" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1. Send a .webp image.</t>
         </is>
       </c>
-      <c r="G137" s="11" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Image should upload and display correctly.</t>
         </is>
       </c>
-      <c r="H137" s="11" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="15.75" customHeight="1" s="7">
-      <c r="A138" s="11" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>MSG_137</t>
         </is>
       </c>
-      <c r="B138" s="11" t="inlineStr"/>
-      <c r="C138" s="11" t="inlineStr"/>
-      <c r="D138" s="11" t="inlineStr"/>
-      <c r="E138" s="11" t="inlineStr">
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Verify sending SVG image</t>
         </is>
       </c>
-      <c r="F138" s="11" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1. Send a .svg file.</t>
         </is>
       </c>
-      <c r="G138" s="11" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Should either render or be treated as document. No XSS via SVG.</t>
         </is>
       </c>
-      <c r="H138" s="11" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="15.75" customHeight="1" s="7">
-      <c r="A139" s="11" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>MSG_138</t>
         </is>
       </c>
-      <c r="B139" s="11" t="inlineStr"/>
-      <c r="C139" s="11" t="inlineStr">
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Video Formats</t>
         </is>
       </c>
-      <c r="D139" s="11" t="inlineStr"/>
-      <c r="E139" s="11" t="inlineStr">
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Verify sending MP4 video</t>
         </is>
       </c>
-      <c r="F139" s="11" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1. Send a .mp4 video.</t>
         </is>
       </c>
-      <c r="G139" s="11" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Video should upload with thumbnail and be playable.</t>
         </is>
       </c>
-      <c r="H139" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="15.75" customHeight="1" s="7">
-      <c r="A140" s="11" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>MSG_139</t>
         </is>
       </c>
-      <c r="B140" s="11" t="inlineStr"/>
-      <c r="C140" s="11" t="inlineStr"/>
-      <c r="D140" s="11" t="inlineStr"/>
-      <c r="E140" s="11" t="inlineStr">
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Verify sending MOV video</t>
         </is>
       </c>
-      <c r="F140" s="11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>1. Send a .mov video.</t>
         </is>
       </c>
-      <c r="G140" s="11" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Video should upload and be playable.</t>
         </is>
       </c>
-      <c r="H140" s="11" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="15.75" customHeight="1" s="7">
-      <c r="A141" s="11" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>MSG_140</t>
         </is>
       </c>
-      <c r="B141" s="11" t="inlineStr"/>
-      <c r="C141" s="11" t="inlineStr">
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Document Formats</t>
         </is>
       </c>
-      <c r="D141" s="11" t="inlineStr"/>
-      <c r="E141" s="11" t="inlineStr">
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Verify sending PDF document</t>
         </is>
       </c>
-      <c r="F141" s="11" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1. Send a .pdf file.</t>
         </is>
       </c>
-      <c r="G141" s="11" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>PDF should upload with file icon and be downloadable/viewable.</t>
         </is>
       </c>
-      <c r="H141" s="11" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="15.75" customHeight="1" s="7">
-      <c r="A142" s="11" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>MSG_141</t>
         </is>
       </c>
-      <c r="B142" s="11" t="inlineStr"/>
-      <c r="C142" s="11" t="inlineStr"/>
-      <c r="D142" s="11" t="inlineStr"/>
-      <c r="E142" s="11" t="inlineStr">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Verify sending DOCX document</t>
         </is>
       </c>
-      <c r="F142" s="11" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1. Send a .docx file.</t>
         </is>
       </c>
-      <c r="G142" s="11" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Document should upload with Word icon and be downloadable.</t>
         </is>
       </c>
-      <c r="H142" s="11" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="15.75" customHeight="1" s="7">
-      <c r="A143" s="11" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>MSG_142</t>
         </is>
       </c>
-      <c r="B143" s="11" t="inlineStr"/>
-      <c r="C143" s="11" t="inlineStr"/>
-      <c r="D143" s="11" t="inlineStr"/>
-      <c r="E143" s="11" t="inlineStr">
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Verify sending XLSX spreadsheet</t>
         </is>
       </c>
-      <c r="F143" s="11" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Send a .xlsx file.</t>
         </is>
       </c>
-      <c r="G143" s="11" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Spreadsheet should upload with Excel icon and be downloadable.</t>
         </is>
       </c>
-      <c r="H143" s="11" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="15.75" customHeight="1" s="7"/>
-    <row r="145" ht="15.75" customHeight="1" s="7"/>
-    <row r="146" ht="15.75" customHeight="1" s="7"/>
-    <row r="147" ht="15.75" customHeight="1" s="7"/>
-    <row r="148" ht="15.75" customHeight="1" s="7"/>
-    <row r="149" ht="15.75" customHeight="1" s="7"/>
-    <row r="150" ht="15.75" customHeight="1" s="7"/>
-    <row r="151" ht="15.75" customHeight="1" s="7"/>
-    <row r="152" ht="15.75" customHeight="1" s="7"/>
-    <row r="153" ht="15.75" customHeight="1" s="7"/>
-    <row r="154" ht="15.75" customHeight="1" s="7"/>
-    <row r="155" ht="15.75" customHeight="1" s="7"/>
-    <row r="156" ht="15.75" customHeight="1" s="7"/>
-    <row r="157" ht="15.75" customHeight="1" s="7"/>
-    <row r="158" ht="15.75" customHeight="1" s="7"/>
-    <row r="159" ht="15.75" customHeight="1" s="7"/>
-    <row r="160" ht="15.75" customHeight="1" s="7"/>
-    <row r="161" ht="15.75" customHeight="1" s="7"/>
-    <row r="162" ht="15.75" customHeight="1" s="7"/>
-    <row r="163" ht="15.75" customHeight="1" s="7"/>
-    <row r="164" ht="15.75" customHeight="1" s="7"/>
-    <row r="165" ht="15.75" customHeight="1" s="7"/>
-    <row r="166" ht="15.75" customHeight="1" s="7"/>
-    <row r="167" ht="15.75" customHeight="1" s="7"/>
-    <row r="168" ht="15.75" customHeight="1" s="7"/>
-    <row r="169" ht="15.75" customHeight="1" s="7"/>
-    <row r="170" ht="15.75" customHeight="1" s="7"/>
-    <row r="171" ht="15.75" customHeight="1" s="7"/>
-    <row r="172" ht="15.75" customHeight="1" s="7"/>
-    <row r="173" ht="15.75" customHeight="1" s="7"/>
-    <row r="174" ht="15.75" customHeight="1" s="7"/>
-    <row r="175" ht="15.75" customHeight="1" s="7"/>
-    <row r="176" ht="15.75" customHeight="1" s="7"/>
-    <row r="177" ht="15.75" customHeight="1" s="7"/>
-    <row r="178" ht="15.75" customHeight="1" s="7"/>
-    <row r="179" ht="15.75" customHeight="1" s="7"/>
-    <row r="180" ht="15.75" customHeight="1" s="7"/>
-    <row r="181" ht="15.75" customHeight="1" s="7"/>
-    <row r="182" ht="15.75" customHeight="1" s="7"/>
-    <row r="183" ht="15.75" customHeight="1" s="7"/>
-    <row r="184" ht="15.75" customHeight="1" s="7"/>
-    <row r="185" ht="15.75" customHeight="1" s="7"/>
-    <row r="186" ht="15.75" customHeight="1" s="7"/>
-    <row r="187" ht="15.75" customHeight="1" s="7"/>
-    <row r="188" ht="15.75" customHeight="1" s="7"/>
-    <row r="189" ht="15.75" customHeight="1" s="7"/>
-    <row r="190" ht="15.75" customHeight="1" s="7"/>
-    <row r="191" ht="15.75" customHeight="1" s="7"/>
-    <row r="192" ht="15.75" customHeight="1" s="7"/>
-    <row r="193" ht="15.75" customHeight="1" s="7"/>
-    <row r="194" ht="15.75" customHeight="1" s="7"/>
-    <row r="195" ht="15.75" customHeight="1" s="7"/>
-    <row r="196" ht="15.75" customHeight="1" s="7"/>
-    <row r="197" ht="15.75" customHeight="1" s="7"/>
-    <row r="198" ht="15.75" customHeight="1" s="7"/>
-    <row r="199" ht="15.75" customHeight="1" s="7"/>
-    <row r="200" ht="15.75" customHeight="1" s="7"/>
-    <row r="201" ht="15.75" customHeight="1" s="7"/>
-    <row r="202" ht="15.75" customHeight="1" s="7"/>
-    <row r="203" ht="15.75" customHeight="1" s="7"/>
-    <row r="204" ht="15.75" customHeight="1" s="7"/>
-    <row r="205" ht="15.75" customHeight="1" s="7"/>
-    <row r="206" ht="15.75" customHeight="1" s="7"/>
-    <row r="207" ht="15.75" customHeight="1" s="7"/>
-    <row r="208" ht="15.75" customHeight="1" s="7"/>
-    <row r="209" ht="15.75" customHeight="1" s="7"/>
-    <row r="210" ht="15.75" customHeight="1" s="7"/>
-    <row r="211" ht="15.75" customHeight="1" s="7"/>
-    <row r="212" ht="15.75" customHeight="1" s="7"/>
-    <row r="213" ht="15.75" customHeight="1" s="7"/>
-    <row r="214" ht="15.75" customHeight="1" s="7"/>
-    <row r="215" ht="15.75" customHeight="1" s="7"/>
-    <row r="216" ht="15.75" customHeight="1" s="7"/>
-    <row r="217" ht="15.75" customHeight="1" s="7"/>
-    <row r="218" ht="15.75" customHeight="1" s="7"/>
-    <row r="219" ht="15.75" customHeight="1" s="7"/>
-    <row r="220" ht="15.75" customHeight="1" s="7"/>
-    <row r="221" ht="15.75" customHeight="1" s="7"/>
-    <row r="222" ht="15.75" customHeight="1" s="7"/>
-    <row r="223" ht="15.75" customHeight="1" s="7"/>
-    <row r="224" ht="15.75" customHeight="1" s="7"/>
-    <row r="225" ht="15.75" customHeight="1" s="7"/>
-    <row r="226" ht="15.75" customHeight="1" s="7"/>
-    <row r="227" ht="15.75" customHeight="1" s="7"/>
-    <row r="228" ht="15.75" customHeight="1" s="7"/>
-    <row r="229" ht="15.75" customHeight="1" s="7"/>
-    <row r="230" ht="15.75" customHeight="1" s="7"/>
-    <row r="231" ht="15.75" customHeight="1" s="7"/>
-    <row r="232" ht="15.75" customHeight="1" s="7"/>
-    <row r="233" ht="15.75" customHeight="1" s="7"/>
-    <row r="234" ht="15.75" customHeight="1" s="7"/>
-    <row r="235" ht="15.75" customHeight="1" s="7"/>
-    <row r="236" ht="15.75" customHeight="1" s="7"/>
-    <row r="237" ht="15.75" customHeight="1" s="7"/>
-    <row r="238" ht="15.75" customHeight="1" s="7"/>
-    <row r="239" ht="15.75" customHeight="1" s="7"/>
-    <row r="240" ht="15.75" customHeight="1" s="7"/>
-    <row r="241" ht="15.75" customHeight="1" s="7"/>
-    <row r="242" ht="15.75" customHeight="1" s="7"/>
-    <row r="243" ht="15.75" customHeight="1" s="7"/>
-    <row r="244" ht="15.75" customHeight="1" s="7"/>
-    <row r="245" ht="15.75" customHeight="1" s="7"/>
-    <row r="246" ht="15.75" customHeight="1" s="7"/>
-    <row r="247" ht="15.75" customHeight="1" s="7"/>
-    <row r="248" ht="15.75" customHeight="1" s="7"/>
-    <row r="249" ht="15.75" customHeight="1" s="7"/>
-    <row r="250" ht="15.75" customHeight="1" s="7"/>
-    <row r="251" ht="15.75" customHeight="1" s="7"/>
-    <row r="252" ht="15.75" customHeight="1" s="7"/>
-    <row r="253" ht="15.75" customHeight="1" s="7"/>
-    <row r="254" ht="15.75" customHeight="1" s="7"/>
-    <row r="255" ht="15.75" customHeight="1" s="7"/>
-    <row r="256" ht="15.75" customHeight="1" s="7"/>
-    <row r="257" ht="15.75" customHeight="1" s="7"/>
-    <row r="258" ht="15.75" customHeight="1" s="7"/>
-    <row r="259" ht="15.75" customHeight="1" s="7"/>
-    <row r="260" ht="15.75" customHeight="1" s="7"/>
-    <row r="261" ht="15.75" customHeight="1" s="7"/>
-    <row r="262" ht="15.75" customHeight="1" s="7"/>
-    <row r="263" ht="15.75" customHeight="1" s="7"/>
-    <row r="264" ht="15.75" customHeight="1" s="7"/>
-    <row r="265" ht="15.75" customHeight="1" s="7"/>
-    <row r="266" ht="15.75" customHeight="1" s="7"/>
-    <row r="267" ht="15.75" customHeight="1" s="7"/>
-    <row r="268" ht="15.75" customHeight="1" s="7"/>
-    <row r="269" ht="15.75" customHeight="1" s="7"/>
-    <row r="270" ht="15.75" customHeight="1" s="7"/>
-    <row r="271" ht="15.75" customHeight="1" s="7"/>
-    <row r="272" ht="15.75" customHeight="1" s="7"/>
-    <row r="273" ht="15.75" customHeight="1" s="7"/>
-    <row r="274" ht="15.75" customHeight="1" s="7"/>
-    <row r="275" ht="15.75" customHeight="1" s="7"/>
-    <row r="276" ht="15.75" customHeight="1" s="7"/>
-    <row r="277" ht="15.75" customHeight="1" s="7"/>
-    <row r="278" ht="15.75" customHeight="1" s="7"/>
-    <row r="279" ht="15.75" customHeight="1" s="7"/>
-    <row r="280" ht="15.75" customHeight="1" s="7"/>
-    <row r="281" ht="15.75" customHeight="1" s="7"/>
-    <row r="282" ht="15.75" customHeight="1" s="7"/>
-    <row r="283" ht="15.75" customHeight="1" s="7"/>
-    <row r="284" ht="15.75" customHeight="1" s="7"/>
-    <row r="285" ht="15.75" customHeight="1" s="7"/>
-    <row r="286" ht="15.75" customHeight="1" s="7"/>
-    <row r="287" ht="15.75" customHeight="1" s="7"/>
-    <row r="288" ht="15.75" customHeight="1" s="7"/>
-    <row r="289" ht="15.75" customHeight="1" s="7"/>
-    <row r="290" ht="15.75" customHeight="1" s="7"/>
-    <row r="291" ht="15.75" customHeight="1" s="7"/>
-    <row r="292" ht="15.75" customHeight="1" s="7"/>
-    <row r="293" ht="15.75" customHeight="1" s="7"/>
-    <row r="294" ht="15.75" customHeight="1" s="7"/>
-    <row r="295" ht="15.75" customHeight="1" s="7"/>
-    <row r="296" ht="15.75" customHeight="1" s="7"/>
-    <row r="297" ht="15.75" customHeight="1" s="7"/>
-    <row r="298" ht="15.75" customHeight="1" s="7"/>
-    <row r="299" ht="15.75" customHeight="1" s="7"/>
-    <row r="300" ht="15.75" customHeight="1" s="7"/>
-    <row r="301" ht="15.75" customHeight="1" s="7"/>
-    <row r="302" ht="15.75" customHeight="1" s="7"/>
-    <row r="303" ht="15.75" customHeight="1" s="7"/>
-    <row r="304" ht="15.75" customHeight="1" s="7"/>
-    <row r="305" ht="15.75" customHeight="1" s="7"/>
-    <row r="306" ht="15.75" customHeight="1" s="7"/>
-    <row r="307" ht="15.75" customHeight="1" s="7"/>
-    <row r="308" ht="15.75" customHeight="1" s="7"/>
-    <row r="309" ht="15.75" customHeight="1" s="7"/>
-    <row r="310" ht="15.75" customHeight="1" s="7"/>
-    <row r="311" ht="15.75" customHeight="1" s="7"/>
-    <row r="312" ht="15.75" customHeight="1" s="7"/>
-    <row r="313" ht="15.75" customHeight="1" s="7"/>
-    <row r="314" ht="15.75" customHeight="1" s="7"/>
-    <row r="315" ht="15.75" customHeight="1" s="7"/>
-    <row r="316" ht="15.75" customHeight="1" s="7"/>
-    <row r="317" ht="15.75" customHeight="1" s="7"/>
-    <row r="318" ht="15.75" customHeight="1" s="7"/>
-    <row r="319" ht="15.75" customHeight="1" s="7"/>
-    <row r="320" ht="15.75" customHeight="1" s="7"/>
-    <row r="321" ht="15.75" customHeight="1" s="7"/>
-    <row r="322" ht="15.75" customHeight="1" s="7"/>
-    <row r="323" ht="15.75" customHeight="1" s="7"/>
-    <row r="324" ht="15.75" customHeight="1" s="7"/>
-    <row r="325" ht="15.75" customHeight="1" s="7"/>
-    <row r="326" ht="15.75" customHeight="1" s="7"/>
-    <row r="327" ht="15.75" customHeight="1" s="7"/>
-    <row r="328" ht="15.75" customHeight="1" s="7"/>
-    <row r="329" ht="15.75" customHeight="1" s="7"/>
-    <row r="330" ht="15.75" customHeight="1" s="7"/>
-    <row r="331" ht="15.75" customHeight="1" s="7"/>
-    <row r="332" ht="15.75" customHeight="1" s="7"/>
-    <row r="333" ht="15.75" customHeight="1" s="7"/>
-    <row r="334" ht="15.75" customHeight="1" s="7"/>
-    <row r="335" ht="15.75" customHeight="1" s="7"/>
-    <row r="336" ht="15.75" customHeight="1" s="7"/>
-    <row r="337" ht="15.75" customHeight="1" s="7"/>
-    <row r="338" ht="15.75" customHeight="1" s="7"/>
-    <row r="339" ht="15.75" customHeight="1" s="7"/>
-    <row r="340" ht="15.75" customHeight="1" s="7"/>
-    <row r="341" ht="15.75" customHeight="1" s="7"/>
-    <row r="342" ht="15.75" customHeight="1" s="7"/>
-    <row r="343" ht="15.75" customHeight="1" s="7"/>
-    <row r="344" ht="15.75" customHeight="1" s="7"/>
-    <row r="345" ht="15.75" customHeight="1" s="7"/>
-    <row r="346" ht="15.75" customHeight="1" s="7"/>
-    <row r="347" ht="15.75" customHeight="1" s="7"/>
-    <row r="348" ht="15.75" customHeight="1" s="7"/>
-    <row r="349" ht="15.75" customHeight="1" s="7"/>
-    <row r="350" ht="15.75" customHeight="1" s="7"/>
-    <row r="351" ht="15.75" customHeight="1" s="7"/>
-    <row r="352" ht="15.75" customHeight="1" s="7"/>
-    <row r="353" ht="15.75" customHeight="1" s="7"/>
-    <row r="354" ht="15.75" customHeight="1" s="7"/>
-    <row r="355" ht="15.75" customHeight="1" s="7"/>
-    <row r="356" ht="15.75" customHeight="1" s="7"/>
-    <row r="357" ht="15.75" customHeight="1" s="7"/>
-    <row r="358" ht="15.75" customHeight="1" s="7"/>
-    <row r="359" ht="15.75" customHeight="1" s="7"/>
-    <row r="360" ht="15.75" customHeight="1" s="7"/>
-    <row r="361" ht="15.75" customHeight="1" s="7"/>
-    <row r="362" ht="15.75" customHeight="1" s="7"/>
-    <row r="363" ht="15.75" customHeight="1" s="7"/>
-    <row r="364" ht="15.75" customHeight="1" s="7"/>
-    <row r="365" ht="15.75" customHeight="1" s="7"/>
-    <row r="366" ht="15.75" customHeight="1" s="7"/>
-    <row r="367" ht="15.75" customHeight="1" s="7"/>
-    <row r="368" ht="15.75" customHeight="1" s="7"/>
-    <row r="369" ht="15.75" customHeight="1" s="7"/>
-    <row r="370" ht="15.75" customHeight="1" s="7"/>
-    <row r="371" ht="15.75" customHeight="1" s="7"/>
-    <row r="372" ht="15.75" customHeight="1" s="7"/>
-    <row r="373" ht="15.75" customHeight="1" s="7"/>
-    <row r="374" ht="15.75" customHeight="1" s="7"/>
-    <row r="375" ht="15.75" customHeight="1" s="7"/>
-    <row r="376" ht="15.75" customHeight="1" s="7"/>
-    <row r="377" ht="15.75" customHeight="1" s="7"/>
-    <row r="378" ht="15.75" customHeight="1" s="7"/>
-    <row r="379" ht="15.75" customHeight="1" s="7"/>
-    <row r="380" ht="15.75" customHeight="1" s="7"/>
-    <row r="381" ht="15.75" customHeight="1" s="7"/>
-    <row r="382" ht="15.75" customHeight="1" s="7"/>
-    <row r="383" ht="15.75" customHeight="1" s="7"/>
-    <row r="384" ht="15.75" customHeight="1" s="7"/>
-    <row r="385" ht="15.75" customHeight="1" s="7"/>
-    <row r="386" ht="15.75" customHeight="1" s="7"/>
-    <row r="387" ht="15.75" customHeight="1" s="7"/>
-    <row r="388" ht="15.75" customHeight="1" s="7"/>
-    <row r="389" ht="15.75" customHeight="1" s="7"/>
-    <row r="390" ht="15.75" customHeight="1" s="7"/>
-    <row r="391" ht="15.75" customHeight="1" s="7"/>
-    <row r="392" ht="15.75" customHeight="1" s="7"/>
-    <row r="393" ht="15.75" customHeight="1" s="7"/>
-    <row r="394" ht="15.75" customHeight="1" s="7"/>
-    <row r="395" ht="15.75" customHeight="1" s="7"/>
-    <row r="396" ht="15.75" customHeight="1" s="7"/>
-    <row r="397" ht="15.75" customHeight="1" s="7"/>
-    <row r="398" ht="15.75" customHeight="1" s="7"/>
-    <row r="399" ht="15.75" customHeight="1" s="7"/>
-    <row r="400" ht="15.75" customHeight="1" s="7"/>
-    <row r="401" ht="15.75" customHeight="1" s="7"/>
-    <row r="402" ht="15.75" customHeight="1" s="7"/>
-    <row r="403" ht="15.75" customHeight="1" s="7"/>
-    <row r="404" ht="15.75" customHeight="1" s="7"/>
-    <row r="405" ht="15.75" customHeight="1" s="7"/>
-    <row r="406" ht="15.75" customHeight="1" s="7"/>
-    <row r="407" ht="15.75" customHeight="1" s="7"/>
-    <row r="408" ht="15.75" customHeight="1" s="7"/>
-    <row r="409" ht="15.75" customHeight="1" s="7"/>
-    <row r="410" ht="15.75" customHeight="1" s="7"/>
-    <row r="411" ht="15.75" customHeight="1" s="7"/>
-    <row r="412" ht="15.75" customHeight="1" s="7"/>
-    <row r="413" ht="15.75" customHeight="1" s="7"/>
-    <row r="414" ht="15.75" customHeight="1" s="7"/>
-    <row r="415" ht="15.75" customHeight="1" s="7"/>
-    <row r="416" ht="15.75" customHeight="1" s="7"/>
-    <row r="417" ht="15.75" customHeight="1" s="7"/>
-    <row r="418" ht="15.75" customHeight="1" s="7"/>
-    <row r="419" ht="15.75" customHeight="1" s="7"/>
-    <row r="420" ht="15.75" customHeight="1" s="7"/>
-    <row r="421" ht="15.75" customHeight="1" s="7"/>
-    <row r="422" ht="15.75" customHeight="1" s="7"/>
-    <row r="423" ht="15.75" customHeight="1" s="7"/>
-    <row r="424" ht="15.75" customHeight="1" s="7"/>
-    <row r="425" ht="15.75" customHeight="1" s="7"/>
-    <row r="426" ht="15.75" customHeight="1" s="7"/>
-    <row r="427" ht="15.75" customHeight="1" s="7"/>
-    <row r="428" ht="15.75" customHeight="1" s="7"/>
-    <row r="429" ht="15.75" customHeight="1" s="7"/>
-    <row r="430" ht="15.75" customHeight="1" s="7"/>
-    <row r="431" ht="15.75" customHeight="1" s="7"/>
-    <row r="432" ht="15.75" customHeight="1" s="7"/>
-    <row r="433" ht="15.75" customHeight="1" s="7"/>
-    <row r="434" ht="15.75" customHeight="1" s="7"/>
-    <row r="435" ht="15.75" customHeight="1" s="7"/>
-    <row r="436" ht="15.75" customHeight="1" s="7"/>
-    <row r="437" ht="15.75" customHeight="1" s="7"/>
-    <row r="438" ht="15.75" customHeight="1" s="7"/>
-    <row r="439" ht="15.75" customHeight="1" s="7"/>
-    <row r="440" ht="15.75" customHeight="1" s="7"/>
-    <row r="441" ht="15.75" customHeight="1" s="7"/>
-    <row r="442" ht="15.75" customHeight="1" s="7"/>
-    <row r="443" ht="15.75" customHeight="1" s="7"/>
-    <row r="444" ht="15.75" customHeight="1" s="7"/>
-    <row r="445" ht="15.75" customHeight="1" s="7"/>
-    <row r="446" ht="15.75" customHeight="1" s="7"/>
-    <row r="447" ht="15.75" customHeight="1" s="7"/>
-    <row r="448" ht="15.75" customHeight="1" s="7"/>
-    <row r="449" ht="15.75" customHeight="1" s="7"/>
-    <row r="450" ht="15.75" customHeight="1" s="7"/>
-    <row r="451" ht="15.75" customHeight="1" s="7"/>
-    <row r="452" ht="15.75" customHeight="1" s="7"/>
-    <row r="453" ht="15.75" customHeight="1" s="7"/>
-    <row r="454" ht="15.75" customHeight="1" s="7"/>
-    <row r="455" ht="15.75" customHeight="1" s="7"/>
-    <row r="456" ht="15.75" customHeight="1" s="7"/>
-    <row r="457" ht="15.75" customHeight="1" s="7"/>
-    <row r="458" ht="15.75" customHeight="1" s="7"/>
-    <row r="459" ht="15.75" customHeight="1" s="7"/>
-    <row r="460" ht="15.75" customHeight="1" s="7"/>
-    <row r="461" ht="15.75" customHeight="1" s="7"/>
-    <row r="462" ht="15.75" customHeight="1" s="7"/>
-    <row r="463" ht="15.75" customHeight="1" s="7"/>
-    <row r="464" ht="15.75" customHeight="1" s="7"/>
-    <row r="465" ht="15.75" customHeight="1" s="7"/>
-    <row r="466" ht="15.75" customHeight="1" s="7"/>
-    <row r="467" ht="15.75" customHeight="1" s="7"/>
-    <row r="468" ht="15.75" customHeight="1" s="7"/>
-    <row r="469" ht="15.75" customHeight="1" s="7"/>
-    <row r="470" ht="15.75" customHeight="1" s="7"/>
-    <row r="471" ht="15.75" customHeight="1" s="7"/>
-    <row r="472" ht="15.75" customHeight="1" s="7"/>
-    <row r="473" ht="15.75" customHeight="1" s="7"/>
-    <row r="474" ht="15.75" customHeight="1" s="7"/>
-    <row r="475" ht="15.75" customHeight="1" s="7"/>
-    <row r="476" ht="15.75" customHeight="1" s="7"/>
-    <row r="477" ht="15.75" customHeight="1" s="7"/>
-    <row r="478" ht="15.75" customHeight="1" s="7"/>
-    <row r="479" ht="15.75" customHeight="1" s="7"/>
-    <row r="480" ht="15.75" customHeight="1" s="7"/>
-    <row r="481" ht="15.75" customHeight="1" s="7"/>
-    <row r="482" ht="15.75" customHeight="1" s="7"/>
-    <row r="483" ht="15.75" customHeight="1" s="7"/>
-    <row r="484" ht="15.75" customHeight="1" s="7"/>
-    <row r="485" ht="15.75" customHeight="1" s="7"/>
-    <row r="486" ht="15.75" customHeight="1" s="7"/>
-    <row r="487" ht="15.75" customHeight="1" s="7"/>
-    <row r="488" ht="15.75" customHeight="1" s="7"/>
-    <row r="489" ht="15.75" customHeight="1" s="7"/>
-    <row r="490" ht="15.75" customHeight="1" s="7"/>
-    <row r="491" ht="15.75" customHeight="1" s="7"/>
-    <row r="492" ht="15.75" customHeight="1" s="7"/>
-    <row r="493" ht="15.75" customHeight="1" s="7"/>
-    <row r="494" ht="15.75" customHeight="1" s="7"/>
-    <row r="495" ht="15.75" customHeight="1" s="7"/>
-    <row r="496" ht="15.75" customHeight="1" s="7"/>
-    <row r="497" ht="15.75" customHeight="1" s="7"/>
-    <row r="498" ht="15.75" customHeight="1" s="7"/>
-    <row r="499" ht="15.75" customHeight="1" s="7"/>
-    <row r="500" ht="15.75" customHeight="1" s="7"/>
-    <row r="501" ht="15.75" customHeight="1" s="7"/>
-    <row r="502" ht="15.75" customHeight="1" s="7"/>
-    <row r="503" ht="15.75" customHeight="1" s="7"/>
-    <row r="504" ht="15.75" customHeight="1" s="7"/>
-    <row r="505" ht="15.75" customHeight="1" s="7"/>
-    <row r="506" ht="15.75" customHeight="1" s="7"/>
-    <row r="507" ht="15.75" customHeight="1" s="7"/>
-    <row r="508" ht="15.75" customHeight="1" s="7"/>
-    <row r="509" ht="15.75" customHeight="1" s="7"/>
-    <row r="510" ht="15.75" customHeight="1" s="7"/>
-    <row r="511" ht="15.75" customHeight="1" s="7"/>
-    <row r="512" ht="15.75" customHeight="1" s="7"/>
-    <row r="513" ht="15.75" customHeight="1" s="7"/>
-    <row r="514" ht="15.75" customHeight="1" s="7"/>
-    <row r="515" ht="15.75" customHeight="1" s="7"/>
-    <row r="516" ht="15.75" customHeight="1" s="7"/>
-    <row r="517" ht="15.75" customHeight="1" s="7"/>
-    <row r="518" ht="15.75" customHeight="1" s="7"/>
-    <row r="519" ht="15.75" customHeight="1" s="7"/>
-    <row r="520" ht="15.75" customHeight="1" s="7"/>
-    <row r="521" ht="15.75" customHeight="1" s="7"/>
-    <row r="522" ht="15.75" customHeight="1" s="7"/>
-    <row r="523" ht="15.75" customHeight="1" s="7"/>
-    <row r="524" ht="15.75" customHeight="1" s="7"/>
-    <row r="525" ht="15.75" customHeight="1" s="7"/>
-    <row r="526" ht="15.75" customHeight="1" s="7"/>
-    <row r="527" ht="15.75" customHeight="1" s="7"/>
-    <row r="528" ht="15.75" customHeight="1" s="7"/>
-    <row r="529" ht="15.75" customHeight="1" s="7"/>
-    <row r="530" ht="15.75" customHeight="1" s="7"/>
-    <row r="531" ht="15.75" customHeight="1" s="7"/>
-    <row r="532" ht="15.75" customHeight="1" s="7"/>
-    <row r="533" ht="15.75" customHeight="1" s="7"/>
-    <row r="534" ht="15.75" customHeight="1" s="7"/>
-    <row r="535" ht="15.75" customHeight="1" s="7"/>
-    <row r="536" ht="15.75" customHeight="1" s="7"/>
-    <row r="537" ht="15.75" customHeight="1" s="7"/>
-    <row r="538" ht="15.75" customHeight="1" s="7"/>
-    <row r="539" ht="15.75" customHeight="1" s="7"/>
-    <row r="540" ht="15.75" customHeight="1" s="7"/>
-    <row r="541" ht="15.75" customHeight="1" s="7"/>
-    <row r="542" ht="15.75" customHeight="1" s="7"/>
-    <row r="543" ht="15.75" customHeight="1" s="7"/>
-    <row r="544" ht="15.75" customHeight="1" s="7"/>
-    <row r="545" ht="15.75" customHeight="1" s="7"/>
-    <row r="546" ht="15.75" customHeight="1" s="7"/>
-    <row r="547" ht="15.75" customHeight="1" s="7"/>
-    <row r="548" ht="15.75" customHeight="1" s="7"/>
-    <row r="549" ht="15.75" customHeight="1" s="7"/>
-    <row r="550" ht="15.75" customHeight="1" s="7"/>
-    <row r="551" ht="15.75" customHeight="1" s="7"/>
-    <row r="552" ht="15.75" customHeight="1" s="7"/>
-    <row r="553" ht="15.75" customHeight="1" s="7"/>
-    <row r="554" ht="15.75" customHeight="1" s="7"/>
-    <row r="555" ht="15.75" customHeight="1" s="7"/>
-    <row r="556" ht="15.75" customHeight="1" s="7"/>
-    <row r="557" ht="15.75" customHeight="1" s="7"/>
-    <row r="558" ht="15.75" customHeight="1" s="7"/>
-    <row r="559" ht="15.75" customHeight="1" s="7"/>
-    <row r="560" ht="15.75" customHeight="1" s="7"/>
-    <row r="561" ht="15.75" customHeight="1" s="7"/>
-    <row r="562" ht="15.75" customHeight="1" s="7"/>
-    <row r="563" ht="15.75" customHeight="1" s="7"/>
-    <row r="564" ht="15.75" customHeight="1" s="7"/>
-    <row r="565" ht="15.75" customHeight="1" s="7"/>
-    <row r="566" ht="15.75" customHeight="1" s="7"/>
-    <row r="567" ht="15.75" customHeight="1" s="7"/>
-    <row r="568" ht="15.75" customHeight="1" s="7"/>
-    <row r="569" ht="15.75" customHeight="1" s="7"/>
-    <row r="570" ht="15.75" customHeight="1" s="7"/>
-    <row r="571" ht="15.75" customHeight="1" s="7"/>
-    <row r="572" ht="15.75" customHeight="1" s="7"/>
-    <row r="573" ht="15.75" customHeight="1" s="7"/>
-    <row r="574" ht="15.75" customHeight="1" s="7"/>
-    <row r="575" ht="15.75" customHeight="1" s="7"/>
-    <row r="576" ht="15.75" customHeight="1" s="7"/>
-    <row r="577" ht="15.75" customHeight="1" s="7"/>
-    <row r="578" ht="15.75" customHeight="1" s="7"/>
-    <row r="579" ht="15.75" customHeight="1" s="7"/>
-    <row r="580" ht="15.75" customHeight="1" s="7"/>
-    <row r="581" ht="15.75" customHeight="1" s="7"/>
-    <row r="582" ht="15.75" customHeight="1" s="7"/>
-    <row r="583" ht="15.75" customHeight="1" s="7"/>
-    <row r="584" ht="15.75" customHeight="1" s="7"/>
-    <row r="585" ht="15.75" customHeight="1" s="7"/>
-    <row r="586" ht="15.75" customHeight="1" s="7"/>
-    <row r="587" ht="15.75" customHeight="1" s="7"/>
-    <row r="588" ht="15.75" customHeight="1" s="7"/>
-    <row r="589" ht="15.75" customHeight="1" s="7"/>
-    <row r="590" ht="15.75" customHeight="1" s="7"/>
-    <row r="591" ht="15.75" customHeight="1" s="7"/>
-    <row r="592" ht="15.75" customHeight="1" s="7"/>
-    <row r="593" ht="15.75" customHeight="1" s="7"/>
-    <row r="594" ht="15.75" customHeight="1" s="7"/>
-    <row r="595" ht="15.75" customHeight="1" s="7"/>
-    <row r="596" ht="15.75" customHeight="1" s="7"/>
-    <row r="597" ht="15.75" customHeight="1" s="7"/>
-    <row r="598" ht="15.75" customHeight="1" s="7"/>
-    <row r="599" ht="15.75" customHeight="1" s="7"/>
-    <row r="600" ht="15.75" customHeight="1" s="7"/>
-    <row r="601" ht="15.75" customHeight="1" s="7"/>
-    <row r="602" ht="15.75" customHeight="1" s="7"/>
-    <row r="603" ht="15.75" customHeight="1" s="7"/>
-    <row r="604" ht="15.75" customHeight="1" s="7"/>
-    <row r="605" ht="15.75" customHeight="1" s="7"/>
-    <row r="606" ht="15.75" customHeight="1" s="7"/>
-    <row r="607" ht="15.75" customHeight="1" s="7"/>
-    <row r="608" ht="15.75" customHeight="1" s="7"/>
-    <row r="609" ht="15.75" customHeight="1" s="7"/>
-    <row r="610" ht="15.75" customHeight="1" s="7"/>
-    <row r="611" ht="15.75" customHeight="1" s="7"/>
-    <row r="612" ht="15.75" customHeight="1" s="7"/>
-    <row r="613" ht="15.75" customHeight="1" s="7"/>
-    <row r="614" ht="15.75" customHeight="1" s="7"/>
-    <row r="615" ht="15.75" customHeight="1" s="7"/>
-    <row r="616" ht="15.75" customHeight="1" s="7"/>
-    <row r="617" ht="15.75" customHeight="1" s="7"/>
-    <row r="618" ht="15.75" customHeight="1" s="7"/>
-    <row r="619" ht="15.75" customHeight="1" s="7"/>
-    <row r="620" ht="15.75" customHeight="1" s="7"/>
-    <row r="621" ht="15.75" customHeight="1" s="7"/>
-    <row r="622" ht="15.75" customHeight="1" s="7"/>
-    <row r="623" ht="15.75" customHeight="1" s="7"/>
-    <row r="624" ht="15.75" customHeight="1" s="7"/>
-    <row r="625" ht="15.75" customHeight="1" s="7"/>
-    <row r="626" ht="15.75" customHeight="1" s="7"/>
-    <row r="627" ht="15.75" customHeight="1" s="7"/>
-    <row r="628" ht="15.75" customHeight="1" s="7"/>
-    <row r="629" ht="15.75" customHeight="1" s="7"/>
-    <row r="630" ht="15.75" customHeight="1" s="7"/>
-    <row r="631" ht="15.75" customHeight="1" s="7"/>
-    <row r="632" ht="15.75" customHeight="1" s="7"/>
-    <row r="633" ht="15.75" customHeight="1" s="7"/>
-    <row r="634" ht="15.75" customHeight="1" s="7"/>
-    <row r="635" ht="15.75" customHeight="1" s="7"/>
-    <row r="636" ht="15.75" customHeight="1" s="7"/>
-    <row r="637" ht="15.75" customHeight="1" s="7"/>
-    <row r="638" ht="15.75" customHeight="1" s="7"/>
-    <row r="639" ht="15.75" customHeight="1" s="7"/>
-    <row r="640" ht="15.75" customHeight="1" s="7"/>
-    <row r="641" ht="15.75" customHeight="1" s="7"/>
-    <row r="642" ht="15.75" customHeight="1" s="7"/>
-    <row r="643" ht="15.75" customHeight="1" s="7"/>
-    <row r="644" ht="15.75" customHeight="1" s="7"/>
-    <row r="645" ht="15.75" customHeight="1" s="7"/>
-    <row r="646" ht="15.75" customHeight="1" s="7"/>
-    <row r="647" ht="15.75" customHeight="1" s="7"/>
-    <row r="648" ht="15.75" customHeight="1" s="7"/>
-    <row r="649" ht="15.75" customHeight="1" s="7"/>
-    <row r="650" ht="15.75" customHeight="1" s="7"/>
-    <row r="651" ht="15.75" customHeight="1" s="7"/>
-    <row r="652" ht="15.75" customHeight="1" s="7"/>
-    <row r="653" ht="15.75" customHeight="1" s="7"/>
-    <row r="654" ht="15.75" customHeight="1" s="7"/>
-    <row r="655" ht="15.75" customHeight="1" s="7"/>
-    <row r="656" ht="15.75" customHeight="1" s="7"/>
-    <row r="657" ht="15.75" customHeight="1" s="7"/>
-    <row r="658" ht="15.75" customHeight="1" s="7"/>
-    <row r="659" ht="15.75" customHeight="1" s="7"/>
-    <row r="660" ht="15.75" customHeight="1" s="7"/>
-    <row r="661" ht="15.75" customHeight="1" s="7"/>
-    <row r="662" ht="15.75" customHeight="1" s="7"/>
-    <row r="663" ht="15.75" customHeight="1" s="7"/>
-    <row r="664" ht="15.75" customHeight="1" s="7"/>
-    <row r="665" ht="15.75" customHeight="1" s="7"/>
-    <row r="666" ht="15.75" customHeight="1" s="7"/>
-    <row r="667" ht="15.75" customHeight="1" s="7"/>
-    <row r="668" ht="15.75" customHeight="1" s="7"/>
-    <row r="669" ht="15.75" customHeight="1" s="7"/>
-    <row r="670" ht="15.75" customHeight="1" s="7"/>
-    <row r="671" ht="15.75" customHeight="1" s="7"/>
-    <row r="672" ht="15.75" customHeight="1" s="7"/>
-    <row r="673" ht="15.75" customHeight="1" s="7"/>
-    <row r="674" ht="15.75" customHeight="1" s="7"/>
-    <row r="675" ht="15.75" customHeight="1" s="7"/>
-    <row r="676" ht="15.75" customHeight="1" s="7"/>
-    <row r="677" ht="15.75" customHeight="1" s="7"/>
-    <row r="678" ht="15.75" customHeight="1" s="7"/>
-    <row r="679" ht="15.75" customHeight="1" s="7"/>
-    <row r="680" ht="15.75" customHeight="1" s="7"/>
-    <row r="681" ht="15.75" customHeight="1" s="7"/>
-    <row r="682" ht="15.75" customHeight="1" s="7"/>
-    <row r="683" ht="15.75" customHeight="1" s="7"/>
-    <row r="684" ht="15.75" customHeight="1" s="7"/>
-    <row r="685" ht="15.75" customHeight="1" s="7"/>
-    <row r="686" ht="15.75" customHeight="1" s="7"/>
-    <row r="687" ht="15.75" customHeight="1" s="7"/>
-    <row r="688" ht="15.75" customHeight="1" s="7"/>
-    <row r="689" ht="15.75" customHeight="1" s="7"/>
-    <row r="690" ht="15.75" customHeight="1" s="7"/>
-    <row r="691" ht="15.75" customHeight="1" s="7"/>
-    <row r="692" ht="15.75" customHeight="1" s="7"/>
-    <row r="693" ht="15.75" customHeight="1" s="7"/>
-    <row r="694" ht="15.75" customHeight="1" s="7"/>
-    <row r="695" ht="15.75" customHeight="1" s="7"/>
-    <row r="696" ht="15.75" customHeight="1" s="7"/>
-    <row r="697" ht="15.75" customHeight="1" s="7"/>
-    <row r="698" ht="15.75" customHeight="1" s="7"/>
-    <row r="699" ht="15.75" customHeight="1" s="7"/>
-    <row r="700" ht="15.75" customHeight="1" s="7"/>
-    <row r="701" ht="15.75" customHeight="1" s="7"/>
-    <row r="702" ht="15.75" customHeight="1" s="7"/>
-    <row r="703" ht="15.75" customHeight="1" s="7"/>
-    <row r="704" ht="15.75" customHeight="1" s="7"/>
-    <row r="705" ht="15.75" customHeight="1" s="7"/>
-    <row r="706" ht="15.75" customHeight="1" s="7"/>
-    <row r="707" ht="15.75" customHeight="1" s="7"/>
-    <row r="708" ht="15.75" customHeight="1" s="7"/>
-    <row r="709" ht="15.75" customHeight="1" s="7"/>
-    <row r="710" ht="15.75" customHeight="1" s="7"/>
-    <row r="711" ht="15.75" customHeight="1" s="7"/>
-    <row r="712" ht="15.75" customHeight="1" s="7"/>
-    <row r="713" ht="15.75" customHeight="1" s="7"/>
-    <row r="714" ht="15.75" customHeight="1" s="7"/>
-    <row r="715" ht="15.75" customHeight="1" s="7"/>
-    <row r="716" ht="15.75" customHeight="1" s="7"/>
-    <row r="717" ht="15.75" customHeight="1" s="7"/>
-    <row r="718" ht="15.75" customHeight="1" s="7"/>
-    <row r="719" ht="15.75" customHeight="1" s="7"/>
-    <row r="720" ht="15.75" customHeight="1" s="7"/>
-    <row r="721" ht="15.75" customHeight="1" s="7"/>
-    <row r="722" ht="15.75" customHeight="1" s="7"/>
-    <row r="723" ht="15.75" customHeight="1" s="7"/>
-    <row r="724" ht="15.75" customHeight="1" s="7"/>
-    <row r="725" ht="15.75" customHeight="1" s="7"/>
-    <row r="726" ht="15.75" customHeight="1" s="7"/>
-    <row r="727" ht="15.75" customHeight="1" s="7"/>
-    <row r="728" ht="15.75" customHeight="1" s="7"/>
-    <row r="729" ht="15.75" customHeight="1" s="7"/>
-    <row r="730" ht="15.75" customHeight="1" s="7"/>
-    <row r="731" ht="15.75" customHeight="1" s="7"/>
-    <row r="732" ht="15.75" customHeight="1" s="7"/>
-    <row r="733" ht="15.75" customHeight="1" s="7"/>
-    <row r="734" ht="15.75" customHeight="1" s="7"/>
-    <row r="735" ht="15.75" customHeight="1" s="7"/>
-    <row r="736" ht="15.75" customHeight="1" s="7"/>
-    <row r="737" ht="15.75" customHeight="1" s="7"/>
-    <row r="738" ht="15.75" customHeight="1" s="7"/>
-    <row r="739" ht="15.75" customHeight="1" s="7"/>
-    <row r="740" ht="15.75" customHeight="1" s="7"/>
-    <row r="741" ht="15.75" customHeight="1" s="7"/>
-    <row r="742" ht="15.75" customHeight="1" s="7"/>
-    <row r="743" ht="15.75" customHeight="1" s="7"/>
-    <row r="744" ht="15.75" customHeight="1" s="7"/>
-    <row r="745" ht="15.75" customHeight="1" s="7"/>
-    <row r="746" ht="15.75" customHeight="1" s="7"/>
-    <row r="747" ht="15.75" customHeight="1" s="7"/>
-    <row r="748" ht="15.75" customHeight="1" s="7"/>
-    <row r="749" ht="15.75" customHeight="1" s="7"/>
-    <row r="750" ht="15.75" customHeight="1" s="7"/>
-    <row r="751" ht="15.75" customHeight="1" s="7"/>
-    <row r="752" ht="15.75" customHeight="1" s="7"/>
-    <row r="753" ht="15.75" customHeight="1" s="7"/>
-    <row r="754" ht="15.75" customHeight="1" s="7"/>
-    <row r="755" ht="15.75" customHeight="1" s="7"/>
-    <row r="756" ht="15.75" customHeight="1" s="7"/>
-    <row r="757" ht="15.75" customHeight="1" s="7"/>
-    <row r="758" ht="15.75" customHeight="1" s="7"/>
-    <row r="759" ht="15.75" customHeight="1" s="7"/>
-    <row r="760" ht="15.75" customHeight="1" s="7"/>
-    <row r="761" ht="15.75" customHeight="1" s="7"/>
-    <row r="762" ht="15.75" customHeight="1" s="7"/>
-    <row r="763" ht="15.75" customHeight="1" s="7"/>
-    <row r="764" ht="15.75" customHeight="1" s="7"/>
-    <row r="765" ht="15.75" customHeight="1" s="7"/>
-    <row r="766" ht="15.75" customHeight="1" s="7"/>
-    <row r="767" ht="15.75" customHeight="1" s="7"/>
-    <row r="768" ht="15.75" customHeight="1" s="7"/>
-    <row r="769" ht="15.75" customHeight="1" s="7"/>
-    <row r="770" ht="15.75" customHeight="1" s="7"/>
-    <row r="771" ht="15.75" customHeight="1" s="7"/>
-    <row r="772" ht="15.75" customHeight="1" s="7"/>
-    <row r="773" ht="15.75" customHeight="1" s="7"/>
-    <row r="774" ht="15.75" customHeight="1" s="7"/>
-    <row r="775" ht="15.75" customHeight="1" s="7"/>
-    <row r="776" ht="15.75" customHeight="1" s="7"/>
-    <row r="777" ht="15.75" customHeight="1" s="7"/>
-    <row r="778" ht="15.75" customHeight="1" s="7"/>
-    <row r="779" ht="15.75" customHeight="1" s="7"/>
-    <row r="780" ht="15.75" customHeight="1" s="7"/>
-    <row r="781" ht="15.75" customHeight="1" s="7"/>
-    <row r="782" ht="15.75" customHeight="1" s="7"/>
-    <row r="783" ht="15.75" customHeight="1" s="7"/>
-    <row r="784" ht="15.75" customHeight="1" s="7"/>
-    <row r="785" ht="15.75" customHeight="1" s="7"/>
-    <row r="786" ht="15.75" customHeight="1" s="7"/>
-    <row r="787" ht="15.75" customHeight="1" s="7"/>
-    <row r="788" ht="15.75" customHeight="1" s="7"/>
-    <row r="789" ht="15.75" customHeight="1" s="7"/>
-    <row r="790" ht="15.75" customHeight="1" s="7"/>
-    <row r="791" ht="15.75" customHeight="1" s="7"/>
-    <row r="792" ht="15.75" customHeight="1" s="7"/>
-    <row r="793" ht="15.75" customHeight="1" s="7"/>
-    <row r="794" ht="15.75" customHeight="1" s="7"/>
-    <row r="795" ht="15.75" customHeight="1" s="7"/>
-    <row r="796" ht="15.75" customHeight="1" s="7"/>
-    <row r="797" ht="15.75" customHeight="1" s="7"/>
-    <row r="798" ht="15.75" customHeight="1" s="7"/>
-    <row r="799" ht="15.75" customHeight="1" s="7"/>
-    <row r="800" ht="15.75" customHeight="1" s="7"/>
-    <row r="801" ht="15.75" customHeight="1" s="7"/>
-    <row r="802" ht="15.75" customHeight="1" s="7"/>
-    <row r="803" ht="15.75" customHeight="1" s="7"/>
-    <row r="804" ht="15.75" customHeight="1" s="7"/>
-    <row r="805" ht="15.75" customHeight="1" s="7"/>
-    <row r="806" ht="15.75" customHeight="1" s="7"/>
-    <row r="807" ht="15.75" customHeight="1" s="7"/>
-    <row r="808" ht="15.75" customHeight="1" s="7"/>
-    <row r="809" ht="15.75" customHeight="1" s="7"/>
-    <row r="810" ht="15.75" customHeight="1" s="7"/>
-    <row r="811" ht="15.75" customHeight="1" s="7"/>
-    <row r="812" ht="15.75" customHeight="1" s="7"/>
-    <row r="813" ht="15.75" customHeight="1" s="7"/>
-    <row r="814" ht="15.75" customHeight="1" s="7"/>
-    <row r="815" ht="15.75" customHeight="1" s="7"/>
-    <row r="816" ht="15.75" customHeight="1" s="7"/>
-    <row r="817" ht="15.75" customHeight="1" s="7"/>
-    <row r="818" ht="15.75" customHeight="1" s="7"/>
-    <row r="819" ht="15.75" customHeight="1" s="7"/>
-    <row r="820" ht="15.75" customHeight="1" s="7"/>
-    <row r="821" ht="15.75" customHeight="1" s="7"/>
-    <row r="822" ht="15.75" customHeight="1" s="7"/>
-    <row r="823" ht="15.75" customHeight="1" s="7"/>
-    <row r="824" ht="15.75" customHeight="1" s="7"/>
-    <row r="825" ht="15.75" customHeight="1" s="7"/>
-    <row r="826" ht="15.75" customHeight="1" s="7"/>
-    <row r="827" ht="15.75" customHeight="1" s="7"/>
-    <row r="828" ht="15.75" customHeight="1" s="7"/>
-    <row r="829" ht="15.75" customHeight="1" s="7"/>
-    <row r="830" ht="15.75" customHeight="1" s="7"/>
-    <row r="831" ht="15.75" customHeight="1" s="7"/>
-    <row r="832" ht="15.75" customHeight="1" s="7"/>
-    <row r="833" ht="15.75" customHeight="1" s="7"/>
-    <row r="834" ht="15.75" customHeight="1" s="7"/>
-    <row r="835" ht="15.75" customHeight="1" s="7"/>
-    <row r="836" ht="15.75" customHeight="1" s="7"/>
-    <row r="837" ht="15.75" customHeight="1" s="7"/>
-    <row r="838" ht="15.75" customHeight="1" s="7"/>
-    <row r="839" ht="15.75" customHeight="1" s="7"/>
-    <row r="840" ht="15.75" customHeight="1" s="7"/>
-    <row r="841" ht="15.75" customHeight="1" s="7"/>
-    <row r="842" ht="15.75" customHeight="1" s="7"/>
-    <row r="843" ht="15.75" customHeight="1" s="7"/>
-    <row r="844" ht="15.75" customHeight="1" s="7"/>
-    <row r="845" ht="15.75" customHeight="1" s="7"/>
-    <row r="846" ht="15.75" customHeight="1" s="7"/>
-    <row r="847" ht="15.75" customHeight="1" s="7"/>
-    <row r="848" ht="15.75" customHeight="1" s="7"/>
-    <row r="849" ht="15.75" customHeight="1" s="7"/>
-    <row r="850" ht="15.75" customHeight="1" s="7"/>
-    <row r="851" ht="15.75" customHeight="1" s="7"/>
-    <row r="852" ht="15.75" customHeight="1" s="7"/>
-    <row r="853" ht="15.75" customHeight="1" s="7"/>
-    <row r="854" ht="15.75" customHeight="1" s="7"/>
-    <row r="855" ht="15.75" customHeight="1" s="7"/>
-    <row r="856" ht="15.75" customHeight="1" s="7"/>
-    <row r="857" ht="15.75" customHeight="1" s="7"/>
-    <row r="858" ht="15.75" customHeight="1" s="7"/>
-    <row r="859" ht="15.75" customHeight="1" s="7"/>
-    <row r="860" ht="15.75" customHeight="1" s="7"/>
-    <row r="861" ht="15.75" customHeight="1" s="7"/>
-    <row r="862" ht="15.75" customHeight="1" s="7"/>
-    <row r="863" ht="15.75" customHeight="1" s="7"/>
-    <row r="864" ht="15.75" customHeight="1" s="7"/>
-    <row r="865" ht="15.75" customHeight="1" s="7"/>
-    <row r="866" ht="15.75" customHeight="1" s="7"/>
-    <row r="867" ht="15.75" customHeight="1" s="7"/>
-    <row r="868" ht="15.75" customHeight="1" s="7"/>
-    <row r="869" ht="15.75" customHeight="1" s="7"/>
-    <row r="870" ht="15.75" customHeight="1" s="7"/>
-    <row r="871" ht="15.75" customHeight="1" s="7"/>
-    <row r="872" ht="15.75" customHeight="1" s="7"/>
-    <row r="873" ht="15.75" customHeight="1" s="7"/>
-    <row r="874" ht="15.75" customHeight="1" s="7"/>
-    <row r="875" ht="15.75" customHeight="1" s="7"/>
-    <row r="876" ht="15.75" customHeight="1" s="7"/>
-    <row r="877" ht="15.75" customHeight="1" s="7"/>
-    <row r="878" ht="15.75" customHeight="1" s="7"/>
-    <row r="879" ht="15.75" customHeight="1" s="7"/>
-    <row r="880" ht="15.75" customHeight="1" s="7"/>
-    <row r="881" ht="15.75" customHeight="1" s="7"/>
-    <row r="882" ht="15.75" customHeight="1" s="7"/>
-    <row r="883" ht="15.75" customHeight="1" s="7"/>
-    <row r="884" ht="15.75" customHeight="1" s="7"/>
-    <row r="885" ht="15.75" customHeight="1" s="7"/>
-    <row r="886" ht="15.75" customHeight="1" s="7"/>
-    <row r="887" ht="15.75" customHeight="1" s="7"/>
-    <row r="888" ht="15.75" customHeight="1" s="7"/>
-    <row r="889" ht="15.75" customHeight="1" s="7"/>
-    <row r="890" ht="15.75" customHeight="1" s="7"/>
-    <row r="891" ht="15.75" customHeight="1" s="7"/>
-    <row r="892" ht="15.75" customHeight="1" s="7"/>
-    <row r="893" ht="15.75" customHeight="1" s="7"/>
-    <row r="894" ht="15.75" customHeight="1" s="7"/>
-    <row r="895" ht="15.75" customHeight="1" s="7"/>
-    <row r="896" ht="15.75" customHeight="1" s="7"/>
-    <row r="897" ht="15.75" customHeight="1" s="7"/>
-    <row r="898" ht="15.75" customHeight="1" s="7"/>
-    <row r="899" ht="15.75" customHeight="1" s="7"/>
-    <row r="900" ht="15.75" customHeight="1" s="7"/>
-    <row r="901" ht="15.75" customHeight="1" s="7"/>
-    <row r="902" ht="15.75" customHeight="1" s="7"/>
-    <row r="903" ht="15.75" customHeight="1" s="7"/>
-    <row r="904" ht="15.75" customHeight="1" s="7"/>
-    <row r="905" ht="15.75" customHeight="1" s="7"/>
-    <row r="906" ht="15.75" customHeight="1" s="7"/>
-    <row r="907" ht="15.75" customHeight="1" s="7"/>
-    <row r="908" ht="15.75" customHeight="1" s="7"/>
-    <row r="909" ht="15.75" customHeight="1" s="7"/>
-    <row r="910" ht="15.75" customHeight="1" s="7"/>
-    <row r="911" ht="15.75" customHeight="1" s="7"/>
-    <row r="912" ht="15.75" customHeight="1" s="7"/>
-    <row r="913" ht="15.75" customHeight="1" s="7"/>
-    <row r="914" ht="15.75" customHeight="1" s="7"/>
-    <row r="915" ht="15.75" customHeight="1" s="7"/>
-    <row r="916" ht="15.75" customHeight="1" s="7"/>
-    <row r="917" ht="15.75" customHeight="1" s="7"/>
-    <row r="918" ht="15.75" customHeight="1" s="7"/>
-    <row r="919" ht="15.75" customHeight="1" s="7"/>
-    <row r="920" ht="15.75" customHeight="1" s="7"/>
-    <row r="921" ht="15.75" customHeight="1" s="7"/>
-    <row r="922" ht="15.75" customHeight="1" s="7"/>
-    <row r="923" ht="15.75" customHeight="1" s="7"/>
-    <row r="924" ht="15.75" customHeight="1" s="7"/>
-    <row r="925" ht="15.75" customHeight="1" s="7"/>
-    <row r="926" ht="15.75" customHeight="1" s="7"/>
-    <row r="927" ht="15.75" customHeight="1" s="7"/>
-    <row r="928" ht="15.75" customHeight="1" s="7"/>
-    <row r="929" ht="15.75" customHeight="1" s="7"/>
-    <row r="930" ht="15.75" customHeight="1" s="7"/>
-    <row r="931" ht="15.75" customHeight="1" s="7"/>
-    <row r="932" ht="15.75" customHeight="1" s="7"/>
-    <row r="933" ht="15.75" customHeight="1" s="7"/>
-    <row r="934" ht="15.75" customHeight="1" s="7"/>
-    <row r="935" ht="15.75" customHeight="1" s="7"/>
-    <row r="936" ht="15.75" customHeight="1" s="7"/>
-    <row r="937" ht="15.75" customHeight="1" s="7"/>
-    <row r="938" ht="15.75" customHeight="1" s="7"/>
-    <row r="939" ht="15.75" customHeight="1" s="7"/>
-    <row r="940" ht="15.75" customHeight="1" s="7"/>
-    <row r="941" ht="15.75" customHeight="1" s="7"/>
-    <row r="942" ht="15.75" customHeight="1" s="7"/>
-    <row r="943" ht="15.75" customHeight="1" s="7"/>
-    <row r="944" ht="15.75" customHeight="1" s="7"/>
-    <row r="945" ht="15.75" customHeight="1" s="7"/>
-    <row r="946" ht="15.75" customHeight="1" s="7"/>
-    <row r="947" ht="15.75" customHeight="1" s="7"/>
-    <row r="948" ht="15.75" customHeight="1" s="7"/>
-    <row r="949" ht="15.75" customHeight="1" s="7"/>
-    <row r="950" ht="15.75" customHeight="1" s="7"/>
-    <row r="951" ht="15.75" customHeight="1" s="7"/>
-    <row r="952" ht="15.75" customHeight="1" s="7"/>
-    <row r="953" ht="15.75" customHeight="1" s="7"/>
-    <row r="954" ht="15.75" customHeight="1" s="7"/>
-    <row r="955" ht="15.75" customHeight="1" s="7"/>
-    <row r="956" ht="15.75" customHeight="1" s="7"/>
-    <row r="957" ht="15.75" customHeight="1" s="7"/>
-    <row r="958" ht="15.75" customHeight="1" s="7"/>
-    <row r="959" ht="15.75" customHeight="1" s="7"/>
-    <row r="960" ht="15.75" customHeight="1" s="7"/>
-    <row r="961" ht="15.75" customHeight="1" s="7"/>
-    <row r="962" ht="15.75" customHeight="1" s="7"/>
-    <row r="963" ht="15.75" customHeight="1" s="7"/>
-    <row r="964" ht="15.75" customHeight="1" s="7"/>
-    <row r="965" ht="15.75" customHeight="1" s="7"/>
-    <row r="966" ht="15.75" customHeight="1" s="7"/>
-    <row r="967" ht="15.75" customHeight="1" s="7"/>
-    <row r="968" ht="15.75" customHeight="1" s="7"/>
-    <row r="969" ht="15.75" customHeight="1" s="7"/>
-    <row r="970" ht="15.75" customHeight="1" s="7"/>
-    <row r="971" ht="15.75" customHeight="1" s="7"/>
-    <row r="972" ht="15.75" customHeight="1" s="7"/>
-    <row r="973" ht="15.75" customHeight="1" s="7"/>
-    <row r="974" ht="15.75" customHeight="1" s="7"/>
-    <row r="975" ht="15.75" customHeight="1" s="7"/>
-    <row r="976" ht="15.75" customHeight="1" s="7"/>
-    <row r="977" ht="15.75" customHeight="1" s="7"/>
-    <row r="978" ht="15.75" customHeight="1" s="7"/>
-    <row r="979" ht="15.75" customHeight="1" s="7"/>
-    <row r="980" ht="15.75" customHeight="1" s="7"/>
-    <row r="981" ht="15.75" customHeight="1" s="7"/>
-    <row r="982" ht="15.75" customHeight="1" s="7"/>
-    <row r="983" ht="15.75" customHeight="1" s="7"/>
-    <row r="984" ht="15.75" customHeight="1" s="7"/>
-    <row r="985" ht="15.75" customHeight="1" s="7"/>
-    <row r="986" ht="15.75" customHeight="1" s="7"/>
-    <row r="987" ht="15.75" customHeight="1" s="7"/>
-    <row r="988" ht="15.75" customHeight="1" s="7"/>
-    <row r="989" ht="15.75" customHeight="1" s="7"/>
-    <row r="990" ht="15.75" customHeight="1" s="7"/>
-    <row r="991" ht="15.75" customHeight="1" s="7"/>
-    <row r="992" ht="15.75" customHeight="1" s="7"/>
-    <row r="993" ht="15.75" customHeight="1" s="7"/>
-    <row r="994" ht="15.75" customHeight="1" s="7"/>
-    <row r="995" ht="15.75" customHeight="1" s="7"/>
-    <row r="996" ht="15.75" customHeight="1" s="7"/>
-    <row r="997" ht="15.75" customHeight="1" s="7"/>
-    <row r="998" ht="15.75" customHeight="1" s="7"/>
-    <row r="999" ht="15.75" customHeight="1" s="7"/>
-    <row r="1000" ht="15.75" customHeight="1" s="7"/>
   </sheetData>
-  <mergeCells count="73">
-    <mergeCell ref="B53:B55"/>
-    <mergeCell ref="B93:B94"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B64:B71"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="B72:B77"/>
-    <mergeCell ref="B85:B92"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="D49:D52"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="D58:D60"/>
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B47:B52"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="B56:B61"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="C64:C71"/>
-    <mergeCell ref="C25:C28"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="D91:D92"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="C93:C94"/>
-    <mergeCell ref="C21:C24"/>
-    <mergeCell ref="C85:C92"/>
-    <mergeCell ref="D79:D81"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B79:B83"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="C47:C52"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="D66:D71"/>
-    <mergeCell ref="C56:C61"/>
-    <mergeCell ref="D13:D18"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="D74:D75"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="D25:D28"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="D89:D90"/>
-    <mergeCell ref="C35:C37"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="C79:C83"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="C72:C77"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="C13:C18"/>
-    <mergeCell ref="D85:D88"/>
-    <mergeCell ref="D40:D41"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Send_Message/Send_Message_Test_Cases.xlsx
+++ b/Send_Message/Send_Message_Test_Cases.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -637,184 +637,136 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>MSG_005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Verify Message Input field</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Verify empty message cannot be sent</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
 2. Leave input field empty.
 3. Click send button.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Send button should be disabled or message should not be sent.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>MSG_006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Verify message with only spaces</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
 2. Type only spaces.
 3. Click send button.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Message should not be sent; spaces-only input should be treated as empty.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>MSG_007</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Verify Send button</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Verify send button is visible</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1. Open any chat conversation.
-2. Observe send button next to input field.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Send button (arrow/paper plane icon) should be visible.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>MSG_008</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="n"/>
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Verify send button enabled when text entered</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1. Open any chat conversation.
-2. Type a message.
-3. Observe send button.</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Send button should become enabled/highlighted when text is entered.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>MSG_009</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
+          <t>MSG_007</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Verify Send button</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and message typed</t>
+          <t>User is logged in and chat is open</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Verify send button click sends message</t>
+          <t>Verify send button is visible</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1. Type a message.
-2. Click send button.
-3. Observe chat.</t>
+          <t>1. Open any chat conversation.
+2. Observe send button next to input field.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Message should be sent and appear in chat with sent status.</t>
+          <t>Send button (arrow/paper plane icon) should be visible.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -826,7 +778,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>MSG_010</t>
+          <t>MSG_008</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -834,247 +786,207 @@
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>Verify send button enabled when text entered</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Open any chat conversation.
+2. Type a message.
+3. Observe send button.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Send button should become enabled/highlighted when text is entered.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>MSG_009</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and message typed</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Verify send button click sends message</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Type a message.
+2. Click send button.
+3. Observe chat.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Message should be sent and appear in chat with sent status.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>MSG_010</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>Verify send button visual feedback on click</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1. Type a message.
 2. Click send button.
 3. Observe button.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Send button should show click feedback (color change, animation).</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>MSG_011</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Verify Send button</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Verify send button disabled when empty</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
 2. Leave input field empty.
 3. Observe send button.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Send button should be disabled or grayed out.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>MSG_012</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Verify Text message sending</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Verify sending simple text message</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
 2. Type "Hello".
 3. Click send.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Message "Hello" should appear in chat on right side (sent).</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>MSG_013</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending long text message</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1. Open any chat conversation.
-2. Type a 500+ character message.
-3. Click send.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Long message should be sent successfully and display properly.</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>MSG_014</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending message with special characters</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1. Open any chat conversation.
-2. Type "Hello @#$%^&amp;*()!".
-3. Click send.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Message with special characters should be sent and displayed correctly.</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>MSG_015</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending message with emojis</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1. Open any chat conversation.
-2. Type "Hello 😀🎉👍".
-3. Click send.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Message with emojis should be sent and emojis displayed correctly.</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>MSG_016</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending message with numbers</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1. Open any chat conversation.
-2. Type "Order #12345".
-3. Click send.</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Message with numbers should be sent correctly.</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>MSG_017</t>
+          <t>MSG_013</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
@@ -1082,19 +994,19 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify sending message with URL</t>
+          <t>Verify sending long text message</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
-2. Type "Check https://example.com".
+2. Type a 500+ character message.
 3. Click send.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Message should be sent; URL may be clickable/highlighted.</t>
+          <t>Long message should be sent successfully and display properly.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1106,129 +1018,103 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>MSG_018</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Verify Text message sending</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network disconnected</t>
-        </is>
-      </c>
+          <t>MSG_014</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify message sending fails without network</t>
+          <t>Verify sending message with special characters</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1. Disconnect network.
-2. Type a message.
+          <t>1. Open any chat conversation.
+2. Type "Hello @#$%^&amp;*()!".
 3. Click send.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Error indicator should show; message should be queued or show failed status.</t>
+          <t>Message with special characters should be sent and displayed correctly.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>MSG_019</t>
+          <t>MSG_015</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify extremely long message handling</t>
+          <t>Verify sending message with emojis</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1. Type a 10000+ character message.
-2. Click send.</t>
+          <t>1. Open any chat conversation.
+2. Type "Hello 😀🎉👍".
+3. Click send.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Application should handle gracefully; either send or show character limit warning.</t>
+          <t>Message with emojis should be sent and emojis displayed correctly.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Low / Medium</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>MSG_020</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Verify Sent message display</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>User has sent a message</t>
-        </is>
-      </c>
+          <t>MSG_016</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Verify sent message alignment</t>
+          <t>Verify sending message with numbers</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1. Send a message.
-2. Observe message position in chat.</t>
+          <t>1. Open any chat conversation.
+2. Type "Order #12345".
+3. Click send.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Sent message should appear on the right side of chat window.</t>
+          <t>Message with numbers should be sent correctly.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MSG_021</t>
+          <t>MSG_017</t>
         </is>
       </c>
       <c r="B22" s="2" t="n"/>
@@ -1236,18 +1122,19 @@
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Verify sent message bubble color</t>
+          <t>Verify sending message with URL</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1. Send a message.
-2. Observe message bubble.</t>
+          <t>1. Open any chat conversation.
+2. Type "Check https://example.com".
+3. Click send.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Sent message should have distinct bubble color (e.g., blue/purple).</t>
+          <t>Message should be sent; URL may be clickable/highlighted.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1257,59 +1144,51 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>MSG_022</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="n"/>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Verify sent message timestamp</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1. Send a message.
-2. Observe timestamp.</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Timestamp should display below or next to sent message.</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MSG_023</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
+          <t>MSG_018</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Verify Text message sending</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, network disconnected</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verify sent message status indicator</t>
+          <t>Verify message sending fails without network</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1. Send a message.
-2. Observe status indicator.</t>
+          <t>1. Disconnect network.
+2. Type a message.
+3. Click send.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Status indicator should show (single tick = sent, double tick = delivered, blue tick = read).</t>
+          <t>Error indicator should show; message should be queued or show failed status.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1321,112 +1200,95 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>MSG_024</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Verify Received message display</t>
-        </is>
-      </c>
+          <t>MSG_019</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>User has received a message</t>
+          <t>User is logged in and chat is open</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Verify received message alignment</t>
+          <t>Verify extremely long message handling</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1. Receive a message from another user.
-2. Observe message position.</t>
+          <t>1. Type a 10000+ character message.
+2. Click send.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Received message should appear on the left side of chat window.</t>
+          <t>Application should handle gracefully; either send or show character limit warning.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Low / Medium</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>MSG_025</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="n"/>
       <c r="B26" s="2" t="n"/>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Verify received message bubble color</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>1. Receive a message.
-2. Observe message bubble.</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Received message should have different bubble color than sent (e.g., gray/white).</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>MSG_026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
+          <t>MSG_020</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Verify Sent message display</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>User has sent a message</t>
+        </is>
+      </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Verify received message sender info</t>
+          <t>Verify sent message alignment</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1. Receive a message in group chat.
-2. Observe sender info.</t>
+          <t>1. Send a message.
+2. Observe message position in chat.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Sender name and/or avatar should display with received message in group chats.</t>
+          <t>Sent message should appear on the right side of chat window.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>MSG_027</t>
+          <t>MSG_021</t>
         </is>
       </c>
       <c r="B28" s="2" t="n"/>
@@ -1434,18 +1296,18 @@
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Verify received message timestamp</t>
+          <t>Verify sent message bubble color</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1. Receive a message.
-2. Observe timestamp.</t>
+          <t>1. Send a message.
+2. Observe message bubble.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Timestamp should display below or next to received message.</t>
+          <t>Sent message should have distinct bubble color (e.g., blue/purple).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1457,51 +1319,38 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>MSG_028</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Verify Enter key to send</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and message typed</t>
-        </is>
-      </c>
+          <t>MSG_022</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Verify Enter key sends message</t>
+          <t>Verify sent message timestamp</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1. Type a message.
-2. Press Enter key.
-3. Observe chat.</t>
+          <t>1. Send a message.
+2. Observe timestamp.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Message should be sent when Enter key is pressed.</t>
+          <t>Timestamp should display below or next to sent message.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>MSG_029</t>
+          <t>MSG_023</t>
         </is>
       </c>
       <c r="B30" s="2" t="n"/>
@@ -1509,161 +1358,135 @@
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Verify Shift+Enter creates new line</t>
+          <t>Verify sent message status indicator</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1. Type a message.
-2. Press Shift+Enter.
-3. Continue typing.</t>
+          <t>1. Send a message.
+2. Observe status indicator.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>New line should be created; message should not be sent.</t>
+          <t>Status indicator should show (single tick = sent, double tick = delivered, blue tick = read).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>MSG_030</t>
+          <t>MSG_024</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Verify Enter key to send</t>
+          <t>Verify Received message display</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and input is empty</t>
+          <t>User has received a message</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Verify Enter key with empty input</t>
+          <t>Verify received message alignment</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1. Leave input field empty.
-2. Press Enter key.</t>
+          <t>1. Receive a message from another user.
+2. Observe message position.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Nothing should happen; empty message should not be sent.</t>
+          <t>Received message should appear on the left side of chat window.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>MSG_031</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Verify Message input clear after send</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>User has sent a message</t>
-        </is>
-      </c>
+          <t>MSG_025</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Verify input field clears after sending</t>
+          <t>Verify received message bubble color</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1. Type a message.
-2. Click send.
-3. Observe input field.</t>
+          <t>1. Receive a message.
+2. Observe message bubble.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Input field should be cleared after message is sent successfully.</t>
+          <t>Received message should have different bubble color than sent (e.g., gray/white).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>MSG_032</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Verify Real-time message delivery</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Two users are in same chat</t>
-        </is>
-      </c>
+          <t>MSG_026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Verify message appears instantly for recipient</t>
+          <t>Verify received message sender info</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1. User A sends message.
-2. User B observes chat.</t>
+          <t>1. Receive a message in group chat.
+2. Observe sender info.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Message should appear in User B's chat within seconds without refresh.</t>
+          <t>Sender name and/or avatar should display with received message in group chats.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>MSG_033</t>
+          <t>MSG_027</t>
         </is>
       </c>
       <c r="B34" s="2" t="n"/>
@@ -1671,18 +1494,18 @@
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Verify typing indicator</t>
+          <t>Verify received message timestamp</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1. User A starts typing.
-2. User B observes chat.</t>
+          <t>1. Receive a message.
+2. Observe timestamp.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Typing indicator should appear for User B (e.g., "User A is typing...").</t>
+          <t>Timestamp should display below or next to received message.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1694,7 +1517,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MSG_034</t>
+          <t>MSG_028</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1704,40 +1527,41 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Verify Message scroll behavior</t>
+          <t>Verify Enter key to send</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>User is in chat with many messages</t>
+          <t>User is logged in and message typed</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Verify auto-scroll to new message</t>
+          <t>Verify Enter key sends message</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1. Be at bottom of chat.
-2. Send or receive new message.</t>
+          <t>1. Type a message.
+2. Press Enter key.
+3. Observe chat.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Chat should auto-scroll to show the new message.</t>
+          <t>Message should be sent when Enter key is pressed.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>MSG_035</t>
+          <t>MSG_029</t>
         </is>
       </c>
       <c r="B36" s="2" t="n"/>
@@ -1745,18 +1569,19 @@
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Verify scroll up to view history</t>
+          <t>Verify Shift+Enter creates new line</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1. Open chat with many messages.
-2. Scroll up.</t>
+          <t>1. Type a message.
+2. Press Shift+Enter.
+3. Continue typing.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Older messages should load; scrolling should be smooth.</t>
+          <t>New line should be created; message should not be sent.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1766,118 +1591,72 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>MSG_036</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="n"/>
       <c r="B37" s="2" t="n"/>
       <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>User is scrolled up in chat</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Verify new message notification when scrolled up</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>1. Scroll up in chat.
-2. Receive new message.</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Notification or "New message" button should appear to scroll to bottom.</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>MSG_037</t>
+          <t>MSG_030</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Verify Attachment button</t>
+          <t>Verify Enter key to send</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and chat is open</t>
+          <t>User is logged in and input is empty</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Verify attachment button is visible</t>
+          <t>Verify Enter key with empty input</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Observe attachment button.</t>
+          <t>1. Leave input field empty.
+2. Press Enter key.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Attachment button (paperclip/+ icon) should be visible near input field.</t>
+          <t>Nothing should happen; empty message should not be sent.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>MSG_038</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="n"/>
       <c r="B39" s="2" t="n"/>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Verify attachment button click opens options</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>1. Open any chat conversation.
-2. Click attachment button.</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Attachment options should appear (image, file, camera, etc.).</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>MSG_039</t>
+          <t>MSG_031</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1887,94 +1666,103 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Verify Emoji button</t>
+          <t>Verify Message input clear after send</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and chat is open</t>
+          <t>User has sent a message</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Verify emoji button is visible</t>
+          <t>Verify input field clears after sending</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Observe emoji button.</t>
+          <t>1. Type a message.
+2. Click send.
+3. Observe input field.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Emoji button (smiley icon) should be visible near input field.</t>
+          <t>Input field should be cleared after message is sent successfully.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>MSG_040</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
+          <t>MSG_032</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Verify Real-time message delivery</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Two users are in same chat</t>
+        </is>
+      </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Verify emoji button click opens picker</t>
+          <t>Verify message appears instantly for recipient</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Click emoji button.</t>
+          <t>1. User A sends message.
+2. User B observes chat.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Emoji picker should open with emoji categories.</t>
+          <t>Message should appear in User B's chat within seconds without refresh.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>MSG_041</t>
+          <t>MSG_033</t>
         </is>
       </c>
       <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and emoji picker open</t>
-        </is>
-      </c>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Verify selecting emoji adds to input</t>
+          <t>Verify typing indicator</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1. Open emoji picker.
-2. Click on an emoji.</t>
+          <t>1. User A starts typing.
+2. User B observes chat.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Selected emoji should be added to message input field.</t>
+          <t>Typing indicator should appear for User B (e.g., "User A is typing...").</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -1986,7 +1774,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>MSG_042</t>
+          <t>MSG_034</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1996,29 +1784,28 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Verify UI responsiveness</t>
+          <t>Verify Message scroll behavior</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>User is logged in</t>
+          <t>User is in chat with many messages</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Verify message input on desktop</t>
+          <t>Verify auto-scroll to new message</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1. Open application on desktop.
-2. Open chat.
-3. Resize browser.</t>
+          <t>1. Be at bottom of chat.
+2. Send or receive new message.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Message input and send button should remain functional and visible.</t>
+          <t>Chat should auto-scroll to show the new message.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2030,7 +1817,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>MSG_043</t>
+          <t>MSG_035</t>
         </is>
       </c>
       <c r="B44" s="2" t="n"/>
@@ -2038,200 +1825,513 @@
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
+          <t>Verify scroll up to view history</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>1. Open chat with many messages.
+2. Scroll up.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Older messages should load; scrolling should be smooth.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>MSG_036</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>User is scrolled up in chat</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Verify new message notification when scrolled up</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>1. Scroll up in chat.
+2. Receive new message.</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Notification or "New message" button should appear to scroll to bottom.</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>MSG_037</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Verify Attachment button</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Verify attachment button is visible</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>1. Open any chat conversation.
+2. Observe attachment button.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Attachment button (paperclip/+ icon) should be visible near input field.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>MSG_038</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Verify attachment button click opens options</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>1. Open any chat conversation.
+2. Click attachment button.</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Attachment options should appear (image, file, camera, etc.).</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>MSG_039</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Verify Emoji button</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Verify emoji button is visible</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>1. Open any chat conversation.
+2. Observe emoji button.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Emoji button (smiley icon) should be visible near input field.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>MSG_040</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Verify emoji button click opens picker</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>1. Open any chat conversation.
+2. Click emoji button.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Emoji picker should open with emoji categories.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>MSG_041</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and emoji picker open</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Verify selecting emoji adds to input</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>1. Open emoji picker.
+2. Click on an emoji.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Selected emoji should be added to message input field.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>MSG_042</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Verify UI responsiveness</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Verify message input on desktop</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>1. Open application on desktop.
+2. Open chat.
+3. Resize browser.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Message input and send button should remain functional and visible.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>MSG_043</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
           <t>Verify message input on mobile</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Open application on mobile.
 2. Open chat.
 3. Check keyboard interaction.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>Input field should work with mobile keyboard; send button should be accessible.</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>MSG_044</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Verify Message loading</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>User is logged in, slow network</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Verify message sending with slow network</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Simulate slow network.
 2. Send a message.
 3. Observe behavior.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Loading indicator should show; message should eventually send or show retry option.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>MSG_045</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n"/>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network error</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Verify message retry on failure</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Send message during network error.
 2. Observe failed message.
 3. Click retry.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>Retry option should be available; message should resend on retry.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>MSG_046</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Verify Attachment feature</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Verify attachment icon is visible</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
 2. Observe attachment icon near input field.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>Attachment icon (paperclip/+ icon) should be visible.</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>MSG_047</t>
         </is>
       </c>
-      <c r="B48" s="2" t="n"/>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Verify attachment options menu</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Click on attachment icon.
 2. Observe options menu.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>Options menu should display (Image, Video, Document, Camera, etc.).</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>MSG_048</t>
         </is>
       </c>
-      <c r="B49" s="2" t="n"/>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>User is logged in and attachment menu open</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Verify sending image attachment</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Click attachment icon.
 2. Select Image option.
@@ -2239,32 +2339,32 @@
 4. Send.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>Image should be uploaded and sent; preview should display in chat.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>MSG_049</t>
         </is>
       </c>
-      <c r="B50" s="2" t="n"/>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Verify sending document attachment</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Click attachment icon.
 2. Select Document option.
@@ -2272,32 +2372,32 @@
 4. Send.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>Document should be uploaded and sent; file icon with name should display.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>MSG_050</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n"/>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Verify sending video attachment</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Click attachment icon.
 2. Select Video option.
@@ -2305,489 +2405,106 @@
 4. Send.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>Video should be uploaded and sent; video thumbnail should display.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>MSG_051</t>
         </is>
       </c>
-      <c r="B52" s="2" t="n"/>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n"/>
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Verify attachment upload progress</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Click attachment icon.
 2. Select a large file.
 3. Observe upload.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>Upload progress indicator should display during file upload.</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="n"/>
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n"/>
+      <c r="E63" s="2" t="n"/>
+      <c r="F63" s="2" t="n"/>
+      <c r="G63" s="2" t="n"/>
+      <c r="H63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>MSG_052</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Verify Attachment feature</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Verify unsupported file type handling</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Click attachment icon.
 2. Try to select unsupported file type.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>Error message should display or file should not be selectable.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>MSG_053</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Verify file size limit handling</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>1. Click attachment icon.
-2. Select file exceeding size limit.</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Error message should display indicating file size limit exceeded.</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>MSG_054</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n"/>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network error</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Verify attachment upload failure handling</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>1. Disconnect network.
-2. Try to send attachment.</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Error message should display; retry option should be available.</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>MSG_055</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Verify Voice Recording feature</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Verify recording button is visible</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>1. Open any chat conversation.
-2. Observe microphone/recording icon.</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Recording button (microphone icon) should be visible near input field.</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>MSG_056</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n"/>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Verify recording starts on button press</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>1. Press and hold recording button.
-2. Observe recording indicator.</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Recording should start; timer and waveform indicator should display.</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>MSG_057</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="n"/>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>User is recording voice message</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Verify recording timer display</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>1. Start recording.
-2. Observe timer.</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Recording duration timer should display and increment.</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>MSG_058</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="n"/>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n"/>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending voice message</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>1. Record a voice message.
-2. Release button or click send.
-3. Observe chat.</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>Voice message should be sent and appear in chat with play button.</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>MSG_059</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="n"/>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Verify cancel recording</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>1. Start recording.
-2. Slide to cancel or click cancel button.</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Recording should be cancelled; no message should be sent.</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>MSG_060</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="n"/>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>User has received voice message</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Verify playing received voice message</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>1. Receive a voice message.
-2. Click play button.</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Voice message should play; progress indicator should show.</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>MSG_061</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Verify Voice Recording feature</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, microphone permission denied</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>Verify recording without microphone permission</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>1. Deny microphone permission.
-2. Try to record voice message.</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>Permission request should appear or error message should display.</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>MSG_062</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="n"/>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>Verify very short recording handling</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>1. Press and release recording button quickly (&lt; 1 second).</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>Recording should be cancelled or warning should display.</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>MSG_063</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Verify Emoji feature</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Verify emoji button is visible</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>1. Open any chat conversation.
-2. Observe emoji button.</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Emoji button (smiley face icon) should be visible near input field.</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>MSG_064</t>
+          <t>MSG_053</t>
         </is>
       </c>
       <c r="B65" s="2" t="n"/>
@@ -2795,127 +2512,118 @@
       <c r="D65" s="2" t="n"/>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Verify emoji picker opens</t>
+          <t>Verify file size limit handling</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>1. Click on emoji button.
-2. Observe emoji picker.</t>
+          <t>1. Click attachment icon.
+2. Select file exceeding size limit.</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Emoji picker should open with categories (Smileys, Animals, Food, etc.).</t>
+          <t>Error message should display indicating file size limit exceeded.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>MSG_065</t>
+          <t>MSG_054</t>
         </is>
       </c>
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and emoji picker open</t>
+          <t>User is logged in, network error</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Verify emoji categories navigation</t>
+          <t>Verify attachment upload failure handling</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>1. Open emoji picker.
-2. Click on different category tabs.</t>
+          <t>1. Disconnect network.
+2. Try to send attachment.</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Different emoji categories should display when tabs are clicked.</t>
+          <t>Error message should display; retry option should be available.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>MSG_066</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="n"/>
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n"/>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Verify selecting emoji adds to input</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>1. Open emoji picker.
-2. Click on any emoji.</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Selected emoji should be added to message input field at cursor position.</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E67" s="2" t="n"/>
+      <c r="F67" s="2" t="n"/>
+      <c r="G67" s="2" t="n"/>
+      <c r="H67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>MSG_067</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="n"/>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="n"/>
+          <t>MSG_055</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Verify Voice Recording feature</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple emoji selection</t>
+          <t>Verify recording button is visible</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>1. Open emoji picker.
-2. Click multiple emojis.</t>
+          <t>1. Open any chat conversation.
+2. Observe microphone/recording icon.</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>All selected emojis should be added to input field.</t>
+          <t>Recording button (microphone icon) should be visible near input field.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>MSG_068</t>
+          <t>MSG_056</t>
         </is>
       </c>
       <c r="B69" s="2" t="n"/>
@@ -2923,63 +2631,65 @@
       <c r="D69" s="2" t="n"/>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Verify emoji search functionality</t>
+          <t>Verify recording starts on button press</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>1. Open emoji picker.
-2. Type in emoji search field.
-3. Observe results.</t>
+          <t>1. Press and hold recording button.
+2. Observe recording indicator.</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Matching emojis should display based on search term.</t>
+          <t>Recording should start; timer and waveform indicator should display.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>MSG_069</t>
+          <t>MSG_057</t>
         </is>
       </c>
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n"/>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>User is recording voice message</t>
+        </is>
+      </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Verify recent emojis section</t>
+          <t>Verify recording timer display</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>1. Send message with emoji.
-2. Open emoji picker again.
-3. Check recent section.</t>
+          <t>1. Start recording.
+2. Observe timer.</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Recently used emojis should appear in recent/frequently used section.</t>
+          <t>Recording duration timer should display and increment.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>MSG_070</t>
+          <t>MSG_058</t>
         </is>
       </c>
       <c r="B71" s="2" t="n"/>
@@ -2987,92 +2697,85 @@
       <c r="D71" s="2" t="n"/>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Verify closing emoji picker</t>
+          <t>Verify sending voice message</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>1. Open emoji picker.
-2. Click outside picker or close button.</t>
+          <t>1. Record a voice message.
+2. Release button or click send.
+3. Observe chat.</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Emoji picker should close.</t>
+          <t>Voice message should be sent and appear in chat with play button.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>MSG_071</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Verify Sticker feature</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>MSG_059</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Verify sticker button/tab is visible</t>
+          <t>Verify cancel recording</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Observe sticker option.</t>
+          <t>1. Start recording.
+2. Slide to cancel or click cancel button.</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Sticker button or tab should be visible (may be in emoji picker).</t>
+          <t>Recording should be cancelled; no message should be sent.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>MSG_072</t>
+          <t>MSG_060</t>
         </is>
       </c>
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n"/>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>User has received voice message</t>
+        </is>
+      </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Verify sticker picker opens</t>
+          <t>Verify playing received voice message</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>1. Click on sticker button/tab.
-2. Observe sticker picker.</t>
+          <t>1. Receive a voice message.
+2. Click play button.</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Sticker picker should open with sticker packs.</t>
+          <t>Voice message should play; progress indicator should show.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -3082,63 +2785,50 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>MSG_073</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="n"/>
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and sticker picker open</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>Verify sticker packs display</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>1. Open sticker picker.
-2. Observe available sticker packs.</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>Different sticker packs should be visible and selectable.</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="n"/>
+      <c r="G74" s="2" t="n"/>
+      <c r="H74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>MSG_074</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="n"/>
-      <c r="C75" s="2" t="n"/>
-      <c r="D75" s="2" t="n"/>
+          <t>MSG_061</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Verify Voice Recording feature</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, microphone permission denied</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Verify sending sticker</t>
+          <t>Verify recording without microphone permission</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>1. Open sticker picker.
-2. Click on any sticker.</t>
+          <t>1. Deny microphone permission.
+2. Try to record voice message.</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Sticker should be sent immediately and appear in chat.</t>
+          <t>Permission request should appear or error message should display.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -3150,151 +2840,113 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>MSG_075</t>
+          <t>MSG_062</t>
         </is>
       </c>
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>User has received sticker</t>
+          <t>User is logged in and chat is open</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Verify received sticker display</t>
+          <t>Verify very short recording handling</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>1. Receive a sticker from another user.
-2. Observe chat.</t>
+          <t>1. Press and release recording button quickly (&lt; 1 second).</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Sticker should display properly in chat on left side.</t>
+          <t>Recording should be cancelled or warning should display.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>MSG_076</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="n"/>
       <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and sticker picker open</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>Verify sticker pack switching</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>1. Open sticker picker.
-2. Click on different sticker pack.</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>Selected sticker pack's stickers should display.</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
+      <c r="D77" s="2" t="n"/>
+      <c r="E77" s="2" t="n"/>
+      <c r="F77" s="2" t="n"/>
+      <c r="G77" s="2" t="n"/>
+      <c r="H77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>MSG_077</t>
+          <t>MSG_063</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Verify Sticker feature</t>
+          <t>Verify Emoji feature</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, no sticker packs available</t>
+          <t>User is logged in and chat is open</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Verify empty sticker state</t>
+          <t>Verify emoji button is visible</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>1. Open sticker picker with no packs.
-2. Observe display.</t>
+          <t>1. Open any chat conversation.
+2. Observe emoji button.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Empty state or option to download sticker packs should display.</t>
+          <t>Emoji button (smiley face icon) should be visible near input field.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>MSG_078</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Verify @all mention feature</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and group chat is open</t>
-        </is>
-      </c>
+          <t>MSG_064</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Verify typing @all shows suggestion</t>
+          <t>Verify emoji picker opens</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>1. Open group chat.
-2. Type "@all" in input field.</t>
+          <t>1. Click on emoji button.
+2. Observe emoji picker.</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>"@all" suggestion should appear to mention all group members.</t>
+          <t>Emoji picker should open with categories (Smileys, Animals, Food, etc.).</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -3306,38 +2958,42 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>MSG_079</t>
+          <t>MSG_065</t>
         </is>
       </c>
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n"/>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and emoji picker open</t>
+        </is>
+      </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Verify selecting @all mention</t>
+          <t>Verify emoji categories navigation</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>1. Type "@all".
-2. Select @all from suggestions.</t>
+          <t>1. Open emoji picker.
+2. Click on different category tabs.</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>"@all" should be added to message with special formatting.</t>
+          <t>Different emoji categories should display when tabs are clicked.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>MSG_080</t>
+          <t>MSG_066</t>
         </is>
       </c>
       <c r="B81" s="2" t="n"/>
@@ -3345,18 +3001,18 @@
       <c r="D81" s="2" t="n"/>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Verify sending message with @all</t>
+          <t>Verify selecting emoji adds to input</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>1. Type message with @all.
-2. Send message.</t>
+          <t>1. Open emoji picker.
+2. Click on any emoji.</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Message should be sent; all group members should receive notification.</t>
+          <t>Selected emoji should be added to message input field at cursor position.</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -3368,42 +3024,38 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>MSG_081</t>
+          <t>MSG_067</t>
         </is>
       </c>
       <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>User has received @all mention</t>
-        </is>
-      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Verify @all mention notification</t>
+          <t>Verify multiple emoji selection</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>1. Another user sends @all in group.
-2. Observe notification.</t>
+          <t>1. Open emoji picker.
+2. Click multiple emojis.</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>User should receive notification for @all mention.</t>
+          <t>All selected emojis should be added to input field.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>MSG_082</t>
+          <t>MSG_068</t>
         </is>
       </c>
       <c r="B83" s="2" t="n"/>
@@ -3411,18 +3063,19 @@
       <c r="D83" s="2" t="n"/>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Verify @all highlight in message</t>
+          <t>Verify emoji search functionality</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>1. Receive message with @all.
-2. Observe message display.</t>
+          <t>1. Open emoji picker.
+2. Type in emoji search field.
+3. Observe results.</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>"@all" should be highlighted/styled differently in the message.</t>
+          <t>Matching emojis should display based on search term.</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -3434,112 +3087,101 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>MSG_083</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Verify @all mention feature</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and one-on-one chat is open</t>
-        </is>
-      </c>
+          <t>MSG_069</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Verify @all not available in direct chat</t>
+          <t>Verify recent emojis section</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>1. Open one-on-one chat.
-2. Type "@all".</t>
+          <t>1. Send message with emoji.
+2. Open emoji picker again.
+3. Check recent section.</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>@all suggestion should not appear in direct/one-on-one chats.</t>
+          <t>Recently used emojis should appear in recent/frequently used section.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>MSG_084</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Verify @ mention feature</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and group chat is open</t>
-        </is>
-      </c>
+          <t>MSG_070</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n"/>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Verify typing @ shows member suggestions</t>
+          <t>Verify closing emoji picker</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>1. Open group chat.
-2. Type "@" in input field.</t>
+          <t>1. Open emoji picker.
+2. Click outside picker or close button.</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>List of group members should appear as suggestions.</t>
+          <t>Emoji picker should close.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>MSG_085</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="n"/>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n"/>
+          <t>MSG_071</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Verify Sticker feature</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Verify filtering members by name</t>
+          <t>Verify sticker button/tab is visible</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>1. Type "@Jo" in input field.
-2. Observe suggestions.</t>
+          <t>1. Open any chat conversation.
+2. Observe sticker option.</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Only members with names starting with "Jo" should appear (e.g., John).</t>
+          <t>Sticker button or tab should be visible (may be in emoji picker).</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -3551,7 +3193,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>MSG_086</t>
+          <t>MSG_072</t>
         </is>
       </c>
       <c r="B87" s="2" t="n"/>
@@ -3559,18 +3201,18 @@
       <c r="D87" s="2" t="n"/>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Verify selecting member from suggestions</t>
+          <t>Verify sticker picker opens</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>1. Type "@".
-2. Click on a member name.</t>
+          <t>1. Click on sticker button/tab.
+2. Observe sticker picker.</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Selected member's name should be added to message with @ prefix.</t>
+          <t>Sticker picker should open with sticker packs.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -3582,61 +3224,61 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>MSG_087</t>
+          <t>MSG_073</t>
         </is>
       </c>
       <c r="B88" s="2" t="n"/>
       <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n"/>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and sticker picker open</t>
+        </is>
+      </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Verify sending message with @ mention</t>
+          <t>Verify sticker packs display</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>1. Type message with @username.
-2. Send message.</t>
+          <t>1. Open sticker picker.
+2. Observe available sticker packs.</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Message should be sent; mentioned user should receive notification.</t>
+          <t>Different sticker packs should be visible and selectable.</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>MSG_088</t>
+          <t>MSG_074</t>
         </is>
       </c>
       <c r="B89" s="2" t="n"/>
       <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>User has been mentioned</t>
-        </is>
-      </c>
+      <c r="D89" s="2" t="n"/>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Verify @ mention notification</t>
+          <t>Verify sending sticker</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>1. Another user mentions you with @.
-2. Observe notification.</t>
+          <t>1. Open sticker picker.
+2. Click on any sticker.</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>User should receive notification for being mentioned.</t>
+          <t>Sticker should be sent immediately and appear in chat.</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -3648,26 +3290,30 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>MSG_089</t>
+          <t>MSG_075</t>
         </is>
       </c>
       <c r="B90" s="2" t="n"/>
       <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n"/>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>User has received sticker</t>
+        </is>
+      </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Verify @ mention highlight in message</t>
+          <t>Verify received sticker display</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>1. Receive message where you are mentioned.
-2. Observe message.</t>
+          <t>1. Receive a sticker from another user.
+2. Observe chat.</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Your @mention should be highlighted/styled differently.</t>
+          <t>Sticker should display properly in chat on left side.</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -3679,30 +3325,30 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>MSG_090</t>
+          <t>MSG_076</t>
         </is>
       </c>
       <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and group chat is open</t>
+          <t>User is logged in and sticker picker open</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple @ mentions in one message</t>
+          <t>Verify sticker pack switching</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>1. Type message with multiple @mentions.
-2. Send message.</t>
+          <t>1. Open sticker picker.
+2. Click on different sticker pack.</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>All mentioned users should receive notifications.</t>
+          <t>Selected sticker pack's stickers should display.</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -3712,40 +3358,19 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>MSG_091</t>
-        </is>
-      </c>
+      <c r="A92" s="2" t="n"/>
       <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="n"/>
       <c r="D92" s="2" t="n"/>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>Verify @ mention with profile picture in suggestions</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>1. Type "@" in input field.
-2. Observe suggestion list.</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>Member suggestions should show profile pictures alongside names.</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
+      <c r="E92" s="2" t="n"/>
+      <c r="F92" s="2" t="n"/>
+      <c r="G92" s="2" t="n"/>
+      <c r="H92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>MSG_092</t>
+          <t>MSG_077</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -3755,75 +3380,50 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Verify @ mention feature</t>
+          <t>Verify Sticker feature</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and group chat is open</t>
+          <t>User is logged in, no sticker packs available</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Verify @ with no matching members</t>
+          <t>Verify empty sticker state</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>1. Type "@xyz123" in input field.
-2. Observe suggestions.</t>
+          <t>1. Open sticker picker with no packs.
+2. Observe display.</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>No suggestions should appear or "No members found" message.</t>
+          <t>Empty state or option to download sticker packs should display.</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>MSG_093</t>
-        </is>
-      </c>
+      <c r="A94" s="2" t="n"/>
       <c r="B94" s="2" t="n"/>
       <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and one-on-one chat is open</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>Verify @ mention in direct chat</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>1. Open one-on-one chat.
-2. Type "@".</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>Only the other user should appear in suggestions (or feature disabled).</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
+      <c r="D94" s="2" t="n"/>
+      <c r="E94" s="2" t="n"/>
+      <c r="F94" s="2" t="n"/>
+      <c r="G94" s="2" t="n"/>
+      <c r="H94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>MSG_094</t>
+          <t>MSG_078</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -3833,29 +3433,28 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Verify Custom Message</t>
+          <t>Verify @all mention feature</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and chat is open</t>
+          <t>User is logged in and group chat is open</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Verify sending a custom message (poll)</t>
+          <t>Verify typing @all shows suggestion</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>1. Open a conversation.
-2. Create a poll via custom message option.
-3. Send.</t>
+          <t>1. Open group chat.
+2. Type "@all" in input field.</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Poll should be sent and display in chat with options for recipients to vote.</t>
+          <t>"@all" suggestion should appear to mention all group members.</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -3867,7 +3466,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>MSG_095</t>
+          <t>MSG_079</t>
         </is>
       </c>
       <c r="B96" s="2" t="n"/>
@@ -3875,30 +3474,30 @@
       <c r="D96" s="2" t="n"/>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Verify sending a custom message (meeting link)</t>
+          <t>Verify selecting @all mention</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>1. Open a conversation.
-2. Send a meeting/conference link as custom message.</t>
+          <t>1. Type "@all".
+2. Select @all from suggestions.</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Custom message with meeting link should display with appropriate formatting and join button.</t>
+          <t>"@all" should be added to message with special formatting.</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>MSG_096</t>
+          <t>MSG_080</t>
         </is>
       </c>
       <c r="B97" s="2" t="n"/>
@@ -3906,49 +3505,53 @@
       <c r="D97" s="2" t="n"/>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Verify sending a custom message (collaborative document)</t>
+          <t>Verify sending message with @all</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>1. Open a conversation.
-2. Share a collaborative document as custom message.</t>
+          <t>1. Type message with @all.
+2. Send message.</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Custom message should display with document preview and open/join action.</t>
+          <t>Message should be sent; all group members should receive notification.</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>MSG_097</t>
+          <t>MSG_081</t>
         </is>
       </c>
       <c r="B98" s="2" t="n"/>
       <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n"/>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>User has received @all mention</t>
+        </is>
+      </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Verify custom message renders correctly for receiver</t>
+          <t>Verify @all mention notification</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>1. Send a custom message from User A.
-2. Observe on User B's side.</t>
+          <t>1. Another user sends @all in group.
+2. Observe notification.</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Custom message should render correctly with all interactive elements on receiver's end.</t>
+          <t>User should receive notification for @all mention.</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -3960,7 +3563,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>MSG_098</t>
+          <t>MSG_082</t>
         </is>
       </c>
       <c r="B99" s="2" t="n"/>
@@ -3968,96 +3571,713 @@
       <c r="D99" s="2" t="n"/>
       <c r="E99" s="2" t="inlineStr">
         <is>
+          <t>Verify @all highlight in message</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>1. Receive message with @all.
+2. Observe message display.</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>"@all" should be highlighted/styled differently in the message.</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n"/>
+      <c r="B100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n"/>
+      <c r="E100" s="2" t="n"/>
+      <c r="F100" s="2" t="n"/>
+      <c r="G100" s="2" t="n"/>
+      <c r="H100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>MSG_083</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Verify @all mention feature</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and one-on-one chat is open</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Verify @all not available in direct chat</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>1. Open one-on-one chat.
+2. Type "@all".</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>@all suggestion should not appear in direct/one-on-one chats.</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n"/>
+      <c r="E102" s="2" t="n"/>
+      <c r="F102" s="2" t="n"/>
+      <c r="G102" s="2" t="n"/>
+      <c r="H102" s="2" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>MSG_084</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Verify @ mention feature</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and group chat is open</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Verify typing @ shows member suggestions</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>1. Open group chat.
+2. Type "@" in input field.</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>List of group members should appear as suggestions.</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>MSG_085</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Verify filtering members by name</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>1. Type "@Jo" in input field.
+2. Observe suggestions.</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Only members with names starting with "Jo" should appear (e.g., John).</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>MSG_086</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n"/>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Verify selecting member from suggestions</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>1. Type "@".
+2. Click on a member name.</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Selected member's name should be added to message with @ prefix.</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>MSG_087</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n"/>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Verify sending message with @ mention</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>1. Type message with @username.
+2. Send message.</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Message should be sent; mentioned user should receive notification.</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>MSG_088</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>User has been mentioned</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Verify @ mention notification</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>1. Another user mentions you with @.
+2. Observe notification.</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>User should receive notification for being mentioned.</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>MSG_089</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n"/>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Verify @ mention highlight in message</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>1. Receive message where you are mentioned.
+2. Observe message.</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Your @mention should be highlighted/styled differently.</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>MSG_090</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and group chat is open</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Verify multiple @ mentions in one message</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>1. Type message with multiple @mentions.
+2. Send message.</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>All mentioned users should receive notifications.</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>MSG_091</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n"/>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Verify @ mention with profile picture in suggestions</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>1. Type "@" in input field.
+2. Observe suggestion list.</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Member suggestions should show profile pictures alongside names.</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n"/>
+      <c r="B111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n"/>
+      <c r="E111" s="2" t="n"/>
+      <c r="F111" s="2" t="n"/>
+      <c r="G111" s="2" t="n"/>
+      <c r="H111" s="2" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>MSG_092</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Verify @ mention feature</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and group chat is open</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Verify @ with no matching members</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>1. Type "@xyz123" in input field.
+2. Observe suggestions.</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>No suggestions should appear or "No members found" message.</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>MSG_093</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and one-on-one chat is open</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Verify @ mention in direct chat</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>1. Open one-on-one chat.
+2. Type "@".</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Only the other user should appear in suggestions (or feature disabled).</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n"/>
+      <c r="B114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n"/>
+      <c r="E114" s="2" t="n"/>
+      <c r="F114" s="2" t="n"/>
+      <c r="G114" s="2" t="n"/>
+      <c r="H114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>MSG_094</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Verify Custom Message</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Verify sending a custom message (poll)</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a conversation.
+2. Create a poll via custom message option.
+3. Send.</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Poll should be sent and display in chat with options for recipients to vote.</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>MSG_095</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n"/>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Verify sending a custom message (meeting link)</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a conversation.
+2. Send a meeting/conference link as custom message.</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Custom message with meeting link should display with appropriate formatting and join button.</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>MSG_096</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n"/>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Verify sending a custom message (collaborative document)</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a conversation.
+2. Share a collaborative document as custom message.</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Custom message should display with document preview and open/join action.</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>MSG_097</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n"/>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Verify custom message renders correctly for receiver</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a custom message from User A.
+2. Observe on User B's side.</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Custom message should render correctly with all interactive elements on receiver's end.</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>MSG_098</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n"/>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
           <t>Verify custom message in group chat</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>1. Open a group conversation.
 2. Send a custom message.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>Custom message should display correctly for all group members.</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n"/>
+      <c r="B120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n"/>
+      <c r="E120" s="2" t="n"/>
+      <c r="F120" s="2" t="n"/>
+      <c r="G120" s="2" t="n"/>
+      <c r="H120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>MSG_099</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t>Verify Custom Message</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Verify custom message fails without network</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Try to send a custom message.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>Error message should display or message should queue with retry option.</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n"/>
+      <c r="B122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n"/>
+      <c r="E122" s="2" t="n"/>
+      <c r="F122" s="2" t="n"/>
+      <c r="G122" s="2" t="n"/>
+      <c r="H122" s="2" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>MSG_100</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
         <is>
           <t>Verify Audio Message</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Verify sending an audio file attachment</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>1. Open a conversation.
 2. Click attach.
@@ -4065,125 +4285,125 @@
 4. Send.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>Audio file should upload and display with audio player, file name, and duration.</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>MSG_101</t>
         </is>
       </c>
-      <c r="B102" s="2" t="n"/>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n"/>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="B124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n"/>
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Verify audio message playback by sender</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>1. Send an audio message.
 2. Click play on the audio player.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>Audio should play with progress bar, play/pause button, and duration indicator.</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>MSG_102</t>
         </is>
       </c>
-      <c r="B103" s="2" t="n"/>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n"/>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="B125" s="2" t="n"/>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" s="2" t="n"/>
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Verify audio message playback by receiver</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>1. Receive an audio message.
 2. Click play.</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>Audio should download (if needed) and play correctly with player controls.</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>MSG_103</t>
         </is>
       </c>
-      <c r="B104" s="2" t="n"/>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n"/>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="B126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n"/>
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Verify audio message shows duration</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>1. Send/receive an audio message.
 2. Observe audio player.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>Audio duration should display (e.g., '0:45', '2:30').</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>MSG_104</t>
         </is>
       </c>
-      <c r="B105" s="2" t="n"/>
-      <c r="C105" s="2" t="n"/>
-      <c r="D105" s="2" t="n"/>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="B127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n"/>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Verify sending recorded audio message</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>1. Open a conversation.
 2. Press and hold record button.
@@ -4191,154 +4411,164 @@
 4. Release to send.</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>Recorded audio should be sent and display with audio player in chat.</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>MSG_105</t>
         </is>
       </c>
-      <c r="B106" s="2" t="n"/>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n"/>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="B128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n"/>
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Verify audio message in group chat</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>1. Open a group conversation.
 2. Send an audio message.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>Audio message should display correctly for all group members with sender info.</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n"/>
+      <c r="B129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n"/>
+      <c r="E129" s="2" t="n"/>
+      <c r="F129" s="2" t="n"/>
+      <c r="G129" s="2" t="n"/>
+      <c r="H129" s="2" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>MSG_106</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
         <is>
           <t>Verify Audio Message</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Verify large audio file exceeding size limit</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>1. Try to send an audio file exceeding the size limit.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>Error message should display indicating file size limit exceeded.</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>MSG_107</t>
         </is>
       </c>
-      <c r="B108" s="2" t="n"/>
-      <c r="C108" s="2" t="n"/>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Verify audio message fails without network</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Try to send an audio message.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>Error message should display or upload should queue with retry option.</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>MSG_108</t>
         </is>
       </c>
-      <c r="B109" s="2" t="n"/>
-      <c r="C109" s="2" t="n"/>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B132" s="2" t="n"/>
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Verify unsupported audio format</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>1. Try to send an unsupported audio file format.</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>Error message should display or file should be rejected.</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
@@ -4908,7 +5138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5100,69 +5330,79 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>MSG_123</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Edge Case: Send Message</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending message with zero-width characters</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1. Send a message containing only zero-width unicode characters.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Message should be blocked or displayed as empty. No invisible messages.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Medium / High</t>
-        </is>
-      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>MSG_124</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
+          <t>MSG_123</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case: Send Message</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>Verify sending message with zero-width characters</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message containing only zero-width unicode characters.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Message should be blocked or displayed as empty. No invisible messages.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>MSG_124</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>Verify sending corrupted media file</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1. Rename a .txt file to .jpg.
 2. Try to send as image.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>App should detect invalid file and show error. Should not crash.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
@@ -5180,7 +5420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5308,98 +5548,118 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>MSG_127</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending text exceeding max character limit</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to send a message exceeding the max limit.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Should be blocked at input or rejected by server with error.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>MSG_128</t>
+          <t>MSG_127</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Verify sending media at minimum file size (1 byte)</t>
+          <t>Verify sending text exceeding max character limit</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1. Send a 1-byte file.</t>
+          <t>1. Try to send a message exceeding the max limit.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>File should either send or be rejected as too small. No crash.</t>
+          <t>Should be blocked at input or rejected by server with error.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>MSG_129</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="n"/>
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>MSG_128</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Verify sending media at minimum file size (1 byte)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a 1-byte file.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>File should either send or be rejected as too small. No crash.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>MSG_129</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Verify sending media at exactly max file size</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1. Send a file at exactly the maximum allowed size.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>File should upload and send successfully.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>

--- a/Send_Message/Send_Message_Test_Cases.xlsx
+++ b/Send_Message/Send_Message_Test_Cases.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H132"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -637,51 +637,72 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>MSG_007</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Verify Send button</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Verify send button is visible</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1. Open any chat conversation.
+2. Observe send button next to input field.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Send button (arrow/paper plane icon) should be visible.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>MSG_005</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Verify Message Input field</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>MSG_008</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Verify empty message cannot be sent</t>
+          <t>Verify send button enabled when text entered</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
-2. Leave input field empty.
-3. Click send button.</t>
+2. Type a message.
+3. Observe send button.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Send button should be disabled or message should not be sent.</t>
+          <t>Send button should become enabled/highlighted when text is entered.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -693,49 +714,75 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>MSG_006</t>
+          <t>MSG_009</t>
         </is>
       </c>
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and message typed</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Verify message with only spaces</t>
+          <t>Verify send button click sends message</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Type only spaces.
-3. Click send button.</t>
+          <t>1. Type a message.
+2. Click send button.
+3. Observe chat.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Message should not be sent; spaces-only input should be treated as empty.</t>
+          <t>Message should be sent and appear in chat with sent status.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>MSG_010</t>
+        </is>
+      </c>
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Verify send button visual feedback on click</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1. Type a message.
+2. Click send button.
+3. Observe button.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Send button should show click feedback (color change, animation).</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>MSG_007</t>
+          <t>MSG_012</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -745,7 +792,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Verify Send button</t>
+          <t>Verify Text message sending</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -755,18 +802,19 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Verify send button is visible</t>
+          <t>Verify sending simple text message</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
-2. Observe send button next to input field.</t>
+2. Type "Hello".
+3. Click send.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Send button (arrow/paper plane icon) should be visible.</t>
+          <t>Message "Hello" should appear in chat on right side (sent).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -778,7 +826,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>MSG_008</t>
+          <t>MSG_013</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -786,67 +834,63 @@
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Verify send button enabled when text entered</t>
+          <t>Verify sending long text message</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
-2. Type a message.
-3. Observe send button.</t>
+2. Type a 500+ character message.
+3. Click send.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Send button should become enabled/highlighted when text is entered.</t>
+          <t>Long message should be sent successfully and display properly.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>MSG_009</t>
+          <t>MSG_014</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and message typed</t>
-        </is>
-      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Verify send button click sends message</t>
+          <t>Verify sending message with special characters</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1. Type a message.
-2. Click send button.
-3. Observe chat.</t>
+          <t>1. Open any chat conversation.
+2. Type "Hello @#$%^&amp;*()!".
+3. Click send.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Message should be sent and appear in chat with sent status.</t>
+          <t>Message with special characters should be sent and displayed correctly.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>MSG_010</t>
+          <t>MSG_015</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -854,139 +898,169 @@
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify send button visual feedback on click</t>
+          <t>Verify sending message with emojis</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1. Type a message.
-2. Click send button.
-3. Observe button.</t>
+          <t>1. Open any chat conversation.
+2. Type "Hello 😀🎉👍".
+3. Click send.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Send button should show click feedback (color change, animation).</t>
+          <t>Message with emojis should be sent and emojis displayed correctly.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>MSG_016</t>
+        </is>
+      </c>
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Verify sending message with numbers</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1. Open any chat conversation.
+2. Type "Order #12345".
+3. Click send.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Message with numbers should be sent correctly.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>MSG_011</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Verify Send button</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>MSG_017</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Verify send button disabled when empty</t>
+          <t>Verify sending message with URL</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
-2. Leave input field empty.
-3. Observe send button.</t>
+2. Type "Check https://example.com".
+3. Click send.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Send button should be disabled or grayed out.</t>
+          <t>Message should be sent; URL may be clickable/highlighted.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n"/>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>MSG_020</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Verify Sent message display</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>User has sent a message</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Verify sent message alignment</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message.
+2. Observe message position in chat.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Sent message should appear on the right side of chat window.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>MSG_012</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Verify Text message sending</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>MSG_021</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Verify sending simple text message</t>
+          <t>Verify sent message bubble color</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Type "Hello".
-3. Click send.</t>
+          <t>1. Send a message.
+2. Observe message bubble.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Message "Hello" should appear in chat on right side (sent).</t>
+          <t>Sent message should have distinct bubble color (e.g., blue/purple).</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>MSG_013</t>
+          <t>MSG_022</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
@@ -994,19 +1068,18 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify sending long text message</t>
+          <t>Verify sent message timestamp</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Type a 500+ character message.
-3. Click send.</t>
+          <t>1. Send a message.
+2. Observe timestamp.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Long message should be sent successfully and display properly.</t>
+          <t>Timestamp should display below or next to sent message.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1018,7 +1091,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>MSG_014</t>
+          <t>MSG_023</t>
         </is>
       </c>
       <c r="B19" s="2" t="n"/>
@@ -1026,63 +1099,73 @@
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify sending message with special characters</t>
+          <t>Verify sent message status indicator</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Type "Hello @#$%^&amp;*()!".
-3. Click send.</t>
+          <t>1. Send a message.
+2. Observe status indicator.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Message with special characters should be sent and displayed correctly.</t>
+          <t>Status indicator should show (single tick = sent, double tick = delivered, blue tick = read).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>MSG_015</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
+          <t>MSG_024</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Verify Received message display</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>User has received a message</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify sending message with emojis</t>
+          <t>Verify received message alignment</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Type "Hello 😀🎉👍".
-3. Click send.</t>
+          <t>1. Receive a message from another user.
+2. Observe message position.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Message with emojis should be sent and emojis displayed correctly.</t>
+          <t>Received message should appear on the left side of chat window.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>MSG_016</t>
+          <t>MSG_025</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
@@ -1090,31 +1173,30 @@
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Verify sending message with numbers</t>
+          <t>Verify received message bubble color</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Type "Order #12345".
-3. Click send.</t>
+          <t>1. Receive a message.
+2. Observe message bubble.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Message with numbers should be sent correctly.</t>
+          <t>Received message should have different bubble color than sent (e.g., gray/white).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MSG_017</t>
+          <t>MSG_026</t>
         </is>
       </c>
       <c r="B22" s="2" t="n"/>
@@ -1122,19 +1204,18 @@
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Verify sending message with URL</t>
+          <t>Verify received message sender info</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Type "Check https://example.com".
-3. Click send.</t>
+          <t>1. Receive a message in group chat.
+2. Observe sender info.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Message should be sent; URL may be clickable/highlighted.</t>
+          <t>Sender name and/or avatar should display with received message in group chats.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1144,51 +1225,72 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>MSG_027</t>
+        </is>
+      </c>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Verify received message timestamp</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1. Receive a message.
+2. Observe timestamp.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp should display below or next to received message.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MSG_018</t>
+          <t>MSG_028</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Verify Text message sending</t>
+          <t>Verify Enter key to send</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, network disconnected</t>
+          <t>User is logged in and message typed</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verify message sending fails without network</t>
+          <t>Verify Enter key sends message</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1. Disconnect network.
-2. Type a message.
-3. Click send.</t>
+          <t>1. Type a message.
+2. Press Enter key.
+3. Observe chat.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Error indicator should show; message should be queued or show failed status.</t>
+          <t>Message should be sent when Enter key is pressed.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1200,52 +1302,83 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>MSG_019</t>
+          <t>MSG_029</t>
         </is>
       </c>
       <c r="B25" s="2" t="n"/>
       <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Verify extremely long message handling</t>
+          <t>Verify Shift+Enter creates new line</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1. Type a 10000+ character message.
-2. Click send.</t>
+          <t>1. Type a message.
+2. Press Shift+Enter.
+3. Continue typing.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Application should handle gracefully; either send or show character limit warning.</t>
+          <t>New line should be created; message should not be sent.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Low / Medium</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>MSG_031</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Verify Message input clear after send</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>User has sent a message</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Verify input field clears after sending</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1. Type a message.
+2. Click send.
+3. Observe input field.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Input field should be cleared after message is sent successfully.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>MSG_020</t>
+          <t>MSG_032</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1255,28 +1388,28 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Verify Sent message display</t>
+          <t>Verify Real-time message delivery</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>User has sent a message</t>
+          <t>Two users are in same chat</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Verify sent message alignment</t>
+          <t>Verify message appears instantly for recipient</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1. Send a message.
-2. Observe message position in chat.</t>
+          <t>1. User A sends message.
+2. User B observes chat.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Sent message should appear on the right side of chat window.</t>
+          <t>Message should appear in User B's chat within seconds without refresh.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1288,7 +1421,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>MSG_021</t>
+          <t>MSG_033</t>
         </is>
       </c>
       <c r="B28" s="2" t="n"/>
@@ -1296,18 +1429,18 @@
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Verify sent message bubble color</t>
+          <t>Verify typing indicator</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1. Send a message.
-2. Observe message bubble.</t>
+          <t>1. User A starts typing.
+2. User B observes chat.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Sent message should have distinct bubble color (e.g., blue/purple).</t>
+          <t>Typing indicator should appear for User B (e.g., "User A is typing...").</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1319,38 +1452,50 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>MSG_022</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
+          <t>MSG_034</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Verify Message scroll behavior</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>User is in chat with many messages</t>
+        </is>
+      </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Verify sent message timestamp</t>
+          <t>Verify auto-scroll to new message</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1. Send a message.
-2. Observe timestamp.</t>
+          <t>1. Be at bottom of chat.
+2. Send or receive new message.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Timestamp should display below or next to sent message.</t>
+          <t>Chat should auto-scroll to show the new message.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>MSG_023</t>
+          <t>MSG_035</t>
         </is>
       </c>
       <c r="B30" s="2" t="n"/>
@@ -1358,104 +1503,108 @@
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Verify sent message status indicator</t>
+          <t>Verify scroll up to view history</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1. Send a message.
-2. Observe status indicator.</t>
+          <t>1. Open chat with many messages.
+2. Scroll up.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Status indicator should show (single tick = sent, double tick = delivered, blue tick = read).</t>
+          <t>Older messages should load; scrolling should be smooth.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>MSG_024</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Verify Received message display</t>
-        </is>
-      </c>
+          <t>MSG_036</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>User has received a message</t>
+          <t>User is scrolled up in chat</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Verify received message alignment</t>
+          <t>Verify new message notification when scrolled up</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1. Receive a message from another user.
-2. Observe message position.</t>
+          <t>1. Scroll up in chat.
+2. Receive new message.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Received message should appear on the left side of chat window.</t>
+          <t>Notification or "New message" button should appear to scroll to bottom.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>MSG_025</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
+          <t>MSG_037</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Verify Attachment button</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Verify received message bubble color</t>
+          <t>Verify attachment button is visible</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1. Receive a message.
-2. Observe message bubble.</t>
+          <t>1. Open any chat conversation.
+2. Observe attachment button.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Received message should have different bubble color than sent (e.g., gray/white).</t>
+          <t>Attachment button (paperclip/+ icon) should be visible near input field.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>MSG_026</t>
+          <t>MSG_038</t>
         </is>
       </c>
       <c r="B33" s="2" t="n"/>
@@ -1463,49 +1612,61 @@
       <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Verify received message sender info</t>
+          <t>Verify attachment button click opens options</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1. Receive a message in group chat.
-2. Observe sender info.</t>
+          <t>1. Open any chat conversation.
+2. Click attachment button.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Sender name and/or avatar should display with received message in group chats.</t>
+          <t>Attachment options should appear (image, file, camera, etc.).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>MSG_027</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
+          <t>MSG_039</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Verify Emoji button</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Verify received message timestamp</t>
+          <t>Verify emoji button is visible</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1. Receive a message.
-2. Observe timestamp.</t>
+          <t>1. Open any chat conversation.
+2. Observe emoji button.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Timestamp should display below or next to received message.</t>
+          <t>Emoji button (smiley icon) should be visible near input field.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1517,71 +1678,61 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MSG_028</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Verify Enter key to send</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and message typed</t>
-        </is>
-      </c>
+          <t>MSG_040</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Verify Enter key sends message</t>
+          <t>Verify emoji button click opens picker</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1. Type a message.
-2. Press Enter key.
-3. Observe chat.</t>
+          <t>1. Open any chat conversation.
+2. Click emoji button.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Message should be sent when Enter key is pressed.</t>
+          <t>Emoji picker should open with emoji categories.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>MSG_029</t>
+          <t>MSG_041</t>
         </is>
       </c>
       <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and emoji picker open</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Verify Shift+Enter creates new line</t>
+          <t>Verify selecting emoji adds to input</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1. Type a message.
-2. Press Shift+Enter.
-3. Continue typing.</t>
+          <t>1. Open emoji picker.
+2. Click on an emoji.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>New line should be created; message should not be sent.</t>
+          <t>Selected emoji should be added to message input field.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1591,104 +1742,147 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>MSG_042</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Verify UI responsiveness</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Verify message input on desktop</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>1. Open application on desktop.
+2. Open chat.
+3. Resize browser.</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Message input and send button should remain functional and visible.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>MSG_030</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Verify Enter key to send</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and input is empty</t>
-        </is>
-      </c>
+          <t>MSG_043</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Verify Enter key with empty input</t>
+          <t>Verify message input on mobile</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1. Leave input field empty.
-2. Press Enter key.</t>
+          <t>1. Open application on mobile.
+2. Open chat.
+3. Check keyboard interaction.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Nothing should happen; empty message should not be sent.</t>
+          <t>Input field should work with mobile keyboard; send button should be accessible.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n"/>
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>MSG_046</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Verify Attachment feature</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Verify attachment icon is visible</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>1. Open any chat conversation.
+2. Observe attachment icon near input field.</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Attachment icon (paperclip/+ icon) should be visible.</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>MSG_031</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Verify Message input clear after send</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>User has sent a message</t>
-        </is>
-      </c>
+          <t>MSG_047</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Verify input field clears after sending</t>
+          <t>Verify attachment options menu</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1. Type a message.
-2. Click send.
-3. Observe input field.</t>
+          <t>1. Click on attachment icon.
+2. Observe options menu.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Input field should be cleared after message is sent successfully.</t>
+          <t>Options menu should display (Image, Video, Document, Camera, etc.).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1700,38 +1894,32 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>MSG_032</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Verify Real-time message delivery</t>
-        </is>
-      </c>
+          <t>MSG_048</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Two users are in same chat</t>
+          <t>User is logged in and attachment menu open</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Verify message appears instantly for recipient</t>
+          <t>Verify sending image attachment</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1. User A sends message.
-2. User B observes chat.</t>
+          <t>1. Click attachment icon.
+2. Select Image option.
+3. Choose an image.
+4. Send.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Message should appear in User B's chat within seconds without refresh.</t>
+          <t>Image should be uploaded and sent; preview should display in chat.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -1743,7 +1931,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>MSG_033</t>
+          <t>MSG_049</t>
         </is>
       </c>
       <c r="B42" s="2" t="n"/>
@@ -1751,73 +1939,65 @@
       <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Verify typing indicator</t>
+          <t>Verify sending document attachment</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1. User A starts typing.
-2. User B observes chat.</t>
+          <t>1. Click attachment icon.
+2. Select Document option.
+3. Choose a file.
+4. Send.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Typing indicator should appear for User B (e.g., "User A is typing...").</t>
+          <t>Document should be uploaded and sent; file icon with name should display.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>MSG_034</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Verify Message scroll behavior</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>User is in chat with many messages</t>
-        </is>
-      </c>
+          <t>MSG_050</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Verify auto-scroll to new message</t>
+          <t>Verify sending video attachment</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1. Be at bottom of chat.
-2. Send or receive new message.</t>
+          <t>1. Click attachment icon.
+2. Select Video option.
+3. Choose a video.
+4. Send.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Chat should auto-scroll to show the new message.</t>
+          <t>Video should be uploaded and sent; video thumbnail should display.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>MSG_035</t>
+          <t>MSG_051</t>
         </is>
       </c>
       <c r="B44" s="2" t="n"/>
@@ -1825,18 +2005,19 @@
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Verify scroll up to view history</t>
+          <t>Verify attachment upload progress</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1. Open chat with many messages.
-2. Scroll up.</t>
+          <t>1. Click attachment icon.
+2. Select a large file.
+3. Observe upload.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Older messages should load; scrolling should be smooth.</t>
+          <t>Upload progress indicator should display during file upload.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -1848,73 +2029,69 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>MSG_036</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n"/>
-      <c r="C45" s="2" t="n"/>
+          <t>MSG_055</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Verify Voice Recording feature</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>User is scrolled up in chat</t>
+          <t>User is logged in and chat is open</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Verify new message notification when scrolled up</t>
+          <t>Verify recording button is visible</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1. Scroll up in chat.
-2. Receive new message.</t>
+          <t>1. Open any chat conversation.
+2. Observe microphone/recording icon.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Notification or "New message" button should appear to scroll to bottom.</t>
+          <t>Recording button (microphone icon) should be visible near input field.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>MSG_037</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Verify Attachment button</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>MSG_056</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Verify attachment button is visible</t>
+          <t>Verify recording starts on button press</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Observe attachment button.</t>
+          <t>1. Press and hold recording button.
+2. Observe recording indicator.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Attachment button (paperclip/+ icon) should be visible near input field.</t>
+          <t>Recording should start; timer and waveform indicator should display.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -1926,81 +2103,74 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MSG_038</t>
+          <t>MSG_057</t>
         </is>
       </c>
       <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n"/>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>User is recording voice message</t>
+        </is>
+      </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Verify attachment button click opens options</t>
+          <t>Verify recording timer display</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Click attachment button.</t>
+          <t>1. Start recording.
+2. Observe timer.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Attachment options should appear (image, file, camera, etc.).</t>
+          <t>Recording duration timer should display and increment.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>MSG_039</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Verify Emoji button</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>MSG_058</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Verify emoji button is visible</t>
+          <t>Verify sending voice message</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Observe emoji button.</t>
+          <t>1. Record a voice message.
+2. Release button or click send.
+3. Observe chat.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Emoji button (smiley icon) should be visible near input field.</t>
+          <t>Voice message should be sent and appear in chat with play button.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>MSG_040</t>
+          <t>MSG_059</t>
         </is>
       </c>
       <c r="B49" s="2" t="n"/>
@@ -2008,65 +2178,65 @@
       <c r="D49" s="2" t="n"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Verify emoji button click opens picker</t>
+          <t>Verify cancel recording</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Click emoji button.</t>
+          <t>1. Start recording.
+2. Slide to cancel or click cancel button.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Emoji picker should open with emoji categories.</t>
+          <t>Recording should be cancelled; no message should be sent.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>MSG_041</t>
+          <t>MSG_060</t>
         </is>
       </c>
       <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and emoji picker open</t>
+          <t>User has received voice message</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Verify selecting emoji adds to input</t>
+          <t>Verify playing received voice message</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1. Open emoji picker.
-2. Click on an emoji.</t>
+          <t>1. Receive a voice message.
+2. Click play button.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Selected emoji should be added to message input field.</t>
+          <t>Voice message should play; progress indicator should show.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>MSG_042</t>
+          <t>MSG_063</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2076,41 +2246,40 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Verify UI responsiveness</t>
+          <t>Verify Emoji feature</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>User is logged in</t>
+          <t>User is logged in and chat is open</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Verify message input on desktop</t>
+          <t>Verify emoji button is visible</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>1. Open application on desktop.
-2. Open chat.
-3. Resize browser.</t>
+          <t>1. Open any chat conversation.
+2. Observe emoji button.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Message input and send button should remain functional and visible.</t>
+          <t>Emoji button (smiley face icon) should be visible near input field.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>MSG_043</t>
+          <t>MSG_064</t>
         </is>
       </c>
       <c r="B52" s="2" t="n"/>
@@ -2118,174 +2287,191 @@
       <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Verify message input on mobile</t>
+          <t>Verify emoji picker opens</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1. Open application on mobile.
-2. Open chat.
-3. Check keyboard interaction.</t>
+          <t>1. Click on emoji button.
+2. Observe emoji picker.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Input field should work with mobile keyboard; send button should be accessible.</t>
+          <t>Emoji picker should open with categories (Smileys, Animals, Food, etc.).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n"/>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>MSG_065</t>
+        </is>
+      </c>
       <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="n"/>
-      <c r="F53" s="2" t="n"/>
-      <c r="G53" s="2" t="n"/>
-      <c r="H53" s="2" t="n"/>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and emoji picker open</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Verify emoji categories navigation</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1. Open emoji picker.
+2. Click on different category tabs.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Different emoji categories should display when tabs are clicked.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>MSG_044</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Verify Message loading</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, slow network</t>
-        </is>
-      </c>
+          <t>MSG_066</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Verify message sending with slow network</t>
+          <t>Verify selecting emoji adds to input</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1. Simulate slow network.
-2. Send a message.
-3. Observe behavior.</t>
+          <t>1. Open emoji picker.
+2. Click on any emoji.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Loading indicator should show; message should eventually send or show retry option.</t>
+          <t>Selected emoji should be added to message input field at cursor position.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>MSG_045</t>
+          <t>MSG_067</t>
         </is>
       </c>
       <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network error</t>
-        </is>
-      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Verify message retry on failure</t>
+          <t>Verify multiple emoji selection</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1. Send message during network error.
-2. Observe failed message.
-3. Click retry.</t>
+          <t>1. Open emoji picker.
+2. Click multiple emojis.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Retry option should be available; message should resend on retry.</t>
+          <t>All selected emojis should be added to input field.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n"/>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>MSG_068</t>
+        </is>
+      </c>
       <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="n"/>
-      <c r="G56" s="2" t="n"/>
-      <c r="H56" s="2" t="n"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Verify emoji search functionality</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>1. Open emoji picker.
+2. Type in emoji search field.
+3. Observe results.</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Matching emojis should display based on search term.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>MSG_046</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Verify Attachment feature</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>MSG_069</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Verify attachment icon is visible</t>
+          <t>Verify recent emojis section</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Observe attachment icon near input field.</t>
+          <t>1. Send message with emoji.
+2. Open emoji picker again.
+3. Check recent section.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Attachment icon (paperclip/+ icon) should be visible.</t>
+          <t>Recently used emojis should appear in recent/frequently used section.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>MSG_047</t>
+          <t>MSG_070</t>
         </is>
       </c>
       <c r="B58" s="2" t="n"/>
@@ -2293,55 +2479,61 @@
       <c r="D58" s="2" t="n"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Verify attachment options menu</t>
+          <t>Verify closing emoji picker</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>1. Click on attachment icon.
-2. Observe options menu.</t>
+          <t>1. Open emoji picker.
+2. Click outside picker or close button.</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Options menu should display (Image, Video, Document, Camera, etc.).</t>
+          <t>Emoji picker should close.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>MSG_048</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="n"/>
-      <c r="C59" s="2" t="n"/>
+          <t>MSG_071</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Verify Sticker feature</t>
+        </is>
+      </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and attachment menu open</t>
+          <t>User is logged in and chat is open</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Verify sending image attachment</t>
+          <t>Verify sticker button/tab is visible</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>1. Click attachment icon.
-2. Select Image option.
-3. Choose an image.
-4. Send.</t>
+          <t>1. Open any chat conversation.
+2. Observe sticker option.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Image should be uploaded and sent; preview should display in chat.</t>
+          <t>Sticker button or tab should be visible (may be in emoji picker).</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2353,7 +2545,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>MSG_049</t>
+          <t>MSG_072</t>
         </is>
       </c>
       <c r="B60" s="2" t="n"/>
@@ -2361,20 +2553,18 @@
       <c r="D60" s="2" t="n"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Verify sending document attachment</t>
+          <t>Verify sticker picker opens</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1. Click attachment icon.
-2. Select Document option.
-3. Choose a file.
-4. Send.</t>
+          <t>1. Click on sticker button/tab.
+2. Observe sticker picker.</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Document should be uploaded and sent; file icon with name should display.</t>
+          <t>Sticker picker should open with sticker packs.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2386,28 +2576,30 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>MSG_050</t>
+          <t>MSG_073</t>
         </is>
       </c>
       <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n"/>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and sticker picker open</t>
+        </is>
+      </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Verify sending video attachment</t>
+          <t>Verify sticker packs display</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>1. Click attachment icon.
-2. Select Video option.
-3. Choose a video.
-4. Send.</t>
+          <t>1. Open sticker picker.
+2. Observe available sticker packs.</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Video should be uploaded and sent; video thumbnail should display.</t>
+          <t>Different sticker packs should be visible and selectable.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2419,7 +2611,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>MSG_051</t>
+          <t>MSG_074</t>
         </is>
       </c>
       <c r="B62" s="2" t="n"/>
@@ -2427,72 +2619,88 @@
       <c r="D62" s="2" t="n"/>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Verify attachment upload progress</t>
+          <t>Verify sending sticker</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>1. Click attachment icon.
-2. Select a large file.
-3. Observe upload.</t>
+          <t>1. Open sticker picker.
+2. Click on any sticker.</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Upload progress indicator should display during file upload.</t>
+          <t>Sticker should be sent immediately and appear in chat.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n"/>
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>MSG_075</t>
+        </is>
+      </c>
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n"/>
-      <c r="E63" s="2" t="n"/>
-      <c r="F63" s="2" t="n"/>
-      <c r="G63" s="2" t="n"/>
-      <c r="H63" s="2" t="n"/>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>User has received sticker</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Verify received sticker display</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>1. Receive a sticker from another user.
+2. Observe chat.</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Sticker should display properly in chat on left side.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>MSG_052</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Verify Attachment feature</t>
-        </is>
-      </c>
+          <t>MSG_076</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and chat is open</t>
+          <t>User is logged in and sticker picker open</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Verify unsupported file type handling</t>
+          <t>Verify sticker pack switching</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>1. Click attachment icon.
-2. Try to select unsupported file type.</t>
+          <t>1. Open sticker picker.
+2. Click on different sticker pack.</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Error message should display or file should not be selectable.</t>
+          <t>Selected sticker pack's stickers should display.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -2504,61 +2712,69 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>MSG_053</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="n"/>
-      <c r="C65" s="2" t="n"/>
-      <c r="D65" s="2" t="n"/>
+          <t>MSG_078</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Verify @all mention feature</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and group chat is open</t>
+        </is>
+      </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Verify file size limit handling</t>
+          <t>Verify typing @all shows suggestion</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>1. Click attachment icon.
-2. Select file exceeding size limit.</t>
+          <t>1. Open group chat.
+2. Type "@all" in input field.</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Error message should display indicating file size limit exceeded.</t>
+          <t>"@all" suggestion should appear to mention all group members.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>MSG_054</t>
+          <t>MSG_079</t>
         </is>
       </c>
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network error</t>
-        </is>
-      </c>
+      <c r="D66" s="2" t="n"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Verify attachment upload failure handling</t>
+          <t>Verify selecting @all mention</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>1. Disconnect network.
-2. Try to send attachment.</t>
+          <t>1. Type "@all".
+2. Select @all from suggestions.</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Error message should display; retry option should be available.</t>
+          <t>"@all" should be added to message with special formatting.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -2568,50 +2784,63 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>MSG_080</t>
+        </is>
+      </c>
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n"/>
-      <c r="E67" s="2" t="n"/>
-      <c r="F67" s="2" t="n"/>
-      <c r="G67" s="2" t="n"/>
-      <c r="H67" s="2" t="n"/>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Verify sending message with @all</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>1. Type message with @all.
+2. Send message.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Message should be sent; all group members should receive notification.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>MSG_055</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Verify Voice Recording feature</t>
-        </is>
-      </c>
+          <t>MSG_081</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and chat is open</t>
+          <t>User has received @all mention</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Verify recording button is visible</t>
+          <t>Verify @all mention notification</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Observe microphone/recording icon.</t>
+          <t>1. Another user sends @all in group.
+2. Observe notification.</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Recording button (microphone icon) should be visible near input field.</t>
+          <t>User should receive notification for @all mention.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -2623,7 +2852,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>MSG_056</t>
+          <t>MSG_082</t>
         </is>
       </c>
       <c r="B69" s="2" t="n"/>
@@ -2631,65 +2860,73 @@
       <c r="D69" s="2" t="n"/>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Verify recording starts on button press</t>
+          <t>Verify @all highlight in message</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>1. Press and hold recording button.
-2. Observe recording indicator.</t>
+          <t>1. Receive message with @all.
+2. Observe message display.</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Recording should start; timer and waveform indicator should display.</t>
+          <t>"@all" should be highlighted/styled differently in the message.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>MSG_057</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="n"/>
-      <c r="C70" s="2" t="n"/>
+          <t>MSG_084</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Verify @ mention feature</t>
+        </is>
+      </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>User is recording voice message</t>
+          <t>User is logged in and group chat is open</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Verify recording timer display</t>
+          <t>Verify typing @ shows member suggestions</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>1. Start recording.
-2. Observe timer.</t>
+          <t>1. Open group chat.
+2. Type "@" in input field.</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Recording duration timer should display and increment.</t>
+          <t>List of group members should appear as suggestions.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>MSG_058</t>
+          <t>MSG_085</t>
         </is>
       </c>
       <c r="B71" s="2" t="n"/>
@@ -2697,19 +2934,18 @@
       <c r="D71" s="2" t="n"/>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Verify sending voice message</t>
+          <t>Verify filtering members by name</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>1. Record a voice message.
-2. Release button or click send.
-3. Observe chat.</t>
+          <t>1. Type "@Jo" in input field.
+2. Observe suggestions.</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Voice message should be sent and appear in chat with play button.</t>
+          <t>Only members with names starting with "Jo" should appear (e.g., John).</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -2721,7 +2957,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>MSG_059</t>
+          <t>MSG_086</t>
         </is>
       </c>
       <c r="B72" s="2" t="n"/>
@@ -2729,53 +2965,49 @@
       <c r="D72" s="2" t="n"/>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Verify cancel recording</t>
+          <t>Verify selecting member from suggestions</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>1. Start recording.
-2. Slide to cancel or click cancel button.</t>
+          <t>1. Type "@".
+2. Click on a member name.</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Recording should be cancelled; no message should be sent.</t>
+          <t>Selected member's name should be added to message with @ prefix.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>MSG_060</t>
+          <t>MSG_087</t>
         </is>
       </c>
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>User has received voice message</t>
-        </is>
-      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Verify playing received voice message</t>
+          <t>Verify sending message with @ mention</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>1. Receive a voice message.
-2. Click play button.</t>
+          <t>1. Type message with @username.
+2. Send message.</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Voice message should play; progress indicator should show.</t>
+          <t>Message should be sent; mentioned user should receive notification.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -2785,106 +3017,141 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n"/>
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>MSG_088</t>
+        </is>
+      </c>
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n"/>
-      <c r="E74" s="2" t="n"/>
-      <c r="F74" s="2" t="n"/>
-      <c r="G74" s="2" t="n"/>
-      <c r="H74" s="2" t="n"/>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>User has been mentioned</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Verify @ mention notification</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>1. Another user mentions you with @.
+2. Observe notification.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>User should receive notification for being mentioned.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>MSG_061</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Verify Voice Recording feature</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, microphone permission denied</t>
-        </is>
-      </c>
+          <t>MSG_089</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n"/>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Verify recording without microphone permission</t>
+          <t>Verify @ mention highlight in message</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>1. Deny microphone permission.
-2. Try to record voice message.</t>
+          <t>1. Receive message where you are mentioned.
+2. Observe message.</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Permission request should appear or error message should display.</t>
+          <t>Your @mention should be highlighted/styled differently.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>MSG_062</t>
+          <t>MSG_090</t>
         </is>
       </c>
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and chat is open</t>
+          <t>User is logged in and group chat is open</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Verify very short recording handling</t>
+          <t>Verify multiple @ mentions in one message</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>1. Press and release recording button quickly (&lt; 1 second).</t>
+          <t>1. Type message with multiple @mentions.
+2. Send message.</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Recording should be cancelled or warning should display.</t>
+          <t>All mentioned users should receive notifications.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n"/>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>MSG_091</t>
+        </is>
+      </c>
       <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="n"/>
-      <c r="E77" s="2" t="n"/>
-      <c r="F77" s="2" t="n"/>
-      <c r="G77" s="2" t="n"/>
-      <c r="H77" s="2" t="n"/>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Verify @ mention with profile picture in suggestions</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>1. Type "@" in input field.
+2. Observe suggestion list.</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Member suggestions should show profile pictures alongside names.</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>MSG_063</t>
+          <t>MSG_094</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -2894,7 +3161,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Verify Emoji feature</t>
+          <t>Verify Custom Message</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -2904,18 +3171,19 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Verify emoji button is visible</t>
+          <t>Verify sending a custom message (poll)</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Observe emoji button.</t>
+          <t>1. Open a conversation.
+2. Create a poll via custom message option.
+3. Send.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Emoji button (smiley face icon) should be visible near input field.</t>
+          <t>Poll should be sent and display in chat with options for recipients to vote.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -2927,7 +3195,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>MSG_064</t>
+          <t>MSG_095</t>
         </is>
       </c>
       <c r="B79" s="2" t="n"/>
@@ -2935,53 +3203,49 @@
       <c r="D79" s="2" t="n"/>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Verify emoji picker opens</t>
+          <t>Verify sending a custom message (meeting link)</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>1. Click on emoji button.
-2. Observe emoji picker.</t>
+          <t>1. Open a conversation.
+2. Send a meeting/conference link as custom message.</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Emoji picker should open with categories (Smileys, Animals, Food, etc.).</t>
+          <t>Custom message with meeting link should display with appropriate formatting and join button.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>MSG_065</t>
+          <t>MSG_096</t>
         </is>
       </c>
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and emoji picker open</t>
-        </is>
-      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Verify emoji categories navigation</t>
+          <t>Verify sending a custom message (collaborative document)</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>1. Open emoji picker.
-2. Click on different category tabs.</t>
+          <t>1. Open a conversation.
+2. Share a collaborative document as custom message.</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Different emoji categories should display when tabs are clicked.</t>
+          <t>Custom message should display with document preview and open/join action.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -2993,7 +3257,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>MSG_066</t>
+          <t>MSG_097</t>
         </is>
       </c>
       <c r="B81" s="2" t="n"/>
@@ -3001,18 +3265,18 @@
       <c r="D81" s="2" t="n"/>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Verify selecting emoji adds to input</t>
+          <t>Verify custom message renders correctly for receiver</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>1. Open emoji picker.
-2. Click on any emoji.</t>
+          <t>1. Send a custom message from User A.
+2. Observe on User B's side.</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Selected emoji should be added to message input field at cursor position.</t>
+          <t>Custom message should render correctly with all interactive elements on receiver's end.</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -3024,7 +3288,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>MSG_067</t>
+          <t>MSG_098</t>
         </is>
       </c>
       <c r="B82" s="2" t="n"/>
@@ -3032,62 +3296,75 @@
       <c r="D82" s="2" t="n"/>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple emoji selection</t>
+          <t>Verify custom message in group chat</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>1. Open emoji picker.
-2. Click multiple emojis.</t>
+          <t>1. Open a group conversation.
+2. Send a custom message.</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>All selected emojis should be added to input field.</t>
+          <t>Custom message should display correctly for all group members.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>MSG_068</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="n"/>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n"/>
+          <t>MSG_100</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Verify Audio Message</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Verify emoji search functionality</t>
+          <t>Verify sending an audio file attachment</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>1. Open emoji picker.
-2. Type in emoji search field.
-3. Observe results.</t>
+          <t>1. Open a conversation.
+2. Click attach.
+3. Select an audio file (.mp3, .wav).
+4. Send.</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Matching emojis should display based on search term.</t>
+          <t>Audio file should upload and display with audio player, file name, and duration.</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>MSG_069</t>
+          <t>MSG_101</t>
         </is>
       </c>
       <c r="B84" s="2" t="n"/>
@@ -3095,31 +3372,30 @@
       <c r="D84" s="2" t="n"/>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Verify recent emojis section</t>
+          <t>Verify audio message playback by sender</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>1. Send message with emoji.
-2. Open emoji picker again.
-3. Check recent section.</t>
+          <t>1. Send an audio message.
+2. Click play on the audio player.</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Recently used emojis should appear in recent/frequently used section.</t>
+          <t>Audio should play with progress bar, play/pause button, and duration indicator.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>MSG_070</t>
+          <t>MSG_102</t>
         </is>
       </c>
       <c r="B85" s="2" t="n"/>
@@ -3127,73 +3403,61 @@
       <c r="D85" s="2" t="n"/>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Verify closing emoji picker</t>
+          <t>Verify audio message playback by receiver</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>1. Open emoji picker.
-2. Click outside picker or close button.</t>
+          <t>1. Receive an audio message.
+2. Click play.</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Emoji picker should close.</t>
+          <t>Audio should download (if needed) and play correctly with player controls.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>MSG_071</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Verify Sticker feature</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>MSG_103</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n"/>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Verify sticker button/tab is visible</t>
+          <t>Verify audio message shows duration</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Observe sticker option.</t>
+          <t>1. Send/receive an audio message.
+2. Observe audio player.</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Sticker button or tab should be visible (may be in emoji picker).</t>
+          <t>Audio duration should display (e.g., '0:45', '2:30').</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>MSG_072</t>
+          <t>MSG_104</t>
         </is>
       </c>
       <c r="B87" s="2" t="n"/>
@@ -3201,18 +3465,20 @@
       <c r="D87" s="2" t="n"/>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Verify sticker picker opens</t>
+          <t>Verify sending recorded audio message</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>1. Click on sticker button/tab.
-2. Observe sticker picker.</t>
+          <t>1. Open a conversation.
+2. Press and hold record button.
+3. Record audio.
+4. Release to send.</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Sticker picker should open with sticker packs.</t>
+          <t>Recorded audio should be sent and display with audio player in chat.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -3224,131 +3490,112 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>MSG_073</t>
+          <t>MSG_105</t>
         </is>
       </c>
       <c r="B88" s="2" t="n"/>
       <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and sticker picker open</t>
-        </is>
-      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Verify sticker packs display</t>
+          <t>Verify audio message in group chat</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>1. Open sticker picker.
-2. Observe available sticker packs.</t>
+          <t>1. Open a group conversation.
+2. Send an audio message.</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Different sticker packs should be visible and selectable.</t>
+          <t>Audio message should display correctly for all group members with sender info.</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>MSG_074</t>
-        </is>
-      </c>
+      <c r="A89" s="2" t="n"/>
       <c r="B89" s="2" t="n"/>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n"/>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending sticker</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>1. Open sticker picker.
-2. Click on any sticker.</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>Sticker should be sent immediately and appear in chat.</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E89" s="2" t="n"/>
+      <c r="F89" s="2" t="n"/>
+      <c r="G89" s="2" t="n"/>
+      <c r="H89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>MSG_075</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="n"/>
-      <c r="C90" s="2" t="n"/>
+          <t>MSG_005</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Verify Message Input field</t>
+        </is>
+      </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>User has received sticker</t>
+          <t>User is logged in and chat is open</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Verify received sticker display</t>
+          <t>Verify empty message cannot be sent</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>1. Receive a sticker from another user.
-2. Observe chat.</t>
+          <t>1. Open any chat conversation.
+2. Leave input field empty.
+3. Click send button.</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Sticker should display properly in chat on left side.</t>
+          <t>Send button should be disabled or message should not be sent.</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>MSG_076</t>
+          <t>MSG_006</t>
         </is>
       </c>
       <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and sticker picker open</t>
-        </is>
-      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Verify sticker pack switching</t>
+          <t>Verify message with only spaces</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>1. Open sticker picker.
-2. Click on different sticker pack.</t>
+          <t>1. Open any chat conversation.
+2. Type only spaces.
+3. Click send button.</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Selected sticker pack's stickers should display.</t>
+          <t>Message should not be sent; spaces-only input should be treated as empty.</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -3358,19 +3605,53 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n"/>
-      <c r="B92" s="2" t="n"/>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n"/>
-      <c r="E92" s="2" t="n"/>
-      <c r="F92" s="2" t="n"/>
-      <c r="G92" s="2" t="n"/>
-      <c r="H92" s="2" t="n"/>
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>MSG_011</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Verify Send button</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Verify send button disabled when empty</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>1. Open any chat conversation.
+2. Leave input field empty.
+3. Observe send button.</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Send button should be disabled or grayed out.</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>MSG_077</t>
+          <t>MSG_018</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -3380,143 +3661,187 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Verify Sticker feature</t>
+          <t>Verify Text message sending</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, no sticker packs available</t>
+          <t>User is logged in, network disconnected</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Verify empty sticker state</t>
+          <t>Verify message sending fails without network</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>1. Open sticker picker with no packs.
-2. Observe display.</t>
+          <t>1. Disconnect network.
+2. Type a message.
+3. Click send.</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Empty state or option to download sticker packs should display.</t>
+          <t>Error indicator should show; message should be queued or show failed status.</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n"/>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>MSG_019</t>
+        </is>
+      </c>
       <c r="B94" s="2" t="n"/>
       <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="n"/>
-      <c r="E94" s="2" t="n"/>
-      <c r="F94" s="2" t="n"/>
-      <c r="G94" s="2" t="n"/>
-      <c r="H94" s="2" t="n"/>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Verify extremely long message handling</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>1. Type a 10000+ character message.
+2. Click send.</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Application should handle gracefully; either send or show character limit warning.</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Low / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>MSG_078</t>
+          <t>MSG_030</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Verify @all mention feature</t>
+          <t>Verify Enter key to send</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and group chat is open</t>
+          <t>User is logged in and input is empty</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Verify typing @all shows suggestion</t>
+          <t>Verify Enter key with empty input</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>1. Open group chat.
-2. Type "@all" in input field.</t>
+          <t>1. Leave input field empty.
+2. Press Enter key.</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>"@all" suggestion should appear to mention all group members.</t>
+          <t>Nothing should happen; empty message should not be sent.</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>MSG_079</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="n"/>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n"/>
+          <t>MSG_044</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Verify Message loading</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, slow network</t>
+        </is>
+      </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Verify selecting @all mention</t>
+          <t>Verify message sending with slow network</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>1. Type "@all".
-2. Select @all from suggestions.</t>
+          <t>1. Simulate slow network.
+2. Send a message.
+3. Observe behavior.</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>"@all" should be added to message with special formatting.</t>
+          <t>Loading indicator should show; message should eventually send or show retry option.</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>MSG_080</t>
+          <t>MSG_045</t>
         </is>
       </c>
       <c r="B97" s="2" t="n"/>
       <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n"/>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, network error</t>
+        </is>
+      </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Verify sending message with @all</t>
+          <t>Verify message retry on failure</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>1. Type message with @all.
-2. Send message.</t>
+          <t>1. Send message during network error.
+2. Observe failed message.
+3. Click retry.</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Message should be sent; all group members should receive notification.</t>
+          <t>Retry option should be available; message should resend on retry.</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -3528,42 +3853,50 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>MSG_081</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="n"/>
-      <c r="C98" s="2" t="n"/>
+          <t>MSG_052</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Verify Attachment feature</t>
+        </is>
+      </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>User has received @all mention</t>
+          <t>User is logged in and chat is open</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Verify @all mention notification</t>
+          <t>Verify unsupported file type handling</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>1. Another user sends @all in group.
-2. Observe notification.</t>
+          <t>1. Click attachment icon.
+2. Try to select unsupported file type.</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>User should receive notification for @all mention.</t>
+          <t>Error message should display or file should not be selectable.</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>MSG_082</t>
+          <t>MSG_053</t>
         </is>
       </c>
       <c r="B99" s="2" t="n"/>
@@ -3571,252 +3904,337 @@
       <c r="D99" s="2" t="n"/>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Verify @all highlight in message</t>
+          <t>Verify file size limit handling</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>1. Receive message with @all.
-2. Observe message display.</t>
+          <t>1. Click attachment icon.
+2. Select file exceeding size limit.</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>"@all" should be highlighted/styled differently in the message.</t>
+          <t>Error message should display indicating file size limit exceeded.</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n"/>
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>MSG_054</t>
+        </is>
+      </c>
       <c r="B100" s="2" t="n"/>
       <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n"/>
-      <c r="E100" s="2" t="n"/>
-      <c r="F100" s="2" t="n"/>
-      <c r="G100" s="2" t="n"/>
-      <c r="H100" s="2" t="n"/>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, network error</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Verify attachment upload failure handling</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Try to send attachment.</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Error message should display; retry option should be available.</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>MSG_061</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Verify Voice Recording feature</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, microphone permission denied</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Verify recording without microphone permission</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>1. Deny microphone permission.
+2. Try to record voice message.</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Permission request should appear or error message should display.</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>MSG_062</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Verify very short recording handling</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>1. Press and release recording button quickly (&lt; 1 second).</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Recording should be cancelled or warning should display.</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>MSG_077</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Verify Sticker feature</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, no sticker packs available</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty sticker state</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>1. Open sticker picker with no packs.
+2. Observe display.</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Empty state or option to download sticker packs should display.</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
           <t>MSG_083</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>Verify @all mention feature</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>User is logged in and one-on-one chat is open</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Verify @all not available in direct chat</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. Open one-on-one chat.
 2. Type "@all".</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>@all suggestion should not appear in direct/one-on-one chats.</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="n"/>
-      <c r="B102" s="2" t="n"/>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n"/>
-      <c r="E102" s="2" t="n"/>
-      <c r="F102" s="2" t="n"/>
-      <c r="G102" s="2" t="n"/>
-      <c r="H102" s="2" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>MSG_084</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Verify @ mention feature</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and group chat is open</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>Verify typing @ shows member suggestions</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>1. Open group chat.
-2. Type "@" in input field.</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>List of group members should appear as suggestions.</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>MSG_085</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="n"/>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n"/>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>Verify filtering members by name</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>1. Type "@Jo" in input field.
-2. Observe suggestions.</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>Only members with names starting with "Jo" should appear (e.g., John).</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>MSG_086</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="n"/>
-      <c r="C105" s="2" t="n"/>
-      <c r="D105" s="2" t="n"/>
+          <t>MSG_092</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Verify @ mention feature</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and group chat is open</t>
+        </is>
+      </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Verify selecting member from suggestions</t>
+          <t>Verify @ with no matching members</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>1. Type "@".
-2. Click on a member name.</t>
+          <t>1. Type "@xyz123" in input field.
+2. Observe suggestions.</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Selected member's name should be added to message with @ prefix.</t>
+          <t>No suggestions should appear or "No members found" message.</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>MSG_087</t>
+          <t>MSG_093</t>
         </is>
       </c>
       <c r="B106" s="2" t="n"/>
       <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n"/>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and one-on-one chat is open</t>
+        </is>
+      </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Verify sending message with @ mention</t>
+          <t>Verify @ mention in direct chat</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>1. Type message with @username.
-2. Send message.</t>
+          <t>1. Open one-on-one chat.
+2. Type "@".</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Message should be sent; mentioned user should receive notification.</t>
+          <t>Only the other user should appear in suggestions (or feature disabled).</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>MSG_088</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="n"/>
-      <c r="C107" s="2" t="n"/>
+          <t>MSG_099</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Verify Custom Message</t>
+        </is>
+      </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>User has been mentioned</t>
+          <t>User is logged in, network disconnected</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Verify @ mention notification</t>
+          <t>Verify custom message fails without network</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>1. Another user mentions you with @.
-2. Observe notification.</t>
+          <t>1. Disconnect network.
+2. Try to send a custom message.</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>User should receive notification for being mentioned.</t>
+          <t>Error message should display or message should queue with retry option.</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -3828,747 +4246,109 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>MSG_089</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="n"/>
-      <c r="C108" s="2" t="n"/>
-      <c r="D108" s="2" t="n"/>
+          <t>MSG_106</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Verify Audio Message</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Verify @ mention highlight in message</t>
+          <t>Verify large audio file exceeding size limit</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>1. Receive message where you are mentioned.
-2. Observe message.</t>
+          <t>1. Try to send an audio file exceeding the size limit.</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Your @mention should be highlighted/styled differently.</t>
+          <t>Error message should display indicating file size limit exceeded.</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>MSG_090</t>
+          <t>MSG_107</t>
         </is>
       </c>
       <c r="B109" s="2" t="n"/>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and group chat is open</t>
+          <t>User is logged in, network disconnected</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple @ mentions in one message</t>
+          <t>Verify audio message fails without network</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>1. Type message with multiple @mentions.
-2. Send message.</t>
+          <t>1. Disconnect network.
+2. Try to send an audio message.</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>All mentioned users should receive notifications.</t>
+          <t>Error message should display or upload should queue with retry option.</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>MSG_091</t>
+          <t>MSG_108</t>
         </is>
       </c>
       <c r="B110" s="2" t="n"/>
       <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n"/>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Verify @ mention with profile picture in suggestions</t>
+          <t>Verify unsupported audio format</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>1. Type "@" in input field.
-2. Observe suggestion list.</t>
+          <t>1. Try to send an unsupported audio file format.</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Member suggestions should show profile pictures alongside names.</t>
+          <t>Error message should display or file should be rejected.</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="n"/>
-      <c r="B111" s="2" t="n"/>
-      <c r="C111" s="2" t="n"/>
-      <c r="D111" s="2" t="n"/>
-      <c r="E111" s="2" t="n"/>
-      <c r="F111" s="2" t="n"/>
-      <c r="G111" s="2" t="n"/>
-      <c r="H111" s="2" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>MSG_092</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Verify @ mention feature</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and group chat is open</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>Verify @ with no matching members</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>1. Type "@xyz123" in input field.
-2. Observe suggestions.</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>No suggestions should appear or "No members found" message.</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>MSG_093</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="n"/>
-      <c r="C113" s="2" t="n"/>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and one-on-one chat is open</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>Verify @ mention in direct chat</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>1. Open one-on-one chat.
-2. Type "@".</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>Only the other user should appear in suggestions (or feature disabled).</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="n"/>
-      <c r="B114" s="2" t="n"/>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n"/>
-      <c r="E114" s="2" t="n"/>
-      <c r="F114" s="2" t="n"/>
-      <c r="G114" s="2" t="n"/>
-      <c r="H114" s="2" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>MSG_094</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Verify Custom Message</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending a custom message (poll)</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a conversation.
-2. Create a poll via custom message option.
-3. Send.</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>Poll should be sent and display in chat with options for recipients to vote.</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>MSG_095</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="n"/>
-      <c r="C116" s="2" t="n"/>
-      <c r="D116" s="2" t="n"/>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending a custom message (meeting link)</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a conversation.
-2. Send a meeting/conference link as custom message.</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>Custom message with meeting link should display with appropriate formatting and join button.</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>MSG_096</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="n"/>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="2" t="n"/>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending a custom message (collaborative document)</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a conversation.
-2. Share a collaborative document as custom message.</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>Custom message should display with document preview and open/join action.</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>MSG_097</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="n"/>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n"/>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>Verify custom message renders correctly for receiver</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>1. Send a custom message from User A.
-2. Observe on User B's side.</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>Custom message should render correctly with all interactive elements on receiver's end.</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>MSG_098</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="n"/>
-      <c r="C119" s="2" t="n"/>
-      <c r="D119" s="2" t="n"/>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>Verify custom message in group chat</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a group conversation.
-2. Send a custom message.</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>Custom message should display correctly for all group members.</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="n"/>
-      <c r="B120" s="2" t="n"/>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n"/>
-      <c r="E120" s="2" t="n"/>
-      <c r="F120" s="2" t="n"/>
-      <c r="G120" s="2" t="n"/>
-      <c r="H120" s="2" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>MSG_099</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>Verify Custom Message</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network disconnected</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>Verify custom message fails without network</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>1. Disconnect network.
-2. Try to send a custom message.</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>Error message should display or message should queue with retry option.</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="n"/>
-      <c r="B122" s="2" t="n"/>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n"/>
-      <c r="E122" s="2" t="n"/>
-      <c r="F122" s="2" t="n"/>
-      <c r="G122" s="2" t="n"/>
-      <c r="H122" s="2" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>MSG_100</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>Verify Audio Message</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending an audio file attachment</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a conversation.
-2. Click attach.
-3. Select an audio file (.mp3, .wav).
-4. Send.</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>Audio file should upload and display with audio player, file name, and duration.</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>MSG_101</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="n"/>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" s="2" t="n"/>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>Verify audio message playback by sender</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>1. Send an audio message.
-2. Click play on the audio player.</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>Audio should play with progress bar, play/pause button, and duration indicator.</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>MSG_102</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="n"/>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n"/>
-      <c r="E125" s="2" t="inlineStr">
-        <is>
-          <t>Verify audio message playback by receiver</t>
-        </is>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>1. Receive an audio message.
-2. Click play.</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>Audio should download (if needed) and play correctly with player controls.</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>MSG_103</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="n"/>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n"/>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>Verify audio message shows duration</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>1. Send/receive an audio message.
-2. Observe audio player.</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>Audio duration should display (e.g., '0:45', '2:30').</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>MSG_104</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="n"/>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n"/>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending recorded audio message</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a conversation.
-2. Press and hold record button.
-3. Record audio.
-4. Release to send.</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>Recorded audio should be sent and display with audio player in chat.</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>MSG_105</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="n"/>
-      <c r="C128" s="2" t="n"/>
-      <c r="D128" s="2" t="n"/>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>Verify audio message in group chat</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a group conversation.
-2. Send an audio message.</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>Audio message should display correctly for all group members with sender info.</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="n"/>
-      <c r="B129" s="2" t="n"/>
-      <c r="C129" s="2" t="n"/>
-      <c r="D129" s="2" t="n"/>
-      <c r="E129" s="2" t="n"/>
-      <c r="F129" s="2" t="n"/>
-      <c r="G129" s="2" t="n"/>
-      <c r="H129" s="2" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>MSG_106</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Verify Audio Message</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>Verify large audio file exceeding size limit</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to send an audio file exceeding the size limit.</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>Error message should display indicating file size limit exceeded.</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>MSG_107</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="n"/>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network disconnected</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>Verify audio message fails without network</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>1. Disconnect network.
-2. Try to send an audio message.</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>Error message should display or upload should queue with retry option.</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>MSG_108</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="n"/>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>Verify unsupported audio format</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to send an unsupported audio file format.</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>Error message should display or file should be rejected.</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
@@ -5420,7 +5200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5548,41 +5328,61 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>MSG_128</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Verify sending media at minimum file size (1 byte)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a 1-byte file.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>File should either send or be rejected as too small. No crash.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>MSG_127</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
+          <t>MSG_129</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Verify sending text exceeding max character limit</t>
+          <t>Verify sending media at exactly max file size</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1. Try to send a message exceeding the max limit.</t>
+          <t>1. Send a file at exactly the maximum allowed size.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Should be blocked at input or rejected by server with error.</t>
+          <t>File should upload and send successfully.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -5604,62 +5404,32 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>MSG_128</t>
+          <t>MSG_127</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Verify sending media at minimum file size (1 byte)</t>
+          <t>Verify sending text exceeding max character limit</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1. Send a 1-byte file.</t>
+          <t>1. Try to send a message exceeding the max limit.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>File should either send or be rejected as too small. No crash.</t>
+          <t>Should be blocked at input or rejected by server with error.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>MSG_129</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending media at exactly max file size</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1. Send a file at exactly the maximum allowed size.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>File should upload and send successfully.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>

--- a/Send_Message/Send_Message_Test_Cases.xlsx
+++ b/Send_Message/Send_Message_Test_Cases.xlsx
@@ -51,7 +51,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -65,11 +65,12 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -77,6 +78,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3519,838 +3524,1273 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n"/>
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>MSG_006</t>
+        </is>
+      </c>
       <c r="B89" s="2" t="n"/>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n"/>
-      <c r="E89" s="2" t="n"/>
-      <c r="F89" s="2" t="n"/>
-      <c r="G89" s="2" t="n"/>
-      <c r="H89" s="2" t="n"/>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Verify message with only spaces</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>1. Open any chat conversation.
+2. Type only spaces.
+3. Click send button.</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Message should not be sent; spaces-only input should be treated as empty.</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>MSG_019</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Verify extremely long message handling</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>1. Type a 10000+ character message.
+2. Click send.</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Application should handle gracefully; either send or show character limit warning.</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Low / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>MSG_045</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, network error</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Verify message retry on failure</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>1. Send message during network error.
+2. Observe failed message.
+3. Click retry.</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Retry option should be available; message should resend on retry.</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>MSG_053</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n"/>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Verify file size limit handling</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>1. Click attachment icon.
+2. Select file exceeding size limit.</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Error message should display indicating file size limit exceeded.</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>MSG_054</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, network error</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Verify attachment upload failure handling</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Try to send attachment.</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Error message should display; retry option should be available.</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>MSG_062</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Verify very short recording handling</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>1. Press and release recording button quickly (&lt; 1 second).</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Recording should be cancelled or warning should display.</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>MSG_093</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and one-on-one chat is open</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Verify @ mention in direct chat</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>1. Open one-on-one chat.
+2. Type "@".</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Only the other user should appear in suggestions (or feature disabled).</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>MSG_107</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, network disconnected</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Verify audio message fails without network</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Try to send an audio message.</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Error message should display or upload should queue with retry option.</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>MSG_108</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Verify unsupported audio format</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to send an unsupported audio file format.</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Error message should display or file should be rejected.</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>MSG_143</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Blocked User - Composer Hidden</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>User is blocked</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Verify composer replaced with blocked message</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>1. Open conversation with blocked user
+2. Observe composer area</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Composer should be hidden, 'Cannot send to blocked user' message displayed</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>MSG_144</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Blocked User - Unblock From Composer</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Blocked user message shown</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Verify unblock link in composer area</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>1. Open blocked user conversation
+2. Click 'Click to unblock' link</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>User should be unblocked, composer should reappear</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>MSG_145</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Blocked User - Real-time Block Update</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Conversation open, user blocked from details</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Verify composer updates when user blocked</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>1. Open conversation
+2. Block user from details panel
+3. Observe composer</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Composer should immediately hide and show blocked message</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>MSG_146</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Blocked User - Real-time Unblock Update</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Blocked user conversation open</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Verify composer updates when user unblocked</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>1. Open blocked user conversation
+2. Unblock from details
+3. Observe composer</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Composer should immediately reappear</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>MSG_147</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Delivery - Auto Mark Delivered</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Message received while not in chat tab</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Verify messages auto-marked as delivered</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>1. Be on Users/Groups tab
+2. Receive a message
+3. Check delivery status</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Message should be auto-marked as delivered via CometChat.markAsDelivered()</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>MSG_148</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Delivery - Skip Own Messages</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Own message received via listener</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Verify own messages not marked as delivered</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message
+2. Observe delivery marking</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Messages from logged-in user should not be marked as delivered again</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>MSG_149</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Delivery - Skip Already Delivered</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Message already has deliveredAt</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Verify already-delivered messages skipped</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>1. Receive message with deliveredAt set
+2. Observe</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Should not call markAsDelivered for already-delivered messages</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>MSG_150</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Fresh Chat - Detection</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>New chat with no messages</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Verify fresh chat is detected</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>1. Start new conversation with user
+2. Observe state</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>isFreshChat should be set to true via ccActiveChatChanged event</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>MSG_151</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Fresh Chat - First Message Converts</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Fresh chat, first message sent</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Verify fresh chat converts to conversation on first message</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>1. Open fresh chat
+2. Send first message
+3. Observe</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>isFreshChat should become false, conversation should be fetched via getConversation()</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>MSG_152</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Fresh Chat - First Message Received</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Fresh chat, message received</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Verify incoming message converts fresh chat</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>1. Open fresh chat
+2. Receive message from other user
+3. Observe</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>isFreshChat should become false, conversation created</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="n"/>
+      <c r="B108" s="3" t="n"/>
+      <c r="C108" s="3" t="n"/>
+      <c r="D108" s="3" t="n"/>
+      <c r="E108" s="3" t="n"/>
+      <c r="F108" s="3" t="n"/>
+      <c r="G108" s="3" t="n"/>
+      <c r="H108" s="3" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
           <t>MSG_005</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>Verify Message Input field</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Verify empty message cannot be sent</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
 2. Leave input field empty.
 3. Click send button.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>Send button should be disabled or message should not be sent.</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>MSG_006</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="n"/>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n"/>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>Verify message with only spaces</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>1. Open any chat conversation.
-2. Type only spaces.
-3. Click send button.</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>Message should not be sent; spaces-only input should be treated as empty.</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>MSG_011</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>Verify Send button</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Verify send button disabled when empty</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
 2. Leave input field empty.
 3. Observe send button.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>Send button should be disabled or grayed out.</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>MSG_018</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>Verify Text message sending</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Verify message sending fails without network</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Type a message.
 3. Click send.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>Error indicator should show; message should be queued or show failed status.</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>MSG_019</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="n"/>
-      <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>Verify extremely long message handling</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>1. Type a 10000+ character message.
-2. Click send.</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>Application should handle gracefully; either send or show character limit warning.</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>Low / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>MSG_030</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>Verify Enter key to send</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>User is logged in and input is empty</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Verify Enter key with empty input</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>1. Leave input field empty.
 2. Press Enter key.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>Nothing should happen; empty message should not be sent.</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>MSG_044</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>Verify Message loading</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>User is logged in, slow network</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Verify message sending with slow network</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>1. Simulate slow network.
 2. Send a message.
 3. Observe behavior.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>Loading indicator should show; message should eventually send or show retry option.</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>MSG_045</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="n"/>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network error</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>Verify message retry on failure</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>1. Send message during network error.
-2. Observe failed message.
-3. Click retry.</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>Retry option should be available; message should resend on retry.</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>MSG_052</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t>Verify Attachment feature</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Verify unsupported file type handling</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>1. Click attachment icon.
 2. Try to select unsupported file type.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>Error message should display or file should not be selectable.</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>MSG_053</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="n"/>
-      <c r="C99" s="2" t="n"/>
-      <c r="D99" s="2" t="n"/>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>Verify file size limit handling</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>1. Click attachment icon.
-2. Select file exceeding size limit.</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>Error message should display indicating file size limit exceeded.</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>MSG_054</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="n"/>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network error</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>Verify attachment upload failure handling</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>1. Disconnect network.
-2. Try to send attachment.</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>Error message should display; retry option should be available.</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>MSG_061</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
         <is>
           <t>Verify Voice Recording feature</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>User is logged in, microphone permission denied</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Verify recording without microphone permission</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>1. Deny microphone permission.
 2. Try to record voice message.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>Permission request should appear or error message should display.</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>MSG_062</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="n"/>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>Verify very short recording handling</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>1. Press and release recording button quickly (&lt; 1 second).</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Recording should be cancelled or warning should display.</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>MSG_077</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>Verify Sticker feature</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>User is logged in, no sticker packs available</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Verify empty sticker state</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>1. Open sticker picker with no packs.
 2. Observe display.</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>Empty state or option to download sticker packs should display.</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>MSG_083</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>Verify @all mention feature</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>User is logged in and one-on-one chat is open</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Verify @all not available in direct chat</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>1. Open one-on-one chat.
 2. Type "@all".</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>@all suggestion should not appear in direct/one-on-one chats.</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>MSG_092</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
         <is>
           <t>Verify @ mention feature</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>User is logged in and group chat is open</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Verify @ with no matching members</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>1. Type "@xyz123" in input field.
 2. Observe suggestions.</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>No suggestions should appear or "No members found" message.</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>MSG_093</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="n"/>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and one-on-one chat is open</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>Verify @ mention in direct chat</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>1. Open one-on-one chat.
-2. Type "@".</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Only the other user should appear in suggestions (or feature disabled).</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>MSG_099</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
         <is>
           <t>Verify Custom Message</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Verify custom message fails without network</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Try to send a custom message.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>Error message should display or message should queue with retry option.</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>MSG_106</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
         <is>
           <t>Verify Audio Message</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Verify large audio file exceeding size limit</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>1. Try to send an audio file exceeding the size limit.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>Error message should display indicating file size limit exceeded.</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>High / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>MSG_107</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="n"/>
-      <c r="C109" s="2" t="n"/>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network disconnected</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>Verify audio message fails without network</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>1. Disconnect network.
-2. Try to send an audio message.</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>Error message should display or upload should queue with retry option.</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>MSG_108</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="n"/>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>Verify unsupported audio format</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to send an unsupported audio file format.</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>Error message should display or file should be rejected.</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4533,6 +4973,136 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>MSG_153</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Blocked User - Event Subscription</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Conversation open</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Verify block/unblock event subscriptions</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1. Open conversation
+2. Block user
+3. Unblock user</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>ccUserBlocked and ccUserUnblocked events should update composer state</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>MSG_154</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Delivery - All Message Types</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Various message types received</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Verify delivery marking for all types</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1. Receive text, media, and custom messages
+2. Check delivery</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>All three message types should trigger markAsDelivered via respective listeners</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>MSG_155</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Fresh Chat - All Message Types Convert</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Fresh chat</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Verify all message types convert fresh chat</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1. Send text/media/custom message in fresh chat
+2. Observe</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>ccMessageSent, onTextMessageReceived, onMediaMessageReceived, onCustomMessageReceived all handle conversion</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4542,179 +5112,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00FFC000"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TestCase_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Sentiment</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Results</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>MSG_112</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Regression: Send Message</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Verify message sending works after failed attempt</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>1. Send a message during network error (fails).
-2. Restore network.
-3. Retry sending.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Message should send successfully on retry. No duplicate messages.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>MSG_113</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Verify message order preserved after rapid sending</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>1. Send 10 messages rapidly one after another.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>All 10 messages should appear in the exact order they were sent.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>MSG_114</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Verify media message sending after app crash recovery</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1. Start uploading a large file.
-2. Force close app.
-3. Reopen.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Upload should either resume or show failed state with retry option.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Medium / High</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00FF0000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4776,17 +5173,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MSG_115</t>
+          <t>MSG_112</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Security: Send Message</t>
+          <t>Regression: Send Message</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4796,29 +5193,31 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Verify message cannot be sent to unauthorized conversation</t>
+          <t>Verify message sending works after failed attempt</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>1. Try to send a message to a group you've been removed from.</t>
+          <t>1. Send a message during network error (fails).
+2. Restore network.
+3. Retry sending.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Message should fail with appropriate error. No message delivered.</t>
+          <t>Message should send successfully on retry. No duplicate messages.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>High / Critical</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MSG_116</t>
+          <t>MSG_113</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -4826,29 +5225,29 @@
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Verify file upload scans for malware (if applicable)</t>
+          <t>Verify message order preserved after rapid sending</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1. Upload a file flagged as potentially malicious.</t>
+          <t>1. Send 10 messages rapidly one after another.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>File should be rejected or quarantined based on security policy.</t>
+          <t>All 10 messages should appear in the exact order they were sent.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>High / Critical</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MSG_117</t>
+          <t>MSG_114</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -4856,18 +5255,187 @@
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Verify media message sending after app crash recovery</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1. Start uploading a large file.
+2. Force close app.
+3. Reopen.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Upload should either resume or show failed state with retry option.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FF0000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>MSG_116</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Verify file upload scans for malware (if applicable)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1. Upload a file flagged as potentially malicious.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>File should be rejected or quarantined based on security policy.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>MSG_117</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>Verify message encryption in transit</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Inspect network traffic.</t>
         </is>
       </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Message content should be encrypted (HTTPS/WSS). Not visible in plain text.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>MSG_118</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Verify spoofed sender ID prevention</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to send a message with a manipulated sender ID via API.</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Message content should be encrypted (HTTPS/WSS). Not visible in plain text.</t>
+          <t>Server should reject the message. Sender ID should be validated server-side.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -4877,30 +5445,52 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>MSG_118</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Verify spoofed sender ID prevention</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to send a message with a manipulated sender ID via API.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Server should reject the message. Sender ID should be validated server-side.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>MSG_115</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Security: Send Message</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Verify message cannot be sent to unauthorized conversation</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to send a message to a group you've been removed from.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Message should fail with appropriate error. No message delivered.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
@@ -4915,6 +5505,298 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>MSG_119</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case: Send Message</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Verify sending message while receiver is typing</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1. Both users type simultaneously.
+2. Both send at the same time.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Both messages should appear in correct order. No message loss.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>MSG_120</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Verify sending message to a user who blocked you</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message to a user who has blocked you.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Message should fail or appear sent but not delivered. Appropriate handling per app policy.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>MSG_121</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Verify sending message immediately after joining a group</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1. Join a new group.
+2. Immediately send a message.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Message should send successfully. Should appear for all group members.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>MSG_122</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Verify sending multiple media types in sequence</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1. Send an image.
+2. Immediately send a video.
+3. Send a document.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>All three should upload and appear in correct order. No upload conflicts.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>MSG_124</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Verify sending corrupted media file</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1. Rename a .txt file to .jpg.
+2. Try to send as image.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>App should detect invalid file and show error. Should not crash.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>MSG_123</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case: Send Message</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Verify sending message with zero-width characters</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a message containing only zero-width unicode characters.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Message should be blocked or displayed as empty. No invisible messages.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4976,7 +5858,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MSG_119</t>
+          <t>MSG_125</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -4986,7 +5868,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Edge Case: Send Message</t>
+          <t>Boundary: Send Message</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4996,30 +5878,29 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Verify sending message while receiver is typing</t>
+          <t>Verify sending text message with exactly 1 character</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>1. Both users type simultaneously.
-2. Both send at the same time.</t>
+          <t>1. Send 'a'.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Both messages should appear in correct order. No message loss.</t>
+          <t>Single character message should send and display correctly.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MSG_120</t>
+          <t>MSG_126</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -5027,60 +5908,63 @@
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Verify sending message to a user who blocked you</t>
+          <t>Verify sending text at max character limit</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1. Send a message to a user who has blocked you.</t>
+          <t>1. Send a message at exactly the maximum character limit.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Message should fail or appear sent but not delivered. Appropriate handling per app policy.</t>
+          <t>Message should send successfully.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MSG_121</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n"/>
+          <t>MSG_128</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Verify sending message immediately after joining a group</t>
+          <t>Verify sending media at minimum file size (1 byte)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1. Join a new group.
-2. Immediately send a message.</t>
+          <t>1. Send a 1-byte file.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Message should send successfully. Should appear for all group members.</t>
+          <t>File should either send or be rejected as too small. No crash.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>MSG_122</t>
+          <t>MSG_129</t>
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
@@ -5088,41 +5972,39 @@
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Verify sending multiple media types in sequence</t>
+          <t>Verify sending media at exactly max file size</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1. Send an image.
-2. Immediately send a video.
-3. Send a document.</t>
+          <t>1. Send a file at exactly the maximum allowed size.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>All three should upload and appear in correct order. No upload conflicts.</t>
+          <t>File should upload and send successfully.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
+      <c r="A6" s="3" t="n"/>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>MSG_123</t>
+          <t>MSG_127</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -5130,77 +6012,52 @@
           <t>Negative</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Edge Case: Send Message</t>
-        </is>
-      </c>
+      <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Verify sending message with zero-width characters</t>
+          <t>Verify sending text exceeding max character limit</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1. Send a message containing only zero-width unicode characters.</t>
+          <t>1. Try to send a message exceeding the max limit.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Message should be blocked or displayed as empty. No invisible messages.</t>
+          <t>Should be blocked at input or rejected by server with error.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Medium / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>MSG_124</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending corrupted media file</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1. Rename a .txt file to .jpg.
-2. Try to send as image.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>App should detect invalid file and show error. Should not crash.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Medium / High</t>
-        </is>
-      </c>
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="007030A0"/>
+    <tabColor rgb="0000B0F0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5258,7 +6115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MSG_125</t>
+          <t>MSG_130</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -5268,39 +6125,40 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Boundary: Send Message</t>
+          <t>Equivalence Partitioning: Message Destinations</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and chat is open</t>
+          <t>User is logged in</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Verify sending text message with exactly 1 character</t>
+          <t>Verify sending message in one-on-one chat</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>1. Send 'a'.</t>
+          <t>1. Open a one-on-one conversation.
+2. Send a text message.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Single character message should send and display correctly.</t>
+          <t>Message should deliver to the single recipient.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MSG_126</t>
+          <t>MSG_131</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -5308,254 +6166,6 @@
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Verify sending text at max character limit</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>1. Send a message at exactly the maximum character limit.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Message should send successfully.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>MSG_128</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending media at minimum file size (1 byte)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1. Send a 1-byte file.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>File should either send or be rejected as too small. No crash.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>MSG_129</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending media at exactly max file size</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1. Send a file at exactly the maximum allowed size.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>File should upload and send successfully.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>MSG_127</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending text exceeding max character limit</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to send a message exceeding the max limit.</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Should be blocked at input or rejected by server with error.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="0000B0F0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TestCase_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Sentiment</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Results</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>MSG_130</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning: Message Destinations</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending message in one-on-one chat</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a one-on-one conversation.
-2. Send a text message.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Message should deliver to the single recipient.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>MSG_131</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
           <t>Verify sending message in small group (2-10 members)</t>
         </is>
       </c>
@@ -5923,6 +6533,16 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
